--- a/docs/Financial/BitWealth_Cashflow_Forecast_v2.0.xlsx
+++ b/docs/Financial/BitWealth_Cashflow_Forecast_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davin\Dropbox\BitWealth\bitwealth-lth-pvr\bitwealth-lth-pvr\docs\Financial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E14E4C-F5CB-46C6-8EE3-BF0EFF92AC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DBE473-1085-4272-ACDC-47B18A3F55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Annual portfolio return — Years 1–3 (p.a.)</t>
-  </si>
-  <si>
-    <t>50% p.a. BTC bull cycle; divided by 12 for monthly</t>
   </si>
   <si>
     <t>Annual portfolio return — Year 4 (p.a.)</t>
@@ -173,13 +170,7 @@
     <t>First new client — start month</t>
   </si>
   <si>
-    <t>Month 4 = September 2026 (first quarter after founding 3)</t>
-  </si>
-  <si>
     <t>Subsequent new clients — interval (months)</t>
-  </si>
-  <si>
-    <t>1 new client every 3 months (quarterly). Change to 1 for monthly growth</t>
   </si>
   <si>
     <t>New client initial lump sum (R)</t>
@@ -416,13 +407,22 @@
     <t>Cloud, Supabase, On-Chain API, Netlify, Domains, etc.</t>
   </si>
   <si>
-    <t>10% — BTC bear/consolidation year; set to e.g. 20% for optimistic Y4</t>
-  </si>
-  <si>
     <t>CLIENT 4 (Founding — lined-up)</t>
   </si>
   <si>
     <t>Conservative R5k/month per new client</t>
+  </si>
+  <si>
+    <t>35% p.a. BTC bull cycle; divided by 12 for monthly</t>
+  </si>
+  <si>
+    <t>9% — BTC bear/consolidation year; set to e.g. 20% for optimistic Y4</t>
+  </si>
+  <si>
+    <t>1 new client every X months. Change to 1 for monthly growth</t>
+  </si>
+  <si>
+    <t>Month 3 = August 2026 (first quarter after founding 3)</t>
   </si>
 </sst>
 </file>
@@ -993,148 +993,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>520312.50000000006</c:v>
+                  <c:v>514218.74999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5999387.6953125009</c:v>
+                  <c:v>5927398.095703125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6497209.6954345722</c:v>
+                  <c:v>6408394.0727996826</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7071575.7533741025</c:v>
+                  <c:v>6907689.3522527358</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7673514.30888227</c:v>
+                  <c:v>7425779.7012566905</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8304093.7103527328</c:v>
+                  <c:v>7963174.3391311113</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8964423.7659206372</c:v>
+                  <c:v>8520396.3029013611</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9655657.3549429178</c:v>
+                  <c:v>9097982.8228301071</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10378992.102214169</c:v>
+                  <c:v>9696485.7081710361</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11135672.117364319</c:v>
+                  <c:v>10316471.743423408</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11926989.801979853</c:v>
+                  <c:v>10958523.095373834</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12754287.727089684</c:v>
+                  <c:v>11623237.731219329</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13618960.583759764</c:v>
+                  <c:v>12311229.848073853</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14522457.209647952</c:v>
+                  <c:v>13023130.314168718</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15466282.69448184</c:v>
+                  <c:v>13759587.122065775</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16394938.067538049</c:v>
+                  <c:v>14521265.854210962</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17359782.726571899</c:v>
+                  <c:v>15308850.161164761</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18362229.2111305</c:v>
+                  <c:v>16123042.252855334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19403745.28329774</c:v>
+                  <c:v>16964563.403209459</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20485856.090039205</c:v>
+                  <c:v>17834154.468526233</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21610146.410352319</c:v>
+                  <c:v>18732576.419968322</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22778262.990552738</c:v>
+                  <c:v>19660610.890555933</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23991916.971159283</c:v>
+                  <c:v>20619060.737059057</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>25252886.408976052</c:v>
+                  <c:v>21608750.61719444</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>26563018.898111507</c:v>
+                  <c:v>22630527.582544833</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>27924234.29382199</c:v>
+                  <c:v>23685261.687629446</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>29338527.543219768</c:v>
+                  <c:v>24773846.615566254</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>30807971.627044745</c:v>
+                  <c:v>25897200.320778869</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>32334720.616864435</c:v>
+                  <c:v>27056265.689213134</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>33921012.852238201</c:v>
+                  <c:v>28252011.216541074</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>35569174.242560796</c:v>
+                  <c:v>29485431.704843152</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>37281621.698485255</c:v>
+                  <c:v>30757548.978273161</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>39060866.69801867</c:v>
+                  <c:v>32069412.618223578</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>40909518.99258434</c:v>
+                  <c:v>33422100.71852383</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>42830290.458552703</c:v>
+                  <c:v>34816720.661218077</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>44825999.09995956</c:v>
+                  <c:v>36254409.913484216</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>45496713.921638824</c:v>
+                  <c:v>36995762.553343765</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46172695.078086659</c:v>
+                  <c:v>37747337.967890143</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46853983.984099418</c:v>
+                  <c:v>38509206.512892544</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>47540622.380662285</c:v>
+                  <c:v>39281439.028908409</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>48232652.337522417</c:v>
+                  <c:v>40064106.844628021</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>48930116.25578218</c:v>
+                  <c:v>40857281.780242249</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>49633056.87051291</c:v>
+                  <c:v>41661036.150833517</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>50341517.2533895</c:v>
+                  <c:v>42475442.769790232</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>51055540.815345481</c:v>
+                  <c:v>43300574.952244766</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>51775171.309249386</c:v>
+                  <c:v>44136506.518535219</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>52500452.832602113</c:v>
+                  <c:v>44983311.797691114</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>53231429.830255568</c:v>
+                  <c:v>45841065.630943067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1461,148 +1461,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>4270.833333333333</c:v>
+                  <c:v>4114.583333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61221.158854166664</c:v>
+                  <c:v>54685.367838541664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24935.820515950527</c:v>
+                  <c:v>18436.467361450195</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26838.512703577686</c:v>
+                  <c:v>19349.547670270604</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28443.767549087614</c:v>
+                  <c:v>20300.590436750044</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30129.528066299903</c:v>
+                  <c:v>21290.603412230485</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31898.849030127174</c:v>
+                  <c:v>22320.621121073924</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33754.901224412853</c:v>
+                  <c:v>23391.705572541323</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>35700.975851370276</c:v>
+                  <c:v>24504.946991616693</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>37740.489108776754</c:v>
+                  <c:v>25661.464569281154</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>39876.986941311217</c:v>
+                  <c:v>26862.407232755006</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42114.14997266703</c:v>
+                  <c:v>28108.954436239714</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>44455.79862532494</c:v>
+                  <c:v>29402.316972705954</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46905.898435133189</c:v>
+                  <c:v>30743.737807288457</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>49468.565568114442</c:v>
+                  <c:v>32134.492932863162</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>51506.405880535494</c:v>
+                  <c:v>33575.892248397788</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>54011.093780235926</c:v>
+                  <c:v>35069.280460682465</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>56611.12904855849</c:v>
+                  <c:v>36616.038010063436</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>59310.144963204613</c:v>
+                  <c:v>38217.58202081926</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>62111.913395939198</c:v>
+                  <c:v>39875.367276836252</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>65020.350105180471</c:v>
+                  <c:v>41590.88722325713</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>68039.520230933747</c:v>
+                  <c:v>43365.674994795008</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>71173.643999814798</c:v>
+                  <c:v>45201.304471423391</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>74427.102648204542</c:v>
+                  <c:v>47099.391362171395</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>77804.444571885426</c:v>
+                  <c:v>49061.59431777351</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>81310.39171082995</c:v>
+                  <c:v>51089.616072942474</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>84949.846178143678</c:v>
+                  <c:v>53185.204619055097</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>88727.897142510978</c:v>
+                  <c:v>55350.154408061091</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>92649.827973849184</c:v>
+                  <c:v>57586.307588447497</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>96721.123662249243</c:v>
+                  <c:v>59895.555274112638</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>100947.47852066834</c:v>
+                  <c:v>62279.838847027117</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>105334.80418223889</c:v>
+                  <c:v>64741.151294581912</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>109889.23790347748</c:v>
+                  <c:v>67281.538582548543</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>114617.15118510813</c:v>
+                  <c:v>69903.101064600356</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>119525.15872266423</c:v>
+                  <c:v>72607.994929369364</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>124620.12769950004</c:v>
+                  <c:v>75398.433686039381</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>27901.837487065244</c:v>
+                  <c:v>22830.434491586358</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>28224.792899141059</c:v>
+                  <c:v>23242.804603706478</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>28550.219637975355</c:v>
+                  <c:v>23661.48975677737</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>28878.13663795331</c:v>
+                  <c:v>24086.532830832955</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>29208.562978713402</c:v>
+                  <c:v>24517.976997201175</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>29541.517886263166</c:v>
+                  <c:v>24955.865720483747</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>29877.020734103535</c:v>
+                  <c:v>25400.242760549449</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>30215.091044361892</c:v>
+                  <c:v>25851.152174540905</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>30555.748488933721</c:v>
+                  <c:v>26308.638318895039</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>30899.012890633127</c:v>
+                  <c:v>26772.745851377294</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>31244.904224352213</c:v>
+                  <c:v>27243.519733129615</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>31593.442618229306</c:v>
+                  <c:v>27721.005230732451</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1832,7 +1832,7 @@
                   <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>79885.719317724215</c:v>
+                  <c:v>77058.094328048319</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>45000</c:v>
@@ -1868,7 +1868,7 @@
                   <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>111132.21602244013</c:v>
+                  <c:v>102021.87654298611</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>45000</c:v>
@@ -1904,7 +1904,7 @@
                   <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>160064.9977498989</c:v>
+                  <c:v>138636.02478371054</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>45000</c:v>
@@ -1940,7 +1940,7 @@
                   <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>181078.57457563892</c:v>
+                  <c:v>162602.66407735768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2249,148 +2249,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>-97312.5</c:v>
+                  <c:v>-78315.416666666672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-87674.674479166672</c:v>
+                  <c:v>-56060.048828125007</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-114322.18729654947</c:v>
+                  <c:v>-70053.581466674805</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-149067.00792630512</c:v>
+                  <c:v>-93134.033796404197</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-182206.57371055085</c:v>
+                  <c:v>-115263.44335965415</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-213660.37897758427</c:v>
+                  <c:v>-136402.83994742366</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-253344.86328079045</c:v>
+                  <c:v>-166512.21882634974</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-291173.29538971093</c:v>
+                  <c:v>-195550.51325380843</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-327055.65287167398</c:v>
+                  <c:v>-223475.56626219174</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-360898.49709623057</c:v>
+                  <c:v>-250244.1016929106</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-392604.84348825266</c:v>
+                  <c:v>-275811.69446015562</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-456959.74616664316</c:v>
+                  <c:v>-332190.83435196424</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-484087.28087465157</c:v>
+                  <c:v>-355218.51737925829</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-508764.71577285172</c:v>
+                  <c:v>-376904.77957196982</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-530879.48353807058</c:v>
+                  <c:v>-397200.28663910663</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-550956.41099086846</c:v>
+                  <c:v>-416054.39439070883</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-568528.65054396586</c:v>
+                  <c:v>-433415.11393002636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-583500.8548287407</c:v>
+                  <c:v>-449229.07591996295</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-595774.04319886945</c:v>
+                  <c:v>-463441.49389914371</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-605245.46313626354</c:v>
+                  <c:v>-475996.12662230746</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-611808.44636441639</c:v>
+                  <c:v>-486835.23939905036</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-615352.25946681597</c:v>
+                  <c:v>-495899.56440425536</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-615761.94880033447</c:v>
+                  <c:v>-503128.25993283198</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-679050.39550790342</c:v>
+                  <c:v>-565480.74511364673</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-672829.28426935128</c:v>
+                  <c:v>-568849.15079587325</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-663102.22589185461</c:v>
+                  <c:v>-570189.53472293075</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-649735.71304704424</c:v>
+                  <c:v>-569434.3301038756</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-632591.14923786663</c:v>
+                  <c:v>-566514.17569581454</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-611524.65459735075</c:v>
+                  <c:v>-561357.86810736707</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-586386.86426843482</c:v>
+                  <c:v>-553892.31283325446</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-557022.71908109984</c:v>
+                  <c:v>-544042.4739862273</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-523271.24823219428</c:v>
+                  <c:v>-531731.32269164536</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-484965.34366205015</c:v>
+                  <c:v>-516879.7841090968</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-441931.52581027534</c:v>
+                  <c:v>-499406.68304449646</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-393989.70042094443</c:v>
+                  <c:v>-479228.68811512709</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-456017.90380467661</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-473116.06631761137</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-489891.27341847029</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-506341.05378049496</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-522462.91714254167</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-538254.35416382831</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-553712.8362775651</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-568835.81554346159</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-583620.72449909966</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-598064.97601016588</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-612165.9631195328</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-625921.05889518058</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-775406.19085259014</c:v>
+                  <c:v>-549896.27921279822</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2587,148 +2587,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>26583.333333333332</c:v>
+                  <c:v>7430</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53166.666666666664</c:v>
+                  <c:v>14860</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79750</c:v>
+                  <c:v>22290</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>106333.33333333333</c:v>
+                  <c:v>29720</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>132916.66666666666</c:v>
+                  <c:v>37150</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>159500</c:v>
+                  <c:v>44580</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>186083.33333333334</c:v>
+                  <c:v>52010</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>212666.66666666669</c:v>
+                  <c:v>59440</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>239250.00000000003</c:v>
+                  <c:v>66870</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>265833.33333333337</c:v>
+                  <c:v>74300</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>292416.66666666669</c:v>
+                  <c:v>81730</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>319000</c:v>
+                  <c:v>89160</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>345583.33333333331</c:v>
+                  <c:v>96590</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>372166.66666666663</c:v>
+                  <c:v>104020</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>398749.99999999994</c:v>
+                  <c:v>111450</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>425333.33333333326</c:v>
+                  <c:v>118880</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>451916.66666666657</c:v>
+                  <c:v>126310</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>478499.99999999988</c:v>
+                  <c:v>133740</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>505083.3333333332</c:v>
+                  <c:v>141170</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>531666.66666666651</c:v>
+                  <c:v>148600</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>558249.99999999988</c:v>
+                  <c:v>156030</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>584833.33333333326</c:v>
+                  <c:v>163460</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>611416.66666666663</c:v>
+                  <c:v>170890</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>638000</c:v>
+                  <c:v>178320</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>664583.33333333337</c:v>
+                  <c:v>185750</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>691166.66666666674</c:v>
+                  <c:v>193180</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>717750.00000000012</c:v>
+                  <c:v>200610</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>744333.33333333349</c:v>
+                  <c:v>208040</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>770916.66666666686</c:v>
+                  <c:v>215470</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>797500.00000000023</c:v>
+                  <c:v>222900</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>824083.3333333336</c:v>
+                  <c:v>230330</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>850666.66666666698</c:v>
+                  <c:v>237760</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>877250.00000000035</c:v>
+                  <c:v>245190</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>903833.33333333372</c:v>
+                  <c:v>252620</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>930416.66666666709</c:v>
+                  <c:v>260050</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>267480</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>245310.43449158635</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>223553.23909529281</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>202214.72885207017</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>181301.26168290313</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>160819.23868010432</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>140775.10440058805</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>121175.3471611375</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>102026.49933567841</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>83335.137654573453</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>65107.883505950747</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>47351.403239080362</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>957000.00000000047</c:v>
+                  <c:v>-87530.255607544881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3242,18 +3242,18 @@
         <v>3</v>
       </c>
       <c r="B5" s="11">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="11">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>115</v>
@@ -3261,143 +3261,143 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="12">
         <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="12">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="13">
+        <f>267480/36</f>
+        <v>7430</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="13">
-        <f>319000/12</f>
-        <v>26583.333333333332</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="13">
+        <v>50000</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="14">
-        <v>50000</v>
-      </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>15</v>
       </c>
       <c r="B13" s="13">
         <v>20000</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="13">
         <v>30000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="13">
         <v>40000</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="11">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="13">
         <v>5000</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="13">
         <v>3000</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="12">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="13">
         <v>300000</v>
@@ -3406,58 +3406,58 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="13">
         <v>200000</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="12">
         <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="12">
         <v>0</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="13">
         <v>40000</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="11">
         <v>7.4999999999999997E-3</v>
@@ -3484,36 +3484,36 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="11">
         <v>0.1</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="12">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="13">
         <v>5000000</v>
@@ -3522,58 +3522,58 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="12">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="11">
         <v>0.1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" s="12">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" s="12">
         <v>0</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B44" s="13">
         <v>20000</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="11">
         <v>7.4999999999999997E-3</v>
@@ -3600,142 +3600,142 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="12">
+        <v>48</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B49" s="12">
-        <v>12</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51" s="12">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B52" s="13">
         <v>50000</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B53" s="13">
         <v>5000</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B54" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B55" s="11">
         <v>0.1</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B58" s="12">
         <v>48</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B59" s="19">
         <v>2026</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B60" s="18">
         <v>6</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -3800,7 +3800,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3843,12 +3843,12 @@
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3866,23 +3866,23 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
       <c r="AC2" s="29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AD2" s="30" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
@@ -3890,131 +3890,131 @@
       <c r="AH2" s="6"/>
       <c r="AI2" s="6"/>
       <c r="AJ2" s="31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AK2" s="29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL2" s="6"/>
       <c r="AM2" s="6"/>
     </row>
     <row r="3" spans="1:39" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="G3" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="H3" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="I3" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="J3" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="K3" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="L3" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="M3" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="N3" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="O3" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="P3" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="Q3" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="R3" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="S3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="T3" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="U3" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="V3" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="W3" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="X3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="Y3" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="Z3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="AA3" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="AB3" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="Z3" s="22" t="s">
+      <c r="AC3" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AA3" s="22" t="s">
+      <c r="AD3" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="AB3" s="22" t="s">
+      <c r="AE3" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="AC3" s="20" t="s">
+      <c r="AF3" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="AD3" s="23" t="s">
+      <c r="AG3" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="AE3" s="23" t="s">
+      <c r="AH3" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="AF3" s="23" t="s">
+      <c r="AI3" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="AG3" s="23" t="s">
+      <c r="AJ3" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AH3" s="23" t="s">
+      <c r="AK3" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="AI3" s="23" t="s">
+      <c r="AL3" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="AJ3" s="24" t="s">
+      <c r="AM3" s="20" t="s">
         <v>107</v>
-      </c>
-      <c r="AK3" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="AM3" s="20" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C4" s="33">
         <f>IF($A4&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D4" s="14">
         <f>IF($A4&lt;VARIABLES!$B$21,0,IF($A4=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4039,11 +4039,11 @@
       </c>
       <c r="F4" s="14">
         <f>IF($A4&lt;VARIABLES!$B$21,0,(IF($A4=VARIABLES!$B$21,0,G3)+D4)*C4*VARIABLES!$B$25)</f>
-        <v>520.83333333333337</v>
+        <v>364.58333333333331</v>
       </c>
       <c r="G4" s="14">
         <f>IF($A4&lt;VARIABLES!$B$21,0,(IF($A4=VARIABLES!$B$21,0,G3)+D4)*(1+C4)-F4)</f>
-        <v>520312.50000000006</v>
+        <v>514218.74999999994</v>
       </c>
       <c r="H4" s="14">
         <f>IF($A4&lt;VARIABLES!$B$28,0,IF($A4=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4123,15 +4123,15 @@
       </c>
       <c r="AA4" s="14">
         <f t="shared" ref="AA4:AA51" si="2">F4+J4+N4+R4+W4</f>
-        <v>520.83333333333337</v>
+        <v>364.58333333333331</v>
       </c>
       <c r="AB4" s="35">
         <f t="shared" ref="AB4:AB51" si="3">Z4+AA4</f>
-        <v>4270.833333333333</v>
+        <v>4114.583333333333</v>
       </c>
       <c r="AC4" s="36">
         <f t="shared" ref="AC4:AC51" si="4">G4+K4+O4+S4+X4</f>
-        <v>520312.50000000006</v>
+        <v>514218.74999999994</v>
       </c>
       <c r="AD4" s="14">
         <f>IF($A4=1,VARIABLES!$B$12,0)</f>
@@ -4159,19 +4159,19 @@
       </c>
       <c r="AJ4" s="38">
         <f>IF($A4&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK4" s="39">
         <f t="shared" ref="AK4:AK51" si="6">AB4-AI4-AJ4</f>
-        <v>-97312.5</v>
+        <v>-78315.416666666672</v>
       </c>
       <c r="AL4" s="39">
         <f>AK4</f>
-        <v>-97312.5</v>
+        <v>-78315.416666666672</v>
       </c>
       <c r="AM4" s="40">
         <f>AJ4</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C5" s="42">
         <f>IF($A5&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$21,0,IF($A5=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4196,11 +4196,11 @@
       </c>
       <c r="F5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$21,0,(IF($A5=VARIABLES!$B$21,0,G4)+D5)*C5*VARIABLES!$B$25)</f>
-        <v>750.32552083333337</v>
+        <v>520.78450520833337</v>
       </c>
       <c r="G5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$21,0,(IF($A5=VARIABLES!$B$21,0,G4)+D5)*(1+C5)-F5)</f>
-        <v>749575.1953125</v>
+        <v>734529.34570312488</v>
       </c>
       <c r="H5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$28,0,IF($A5=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4212,11 +4212,11 @@
       </c>
       <c r="J5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$28,0,(IF($A5=VARIABLES!$B$28,0,K4)+H5)*C5*VARIABLES!$B$32)</f>
-        <v>166.66666666666666</v>
+        <v>116.66666666666666</v>
       </c>
       <c r="K5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$28,0,(IF($A5=VARIABLES!$B$28,0,K4)+H5)*(1+C5)-J5)</f>
-        <v>41500.000000000007</v>
+        <v>41050</v>
       </c>
       <c r="L5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$35,0,IF($A5=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4228,11 +4228,11 @@
       </c>
       <c r="N5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$35,0,(IF($A5=VARIABLES!$B$35,0,O4)+L5)*C5*VARIABLES!$B$39)</f>
-        <v>20833.333333333332</v>
+        <v>14583.333333333332</v>
       </c>
       <c r="O5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$35,0,(IF($A5=VARIABLES!$B$35,0,O4)+L5)*(1+C5)-N5)</f>
-        <v>5187500.0000000009</v>
+        <v>5131250</v>
       </c>
       <c r="P5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$42,0,IF($A5=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4244,11 +4244,11 @@
       </c>
       <c r="R5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$42,0,(IF($A5=VARIABLES!$B$42,0,S4)+P5)*C5*VARIABLES!$B$46)</f>
-        <v>20.833333333333332</v>
+        <v>14.583333333333332</v>
       </c>
       <c r="S5" s="43">
         <f>IF($A5&lt;VARIABLES!$B$42,0,(IF($A5=VARIABLES!$B$42,0,S4)+P5)*(1+C5)-R5)</f>
-        <v>20812.500000000004</v>
+        <v>20568.75</v>
       </c>
       <c r="T5" s="44">
         <f>IF($A5&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A5-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
@@ -4280,15 +4280,15 @@
       </c>
       <c r="AA5" s="43">
         <f t="shared" si="2"/>
-        <v>21771.158854166664</v>
+        <v>15235.367838541666</v>
       </c>
       <c r="AB5" s="35">
         <f t="shared" si="3"/>
-        <v>61221.158854166664</v>
+        <v>54685.367838541664</v>
       </c>
       <c r="AC5" s="36">
         <f t="shared" si="4"/>
-        <v>5999387.6953125009</v>
+        <v>5927398.095703125</v>
       </c>
       <c r="AD5" s="43">
         <f>IF($A5=1,VARIABLES!$B$12,0)</f>
@@ -4316,19 +4316,19 @@
       </c>
       <c r="AJ5" s="38">
         <f>IF($A5&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK5" s="45">
         <f t="shared" si="6"/>
-        <v>9637.8255208333321</v>
+        <v>22255.367838541664</v>
       </c>
       <c r="AL5" s="45">
-        <f t="shared" ref="AL5:AL51" si="7">AL4+AK5</f>
-        <v>-87674.674479166672</v>
+        <f t="shared" ref="AL5:AL39" si="7">IF(AJ5&gt;0,AL4+AK5,AL4)</f>
+        <v>-56060.048828125007</v>
       </c>
       <c r="AM5" s="40">
-        <f t="shared" ref="AM5:AM51" si="8">AM4+AJ5</f>
-        <v>53166.666666666664</v>
+        <f t="shared" ref="AM5:AM51" si="8">IF(AJ5&gt;0,AM4+AJ5,AM4+AK5)</f>
+        <v>14860</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C6" s="33">
         <f>IF($A6&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$21,0,IF($A6=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4353,11 +4353,11 @@
       </c>
       <c r="F6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$21,0,(IF($A6=VARIABLES!$B$21,0,G5)+D6)*C6*VARIABLES!$B$25)</f>
-        <v>989.14082845052076</v>
+        <v>681.42764790852857</v>
       </c>
       <c r="G6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$21,0,(IF($A6=VARIABLES!$B$21,0,G5)+D6)*(1+C6)-F6)</f>
-        <v>988151.68762207031</v>
+        <v>961105.02397155738</v>
       </c>
       <c r="H6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$28,0,IF($A6=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4369,11 +4369,11 @@
       </c>
       <c r="J6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$28,0,(IF($A6=VARIABLES!$B$28,0,K5)+H6)*C6*VARIABLES!$B$32)</f>
-        <v>339.58333333333331</v>
+        <v>236.39583333333331</v>
       </c>
       <c r="K6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$28,0,(IF($A6=VARIABLES!$B$28,0,K5)+H6)*(1+C6)-J6)</f>
-        <v>84556.250000000015</v>
+        <v>83177.5625</v>
       </c>
       <c r="L6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$35,0,IF($A6=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4385,11 +4385,11 @@
       </c>
       <c r="N6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$35,0,(IF($A6=VARIABLES!$B$35,0,O5)+L6)*C6*VARIABLES!$B$39)</f>
-        <v>21614.583333333339</v>
+        <v>14966.145833333332</v>
       </c>
       <c r="O6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$35,0,(IF($A6=VARIABLES!$B$35,0,O5)+L6)*(1+C6)-N6)</f>
-        <v>5382031.2500000019</v>
+        <v>5265945.3125</v>
       </c>
       <c r="P6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$42,0,IF($A6=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4401,51 +4401,51 @@
       </c>
       <c r="R6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$42,0,(IF($A6=VARIABLES!$B$42,0,S5)+P6)*C6*VARIABLES!$B$46)</f>
-        <v>42.513020833333336</v>
+        <v>29.581380208333332</v>
       </c>
       <c r="S6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$42,0,(IF($A6=VARIABLES!$B$42,0,S5)+P6)*(1+C6)-R6)</f>
-        <v>42470.5078125</v>
+        <v>41722.423828124993</v>
       </c>
       <c r="T6" s="34">
         <f>IF($A6&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A6-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="14">
         <f>T6*VARIABLES!$B$53+IF(AND($A6&gt;=VARIABLES!$B$50,MOD($A6-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A6-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="V6" s="14">
         <f>U6*VARIABLES!$B$54</f>
-        <v>0</v>
+        <v>412.5</v>
       </c>
       <c r="W6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$50,0,(IF($A6&lt;VARIABLES!$B$50+1,0,X5)+U6)*C6*VARIABLES!$B$55)</f>
-        <v>0</v>
+        <v>160.41666666666666</v>
       </c>
       <c r="X6" s="14">
         <f>IF($A6&lt;VARIABLES!$B$50,0,(IF($A6&lt;VARIABLES!$B$50+1,0,X5)+U6)*(1+C6)-W6)</f>
-        <v>0</v>
+        <v>56443.75</v>
       </c>
       <c r="Y6" s="14">
         <f t="shared" si="0"/>
-        <v>260000</v>
+        <v>315000</v>
       </c>
       <c r="Z6" s="14">
         <f t="shared" si="1"/>
-        <v>1950</v>
+        <v>2362.5</v>
       </c>
       <c r="AA6" s="14">
         <f t="shared" si="2"/>
-        <v>22985.820515950527</v>
+        <v>16073.967361450193</v>
       </c>
       <c r="AB6" s="35">
         <f t="shared" si="3"/>
-        <v>24935.820515950527</v>
+        <v>18436.467361450195</v>
       </c>
       <c r="AC6" s="36">
         <f t="shared" si="4"/>
-        <v>6497209.6954345722</v>
+        <v>6408394.0727996826</v>
       </c>
       <c r="AD6" s="14">
         <f>IF($A6=1,VARIABLES!$B$12,0)</f>
@@ -4473,19 +4473,19 @@
       </c>
       <c r="AJ6" s="38">
         <f>IF($A6&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK6" s="39">
         <f t="shared" si="6"/>
-        <v>-26647.512817382805</v>
+        <v>-13993.532638549805</v>
       </c>
       <c r="AL6" s="39">
         <f t="shared" si="7"/>
-        <v>-114322.18729654947</v>
+        <v>-70053.581466674805</v>
       </c>
       <c r="AM6" s="40">
         <f t="shared" si="8"/>
-        <v>79750</v>
+        <v>22290</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C7" s="42">
         <f>IF($A7&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$21,0,IF($A7=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4510,11 +4510,11 @@
       </c>
       <c r="F7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$21,0,(IF($A7=VARIABLES!$B$21,0,G6)+D7)*C7*VARIABLES!$B$25)</f>
-        <v>1237.6580079396565</v>
+        <v>846.6390799792606</v>
       </c>
       <c r="G7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$21,0,(IF($A7=VARIABLES!$B$21,0,G6)+D7)*(1+C7)-F7)</f>
-        <v>1236420.3499317172</v>
+        <v>1194123.9480907486</v>
       </c>
       <c r="H7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$28,0,IF($A7=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4526,11 +4526,11 @@
       </c>
       <c r="J7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$28,0,(IF($A7=VARIABLES!$B$28,0,K6)+H7)*C7*VARIABLES!$B$32)</f>
-        <v>518.984375</v>
+        <v>359.26789062500001</v>
       </c>
       <c r="K7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$28,0,(IF($A7=VARIABLES!$B$28,0,K6)+H7)*(1+C7)-J7)</f>
-        <v>129227.10937500003</v>
+        <v>126410.973515625</v>
       </c>
       <c r="L7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$35,0,IF($A7=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="N7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$35,0,(IF($A7=VARIABLES!$B$35,0,O6)+L7)*C7*VARIABLES!$B$39)</f>
-        <v>22425.130208333343</v>
+        <v>15359.007161458332</v>
       </c>
       <c r="O7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$35,0,(IF($A7=VARIABLES!$B$35,0,O6)+L7)*(1+C7)-N7)</f>
-        <v>5583857.4218750028</v>
+        <v>5404176.376953125</v>
       </c>
       <c r="P7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$42,0,IF($A7=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4558,51 +4558,51 @@
       </c>
       <c r="R7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$42,0,(IF($A7=VARIABLES!$B$42,0,S6)+P7)*C7*VARIABLES!$B$46)</f>
-        <v>65.073445638020829</v>
+        <v>45.005934041341135</v>
       </c>
       <c r="S7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$42,0,(IF($A7=VARIABLES!$B$42,0,S6)+P7)*(1+C7)-R7)</f>
-        <v>65008.372192382813</v>
+        <v>63477.655255737292</v>
       </c>
       <c r="T7" s="44">
         <f>IF($A7&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A7-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="43">
         <f>T7*VARIABLES!$B$53+IF(AND($A7&gt;=VARIABLES!$B$50,MOD($A7-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A7-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="V7" s="43">
         <f>U7*VARIABLES!$B$54</f>
-        <v>412.5</v>
+        <v>450</v>
       </c>
       <c r="W7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$50,0,(IF($A7&lt;VARIABLES!$B$50+1,0,X6)+U7)*C7*VARIABLES!$B$55)</f>
-        <v>229.16666666666666</v>
+        <v>339.62760416666669</v>
       </c>
       <c r="X7" s="43">
         <f>IF($A7&lt;VARIABLES!$B$50,0,(IF($A7&lt;VARIABLES!$B$50+1,0,X6)+U7)*(1+C7)-W7)</f>
-        <v>57062.500000000007</v>
+        <v>119500.39843749999</v>
       </c>
       <c r="Y7" s="43">
         <f t="shared" si="0"/>
-        <v>315000</v>
+        <v>320000</v>
       </c>
       <c r="Z7" s="43">
         <f t="shared" si="1"/>
-        <v>2362.5</v>
+        <v>2400</v>
       </c>
       <c r="AA7" s="43">
         <f t="shared" si="2"/>
-        <v>24476.012703577686</v>
+        <v>16949.547670270604</v>
       </c>
       <c r="AB7" s="35">
         <f t="shared" si="3"/>
-        <v>26838.512703577686</v>
+        <v>19349.547670270604</v>
       </c>
       <c r="AC7" s="36">
         <f t="shared" si="4"/>
-        <v>7071575.7533741025</v>
+        <v>6907689.3522527358</v>
       </c>
       <c r="AD7" s="43">
         <f>IF($A7=1,VARIABLES!$B$12,0)</f>
@@ -4630,19 +4630,19 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF($A7&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK7" s="45">
         <f t="shared" si="6"/>
-        <v>-34744.820629755646</v>
+        <v>-23080.452329729396</v>
       </c>
       <c r="AL7" s="45">
         <f t="shared" si="7"/>
-        <v>-149067.00792630512</v>
+        <v>-93134.033796404197</v>
       </c>
       <c r="AM7" s="40">
         <f t="shared" si="8"/>
-        <v>106333.33333333333</v>
+        <v>29720</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C8" s="33">
         <f>IF($A8&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$21,0,IF($A8=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4667,11 +4667,11 @@
       </c>
       <c r="F8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$21,0,(IF($A8=VARIABLES!$B$21,0,G7)+D8)*C8*VARIABLES!$B$25)</f>
-        <v>1496.2711978455388</v>
+        <v>1016.5487121495042</v>
       </c>
       <c r="G8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$21,0,(IF($A8=VARIABLES!$B$21,0,G7)+D8)*(1+C8)-F8)</f>
-        <v>1494774.9266476934</v>
+        <v>1433769.3478645792</v>
       </c>
       <c r="H8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$28,0,IF($A8=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4683,11 +4683,11 @@
       </c>
       <c r="J8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$28,0,(IF($A8=VARIABLES!$B$28,0,K7)+H8)*C8*VARIABLES!$B$32)</f>
-        <v>705.11295572916686</v>
+        <v>485.36533942057287</v>
       </c>
       <c r="K8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$28,0,(IF($A8=VARIABLES!$B$28,0,K7)+H8)*(1+C8)-J8)</f>
-        <v>175573.12597656256</v>
+        <v>170779.26157041013</v>
       </c>
       <c r="L8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$35,0,IF($A8=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4699,11 +4699,11 @@
       </c>
       <c r="N8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$35,0,(IF($A8=VARIABLES!$B$35,0,O7)+L8)*C8*VARIABLES!$B$39)</f>
-        <v>23266.072591145843</v>
+        <v>15762.181099446614</v>
       </c>
       <c r="O8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$35,0,(IF($A8=VARIABLES!$B$35,0,O7)+L8)*(1+C8)-N8)</f>
-        <v>5793252.0751953162</v>
+        <v>5546036.0068481443</v>
       </c>
       <c r="P8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$42,0,IF($A8=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4715,51 +4715,51 @@
       </c>
       <c r="R8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$42,0,(IF($A8=VARIABLES!$B$42,0,S7)+P8)*C8*VARIABLES!$B$46)</f>
-        <v>88.550387700398758</v>
+        <v>60.869123623975099</v>
       </c>
       <c r="S8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$42,0,(IF($A8=VARIABLES!$B$42,0,S7)+P8)*(1+C8)-R8)</f>
-        <v>88461.837312698379</v>
+        <v>85851.551077072319</v>
       </c>
       <c r="T8" s="34">
         <f>IF($A8&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A8-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" s="14">
         <f>T8*VARIABLES!$B$53+IF(AND($A8&gt;=VARIABLES!$B$50,MOD($A8-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A8-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>65000</v>
       </c>
       <c r="V8" s="14">
         <f>U8*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>487.5</v>
       </c>
       <c r="W8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$50,0,(IF($A8&lt;VARIABLES!$B$50+1,0,X7)+U8)*C8*VARIABLES!$B$55)</f>
-        <v>487.76041666666663</v>
+        <v>538.12616210937495</v>
       </c>
       <c r="X8" s="14">
         <f>IF($A8&lt;VARIABLES!$B$50,0,(IF($A8&lt;VARIABLES!$B$50+1,0,X7)+U8)*(1+C8)-W8)</f>
-        <v>121452.34375</v>
+        <v>189343.53389648435</v>
       </c>
       <c r="Y8" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>325000</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2437.5</v>
       </c>
       <c r="AA8" s="14">
         <f t="shared" si="2"/>
-        <v>26043.767549087614</v>
+        <v>17863.090436750044</v>
       </c>
       <c r="AB8" s="35">
         <f t="shared" si="3"/>
-        <v>28443.767549087614</v>
+        <v>20300.590436750044</v>
       </c>
       <c r="AC8" s="36">
         <f t="shared" si="4"/>
-        <v>7673514.30888227</v>
+        <v>7425779.7012566905</v>
       </c>
       <c r="AD8" s="14">
         <f>IF($A8=1,VARIABLES!$B$12,0)</f>
@@ -4787,19 +4787,19 @@
       </c>
       <c r="AJ8" s="38">
         <f>IF($A8&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK8" s="39">
         <f t="shared" si="6"/>
-        <v>-33139.565784245715</v>
+        <v>-22129.409563249956</v>
       </c>
       <c r="AL8" s="39">
         <f t="shared" si="7"/>
-        <v>-182206.57371055085</v>
+        <v>-115263.44335965415</v>
       </c>
       <c r="AM8" s="40">
         <f t="shared" si="8"/>
-        <v>132916.66666666666</v>
+        <v>37150</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="C9" s="42">
         <f>IF($A9&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$21,0,IF($A9=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4824,11 +4824,11 @@
       </c>
       <c r="F9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$21,0,(IF($A9=VARIABLES!$B$21,0,G8)+D9)*C9*VARIABLES!$B$25)</f>
-        <v>1765.3905485913472</v>
+        <v>1191.2901494845889</v>
       </c>
       <c r="G9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$21,0,(IF($A9=VARIABLES!$B$21,0,G8)+D9)*(1+C9)-F9)</f>
-        <v>1763625.1580427561</v>
+        <v>1680229.6636944781</v>
       </c>
       <c r="H9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$28,0,IF($A9=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4840,11 +4840,11 @@
       </c>
       <c r="J9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$28,0,(IF($A9=VARIABLES!$B$28,0,K8)+H9)*C9*VARIABLES!$B$32)</f>
-        <v>898.22135823567737</v>
+        <v>614.77284624702952</v>
       </c>
       <c r="K9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$28,0,(IF($A9=VARIABLES!$B$28,0,K8)+H9)*(1+C9)-J9)</f>
-        <v>223657.11820068368</v>
+        <v>216312.21718663338</v>
       </c>
       <c r="L9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$35,0,IF($A9=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="N9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$35,0,(IF($A9=VARIABLES!$B$35,0,O8)+L9)*C9*VARIABLES!$B$39)</f>
-        <v>24138.550313313819</v>
+        <v>16175.938353307087</v>
       </c>
       <c r="O9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$35,0,(IF($A9=VARIABLES!$B$35,0,O8)+L9)*(1+C9)-N9)</f>
-        <v>6010499.0280151414</v>
+        <v>5691619.4520279067</v>
       </c>
       <c r="P9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$42,0,IF($A9=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4872,51 +4872,51 @@
       </c>
       <c r="R9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$42,0,(IF($A9=VARIABLES!$B$42,0,S8)+P9)*C9*VARIABLES!$B$46)</f>
-        <v>112.98108053406082</v>
+        <v>77.183422660365238</v>
       </c>
       <c r="S9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$42,0,(IF($A9=VARIABLES!$B$42,0,S8)+P9)*(1+C9)-R9)</f>
-        <v>112868.09945352675</v>
+        <v>108861.70456082655</v>
       </c>
       <c r="T9" s="44">
         <f>IF($A9&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A9-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9" s="43">
         <f>T9*VARIABLES!$B$53+IF(AND($A9&gt;=VARIABLES!$B$50,MOD($A9-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A9-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>65000</v>
+        <v>70000</v>
       </c>
       <c r="V9" s="43">
         <f>U9*VARIABLES!$B$54</f>
-        <v>487.5</v>
+        <v>525</v>
       </c>
       <c r="W9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$50,0,(IF($A9&lt;VARIABLES!$B$50+1,0,X8)+U9)*C9*VARIABLES!$B$55)</f>
-        <v>776.884765625</v>
+        <v>756.41864053141262</v>
       </c>
       <c r="X9" s="43">
         <f>IF($A9&lt;VARIABLES!$B$50,0,(IF($A9&lt;VARIABLES!$B$50+1,0,X8)+U9)*(1+C9)-W9)</f>
-        <v>193444.306640625</v>
+        <v>266151.301661267</v>
       </c>
       <c r="Y9" s="43">
         <f t="shared" si="0"/>
-        <v>325000</v>
+        <v>330000</v>
       </c>
       <c r="Z9" s="43">
         <f t="shared" si="1"/>
-        <v>2437.5</v>
+        <v>2475</v>
       </c>
       <c r="AA9" s="43">
         <f t="shared" si="2"/>
-        <v>27692.028066299903</v>
+        <v>18815.603412230485</v>
       </c>
       <c r="AB9" s="35">
         <f t="shared" si="3"/>
-        <v>30129.528066299903</v>
+        <v>21290.603412230485</v>
       </c>
       <c r="AC9" s="36">
         <f t="shared" si="4"/>
-        <v>8304093.7103527328</v>
+        <v>7963174.3391311113</v>
       </c>
       <c r="AD9" s="43">
         <f>IF($A9=1,VARIABLES!$B$12,0)</f>
@@ -4944,19 +4944,19 @@
       </c>
       <c r="AJ9" s="38">
         <f>IF($A9&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK9" s="45">
         <f t="shared" si="6"/>
-        <v>-31453.805267033429</v>
+        <v>-21139.396587769515</v>
       </c>
       <c r="AL9" s="45">
         <f t="shared" si="7"/>
-        <v>-213660.37897758427</v>
+        <v>-136402.83994742366</v>
       </c>
       <c r="AM9" s="40">
         <f t="shared" si="8"/>
-        <v>159500</v>
+        <v>44580</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C10" s="33">
         <f>IF($A10&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$21,0,IF($A10=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4981,11 +4981,11 @@
       </c>
       <c r="F10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$21,0,(IF($A10=VARIABLES!$B$21,0,G9)+D10)*C10*VARIABLES!$B$25)</f>
-        <v>2045.4428729612043</v>
+        <v>1371.0007964438901</v>
       </c>
       <c r="G10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$21,0,(IF($A10=VARIABLES!$B$21,0,G9)+D10)*(1+C10)-F10)</f>
-        <v>2043397.4300882432</v>
+        <v>1933698.6947557898</v>
       </c>
       <c r="H10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$28,0,IF($A10=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="J10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$28,0,(IF($A10=VARIABLES!$B$28,0,K9)+H10)*C10*VARIABLES!$B$32)</f>
-        <v>1098.5713258361818</v>
+        <v>747.5773001276807</v>
       </c>
       <c r="K10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$28,0,(IF($A10=VARIABLES!$B$28,0,K9)+H10)*(1+C10)-J10)</f>
-        <v>273544.26013320935</v>
+        <v>263040.4128877825</v>
       </c>
       <c r="L10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$35,0,IF($A10=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5013,11 +5013,11 @@
       </c>
       <c r="N10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$35,0,(IF($A10=VARIABLES!$B$35,0,O9)+L10)*C10*VARIABLES!$B$39)</f>
-        <v>25043.74595006309</v>
+        <v>16600.556735081391</v>
       </c>
       <c r="O10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$35,0,(IF($A10=VARIABLES!$B$35,0,O9)+L10)*(1+C10)-N10)</f>
-        <v>6235892.7415657099</v>
+        <v>5841024.4626436383</v>
       </c>
       <c r="P10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$42,0,IF($A10=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5029,51 +5029,51 @@
       </c>
       <c r="R10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$42,0,(IF($A10=VARIABLES!$B$42,0,S9)+P10)*C10*VARIABLES!$B$46)</f>
-        <v>138.40427026409037</v>
+        <v>93.961659575602681</v>
       </c>
       <c r="S10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$42,0,(IF($A10=VARIABLES!$B$42,0,S9)+P10)*(1+C10)-R10)</f>
-        <v>138265.8659938263</v>
+        <v>132526.20928427504</v>
       </c>
       <c r="T10" s="34">
         <f>IF($A10&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A10-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U10" s="14">
         <f>T10*VARIABLES!$B$53+IF(AND($A10&gt;=VARIABLES!$B$50,MOD($A10-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A10-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>70000</v>
+        <v>75000</v>
       </c>
       <c r="V10" s="14">
         <f>U10*VARIABLES!$B$54</f>
-        <v>525</v>
+        <v>562.5</v>
       </c>
       <c r="W10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$50,0,(IF($A10&lt;VARIABLES!$B$50+1,0,X9)+U10)*C10*VARIABLES!$B$55)</f>
-        <v>1097.6846110026042</v>
+        <v>995.02462984536203</v>
       </c>
       <c r="X10" s="14">
         <f>IF($A10&lt;VARIABLES!$B$50,0,(IF($A10&lt;VARIABLES!$B$50+1,0,X9)+U10)*(1+C10)-W10)</f>
-        <v>273323.46813964844</v>
+        <v>350106.52332987526</v>
       </c>
       <c r="Y10" s="14">
         <f t="shared" si="0"/>
-        <v>330000</v>
+        <v>335000</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="1"/>
-        <v>2475</v>
+        <v>2512.5</v>
       </c>
       <c r="AA10" s="14">
         <f t="shared" si="2"/>
-        <v>29423.849030127174</v>
+        <v>19808.121121073924</v>
       </c>
       <c r="AB10" s="35">
         <f t="shared" si="3"/>
-        <v>31898.849030127174</v>
+        <v>22320.621121073924</v>
       </c>
       <c r="AC10" s="36">
         <f t="shared" si="4"/>
-        <v>8964423.7659206372</v>
+        <v>8520396.3029013611</v>
       </c>
       <c r="AD10" s="14">
         <f>IF($A10=1,VARIABLES!$B$12,0)</f>
@@ -5101,19 +5101,19 @@
       </c>
       <c r="AJ10" s="38">
         <f>IF($A10&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK10" s="39">
         <f t="shared" si="6"/>
-        <v>-39684.484303206162</v>
+        <v>-30109.378878926076</v>
       </c>
       <c r="AL10" s="39">
         <f t="shared" si="7"/>
-        <v>-253344.86328079045</v>
+        <v>-166512.21882634974</v>
       </c>
       <c r="AM10" s="40">
         <f t="shared" si="8"/>
-        <v>186083.33333333334</v>
+        <v>52010</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C11" s="42">
         <f>IF($A11&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$21,0,IF($A11=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5138,11 +5138,11 @@
       </c>
       <c r="F11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$21,0,(IF($A11=VARIABLES!$B$21,0,G10)+D11)*C11*VARIABLES!$B$25)</f>
-        <v>2336.8723230085866</v>
+        <v>1555.8219649260966</v>
       </c>
       <c r="G11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$21,0,(IF($A11=VARIABLES!$B$21,0,G10)+D11)*(1+C11)-F11)</f>
-        <v>2334535.4506855784</v>
+        <v>2194375.7513879072</v>
       </c>
       <c r="H11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$28,0,IF($A11=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5154,11 +5154,11 @@
       </c>
       <c r="J11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$28,0,(IF($A11=VARIABLES!$B$28,0,K10)+H11)*C11*VARIABLES!$B$32)</f>
-        <v>1306.4344172217056</v>
+        <v>883.86787092269878</v>
       </c>
       <c r="K11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$28,0,(IF($A11=VARIABLES!$B$28,0,K10)+H11)*(1+C11)-J11)</f>
-        <v>325302.16988820472</v>
+        <v>310995.22372608673</v>
       </c>
       <c r="L11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$35,0,IF($A11=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5170,11 +5170,11 @@
       </c>
       <c r="N11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$35,0,(IF($A11=VARIABLES!$B$35,0,O10)+L11)*C11*VARIABLES!$B$39)</f>
-        <v>25982.886423190459</v>
+        <v>17036.321349377275</v>
       </c>
       <c r="O11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$35,0,(IF($A11=VARIABLES!$B$35,0,O10)+L11)*(1+C11)-N11)</f>
-        <v>6469738.7193744248</v>
+        <v>5994351.3547880333</v>
       </c>
       <c r="P11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$42,0,IF($A11=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5186,51 +5186,51 @@
       </c>
       <c r="R11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$42,0,(IF($A11=VARIABLES!$B$42,0,S10)+P11)*C11*VARIABLES!$B$46)</f>
-        <v>164.86027707690241</v>
+        <v>111.21702760311722</v>
       </c>
       <c r="S11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$42,0,(IF($A11=VARIABLES!$B$42,0,S10)+P11)*(1+C11)-R11)</f>
-        <v>164695.41679982553</v>
+        <v>156863.67336079659</v>
       </c>
       <c r="T11" s="44">
         <f>IF($A11&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A11-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11" s="43">
         <f>T11*VARIABLES!$B$53+IF(AND($A11&gt;=VARIABLES!$B$50,MOD($A11-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A11-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>75000</v>
+        <v>80000</v>
       </c>
       <c r="V11" s="43">
         <f>U11*VARIABLES!$B$54</f>
-        <v>562.5</v>
+        <v>600</v>
       </c>
       <c r="W11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$50,0,(IF($A11&lt;VARIABLES!$B$50+1,0,X10)+U11)*C11*VARIABLES!$B$55)</f>
-        <v>1451.3477839152019</v>
+        <v>1254.4773597121361</v>
       </c>
       <c r="X11" s="43">
         <f>IF($A11&lt;VARIABLES!$B$50,0,(IF($A11&lt;VARIABLES!$B$50+1,0,X10)+U11)*(1+C11)-W11)</f>
-        <v>361385.5981948853</v>
+        <v>441396.81956728443</v>
       </c>
       <c r="Y11" s="43">
         <f t="shared" si="0"/>
-        <v>335000</v>
+        <v>340000</v>
       </c>
       <c r="Z11" s="43">
         <f t="shared" si="1"/>
-        <v>2512.5</v>
+        <v>2550</v>
       </c>
       <c r="AA11" s="43">
         <f t="shared" si="2"/>
-        <v>31242.401224412853</v>
+        <v>20841.705572541323</v>
       </c>
       <c r="AB11" s="35">
         <f t="shared" si="3"/>
-        <v>33754.901224412853</v>
+        <v>23391.705572541323</v>
       </c>
       <c r="AC11" s="36">
         <f t="shared" si="4"/>
-        <v>9655657.3549429178</v>
+        <v>9097982.8228301071</v>
       </c>
       <c r="AD11" s="43">
         <f>IF($A11=1,VARIABLES!$B$12,0)</f>
@@ -5258,19 +5258,19 @@
       </c>
       <c r="AJ11" s="38">
         <f>IF($A11&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK11" s="45">
         <f t="shared" si="6"/>
-        <v>-37828.432108920475</v>
+        <v>-29038.294427458677</v>
       </c>
       <c r="AL11" s="45">
         <f t="shared" si="7"/>
-        <v>-291173.29538971093</v>
+        <v>-195550.51325380843</v>
       </c>
       <c r="AM11" s="40">
         <f t="shared" si="8"/>
-        <v>212666.66666666669</v>
+        <v>59440</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="C12" s="33">
         <f>IF($A12&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$21,0,IF($A12=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5295,11 +5295,11 @@
       </c>
       <c r="F12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$21,0,(IF($A12=VARIABLES!$B$21,0,G11)+D12)*C12*VARIABLES!$B$25)</f>
-        <v>2640.1410944641443</v>
+        <v>1745.8989853870157</v>
       </c>
       <c r="G12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$21,0,(IF($A12=VARIABLES!$B$21,0,G11)+D12)*(1+C12)-F12)</f>
-        <v>2637500.9533696799</v>
+        <v>2462465.8118180009</v>
       </c>
       <c r="H12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$28,0,IF($A12=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5311,11 +5311,11 @@
       </c>
       <c r="J12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$28,0,(IF($A12=VARIABLES!$B$28,0,K11)+H12)*C12*VARIABLES!$B$32)</f>
-        <v>1522.0923745341863</v>
+        <v>1023.7360692010861</v>
       </c>
       <c r="K12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$28,0,(IF($A12=VARIABLES!$B$28,0,K11)+H12)*(1+C12)-J12)</f>
-        <v>379001.00125901244</v>
+        <v>360208.84834889648</v>
       </c>
       <c r="L12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$35,0,IF($A12=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5327,11 +5327,11 @@
       </c>
       <c r="N12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$35,0,(IF($A12=VARIABLES!$B$35,0,O11)+L12)*C12*VARIABLES!$B$39)</f>
-        <v>26957.244664060105</v>
+        <v>17483.524784798428</v>
       </c>
       <c r="O12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$35,0,(IF($A12=VARIABLES!$B$35,0,O11)+L12)*(1+C12)-N12)</f>
-        <v>6712353.9213509662</v>
+        <v>6151703.0778512182</v>
       </c>
       <c r="P12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$42,0,IF($A12=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5343,51 +5343,51 @@
       </c>
       <c r="R12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$42,0,(IF($A12=VARIABLES!$B$42,0,S11)+P12)*C12*VARIABLES!$B$46)</f>
-        <v>192.39105916648492</v>
+        <v>128.96309515891417</v>
       </c>
       <c r="S12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$42,0,(IF($A12=VARIABLES!$B$42,0,S11)+P12)*(1+C12)-R12)</f>
-        <v>192198.66810731846</v>
+        <v>181893.23407199423</v>
       </c>
       <c r="T12" s="34">
         <f>IF($A12&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A12-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12" s="14">
         <f>T12*VARIABLES!$B$53+IF(AND($A12&gt;=VARIABLES!$B$50,MOD($A12-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A12-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>80000</v>
+        <v>85000</v>
       </c>
       <c r="V12" s="14">
         <f>U12*VARIABLES!$B$54</f>
-        <v>600</v>
+        <v>637.5</v>
       </c>
       <c r="W12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$50,0,(IF($A12&lt;VARIABLES!$B$50+1,0,X11)+U12)*C12*VARIABLES!$B$55)</f>
-        <v>1839.1066591453555</v>
+        <v>1535.3240570712462</v>
       </c>
       <c r="X12" s="14">
         <f>IF($A12&lt;VARIABLES!$B$50,0,(IF($A12&lt;VARIABLES!$B$50+1,0,X11)+U12)*(1+C12)-W12)</f>
-        <v>457937.55812719354</v>
+        <v>540214.73608092556</v>
       </c>
       <c r="Y12" s="14">
         <f t="shared" si="0"/>
-        <v>340000</v>
+        <v>345000</v>
       </c>
       <c r="Z12" s="14">
         <f t="shared" si="1"/>
-        <v>2550</v>
+        <v>2587.5</v>
       </c>
       <c r="AA12" s="14">
         <f t="shared" si="2"/>
-        <v>33150.975851370276</v>
+        <v>21917.446991616693</v>
       </c>
       <c r="AB12" s="35">
         <f t="shared" si="3"/>
-        <v>35700.975851370276</v>
+        <v>24504.946991616693</v>
       </c>
       <c r="AC12" s="36">
         <f t="shared" si="4"/>
-        <v>10378992.102214169</v>
+        <v>9696485.7081710361</v>
       </c>
       <c r="AD12" s="14">
         <f>IF($A12=1,VARIABLES!$B$12,0)</f>
@@ -5415,19 +5415,19 @@
       </c>
       <c r="AJ12" s="38">
         <f>IF($A12&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK12" s="39">
         <f t="shared" si="6"/>
-        <v>-35882.357481963059</v>
+        <v>-27925.053008383307</v>
       </c>
       <c r="AL12" s="39">
         <f t="shared" si="7"/>
-        <v>-327055.65287167398</v>
+        <v>-223475.56626219174</v>
       </c>
       <c r="AM12" s="40">
         <f t="shared" si="8"/>
-        <v>239250.00000000003</v>
+        <v>66870</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.2">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C13" s="42">
         <f>IF($A13&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$21,0,IF($A13=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="F13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$21,0,(IF($A13=VARIABLES!$B$21,0,G12)+D13)*C13*VARIABLES!$B$25)</f>
-        <v>2955.7301597600836</v>
+        <v>1941.3813211172921</v>
       </c>
       <c r="G13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$21,0,(IF($A13=VARIABLES!$B$21,0,G12)+D13)*(1+C13)-F13)</f>
-        <v>2952774.4296003236</v>
+        <v>2738179.6833415749</v>
       </c>
       <c r="H13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$28,0,IF($A13=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5468,11 +5468,11 @@
       </c>
       <c r="J13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$28,0,(IF($A13=VARIABLES!$B$28,0,K12)+H13)*C13*VARIABLES!$B$32)</f>
-        <v>1745.837505245885</v>
+        <v>1167.2758076842813</v>
       </c>
       <c r="K13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$28,0,(IF($A13=VARIABLES!$B$28,0,K12)+H13)*(1+C13)-J13)</f>
-        <v>434713.53880622546</v>
+        <v>410714.33061805496</v>
       </c>
       <c r="L13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$35,0,IF($A13=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5484,11 +5484,11 @@
       </c>
       <c r="N13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$35,0,(IF($A13=VARIABLES!$B$35,0,O12)+L13)*C13*VARIABLES!$B$39)</f>
-        <v>27968.141338962359</v>
+        <v>17942.467310399385</v>
       </c>
       <c r="O13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$35,0,(IF($A13=VARIABLES!$B$35,0,O12)+L13)*(1+C13)-N13)</f>
-        <v>6964067.1934016282</v>
+        <v>6313185.2836448113</v>
       </c>
       <c r="P13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$42,0,IF($A13=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5500,51 +5500,51 @@
       </c>
       <c r="R13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$42,0,(IF($A13=VARIABLES!$B$42,0,S12)+P13)*C13*VARIABLES!$B$46)</f>
-        <v>221.04027927845675</v>
+        <v>147.2138165108291</v>
       </c>
       <c r="S13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$42,0,(IF($A13=VARIABLES!$B$42,0,S12)+P13)*(1+C13)-R13)</f>
-        <v>220819.23899917831</v>
+        <v>207634.57291591653</v>
       </c>
       <c r="T13" s="44">
         <f>IF($A13&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A13-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13" s="43">
         <f>T13*VARIABLES!$B$53+IF(AND($A13&gt;=VARIABLES!$B$50,MOD($A13-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A13-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>85000</v>
+        <v>90000</v>
       </c>
       <c r="V13" s="43">
         <f>U13*VARIABLES!$B$54</f>
-        <v>637.5</v>
+        <v>675</v>
       </c>
       <c r="W13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$50,0,(IF($A13&lt;VARIABLES!$B$50+1,0,X12)+U13)*C13*VARIABLES!$B$55)</f>
-        <v>2262.2398255299727</v>
+        <v>1838.1263135693662</v>
       </c>
       <c r="X13" s="43">
         <f>IF($A13&lt;VARIABLES!$B$50,0,(IF($A13&lt;VARIABLES!$B$50+1,0,X12)+U13)*(1+C13)-W13)</f>
-        <v>563297.71655696328</v>
+        <v>646757.87290304981</v>
       </c>
       <c r="Y13" s="43">
         <f t="shared" si="0"/>
-        <v>345000</v>
+        <v>350000</v>
       </c>
       <c r="Z13" s="43">
         <f t="shared" si="1"/>
-        <v>2587.5</v>
+        <v>2625</v>
       </c>
       <c r="AA13" s="43">
         <f t="shared" si="2"/>
-        <v>35152.989108776754</v>
+        <v>23036.464569281154</v>
       </c>
       <c r="AB13" s="35">
         <f t="shared" si="3"/>
-        <v>37740.489108776754</v>
+        <v>25661.464569281154</v>
       </c>
       <c r="AC13" s="36">
         <f t="shared" si="4"/>
-        <v>11135672.117364319</v>
+        <v>10316471.743423408</v>
       </c>
       <c r="AD13" s="43">
         <f>IF($A13=1,VARIABLES!$B$12,0)</f>
@@ -5572,19 +5572,19 @@
       </c>
       <c r="AJ13" s="38">
         <f>IF($A13&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK13" s="45">
         <f t="shared" si="6"/>
-        <v>-33842.844224556582</v>
+        <v>-26768.535430718846</v>
       </c>
       <c r="AL13" s="45">
         <f t="shared" si="7"/>
-        <v>-360898.49709623057</v>
+        <v>-250244.1016929106</v>
       </c>
       <c r="AM13" s="40">
         <f t="shared" si="8"/>
-        <v>265833.33333333337</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.2">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C14" s="33">
         <f>IF($A14&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$21,0,IF($A14=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5609,11 +5609,11 @@
       </c>
       <c r="F14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$21,0,(IF($A14=VARIABLES!$B$21,0,G13)+D14)*C14*VARIABLES!$B$25)</f>
-        <v>3284.1400308336702</v>
+        <v>2142.4226857698982</v>
       </c>
       <c r="G14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$21,0,(IF($A14=VARIABLES!$B$21,0,G13)+D14)*(1+C14)-F14)</f>
-        <v>3280855.8908028365</v>
+        <v>3021734.1680866005</v>
       </c>
       <c r="H14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$28,0,IF($A14=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="J14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$28,0,(IF($A14=VARIABLES!$B$28,0,K13)+H14)*C14*VARIABLES!$B$32)</f>
-        <v>1977.9730783592729</v>
+        <v>1314.5834643026601</v>
       </c>
       <c r="K14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$28,0,(IF($A14=VARIABLES!$B$28,0,K13)+H14)*(1+C14)-J14)</f>
-        <v>492515.29651145893</v>
+        <v>462545.58179677889</v>
       </c>
       <c r="L14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$35,0,IF($A14=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5641,11 +5641,11 @@
       </c>
       <c r="N14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$35,0,(IF($A14=VARIABLES!$B$35,0,O13)+L14)*C14*VARIABLES!$B$39)</f>
-        <v>29016.94663917345</v>
+        <v>18413.457077297364</v>
       </c>
       <c r="O14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$35,0,(IF($A14=VARIABLES!$B$35,0,O13)+L14)*(1+C14)-N14)</f>
-        <v>7225219.7131541893</v>
+        <v>6478906.3973404868</v>
       </c>
       <c r="P14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$42,0,IF($A14=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5657,51 +5657,51 @@
       </c>
       <c r="R14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$42,0,(IF($A14=VARIABLES!$B$42,0,S13)+P14)*C14*VARIABLES!$B$46)</f>
-        <v>250.8533739574774</v>
+        <v>165.98354275118913</v>
       </c>
       <c r="S14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$42,0,(IF($A14=VARIABLES!$B$42,0,S13)+P14)*(1+C14)-R14)</f>
-        <v>250602.52058351994</v>
+        <v>234107.93108321287</v>
       </c>
       <c r="T14" s="34">
         <f>IF($A14&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A14-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14" s="14">
         <f>T14*VARIABLES!$B$53+IF(AND($A14&gt;=VARIABLES!$B$50,MOD($A14-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A14-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="V14" s="14">
         <f>U14*VARIABLES!$B$54</f>
-        <v>675</v>
+        <v>712.5</v>
       </c>
       <c r="W14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$50,0,(IF($A14&lt;VARIABLES!$B$50+1,0,X13)+U14)*C14*VARIABLES!$B$55)</f>
-        <v>2722.0738189873468</v>
+        <v>2163.4604626338951</v>
       </c>
       <c r="X14" s="14">
         <f>IF($A14&lt;VARIABLES!$B$50,0,(IF($A14&lt;VARIABLES!$B$50+1,0,X13)+U14)*(1+C14)-W14)</f>
-        <v>677796.38092784944</v>
+        <v>761229.01706675487</v>
       </c>
       <c r="Y14" s="14">
         <f t="shared" si="0"/>
-        <v>350000</v>
+        <v>355000</v>
       </c>
       <c r="Z14" s="14">
         <f t="shared" si="1"/>
-        <v>2625</v>
+        <v>2662.5</v>
       </c>
       <c r="AA14" s="14">
         <f t="shared" si="2"/>
-        <v>37251.986941311217</v>
+        <v>24199.907232755006</v>
       </c>
       <c r="AB14" s="35">
         <f t="shared" si="3"/>
-        <v>39876.986941311217</v>
+        <v>26862.407232755006</v>
       </c>
       <c r="AC14" s="36">
         <f t="shared" si="4"/>
-        <v>11926989.801979853</v>
+        <v>10958523.095373834</v>
       </c>
       <c r="AD14" s="14">
         <f>IF($A14=1,VARIABLES!$B$12,0)</f>
@@ -5729,19 +5729,19 @@
       </c>
       <c r="AJ14" s="38">
         <f>IF($A14&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK14" s="39">
         <f t="shared" si="6"/>
-        <v>-31706.346392022115</v>
+        <v>-25567.592767244994</v>
       </c>
       <c r="AL14" s="39">
         <f t="shared" si="7"/>
-        <v>-392604.84348825266</v>
+        <v>-275811.69446015562</v>
       </c>
       <c r="AM14" s="40">
         <f t="shared" si="8"/>
-        <v>292416.66666666669</v>
+        <v>81730</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.2">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C15" s="42">
         <f>IF($A15&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$21,0,IF($A15=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="F15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$21,0,(IF($A15=VARIABLES!$B$21,0,G14)+D15)*C15*VARIABLES!$B$25)</f>
-        <v>3625.8915529196211</v>
+        <v>2349.1811642298126</v>
       </c>
       <c r="G15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$21,0,(IF($A15=VARIABLES!$B$21,0,G14)+D15)*(1+C15)-F15)</f>
-        <v>3622265.6613667021</v>
+        <v>3313352.2334915628</v>
       </c>
       <c r="H15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$28,0,IF($A15=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5782,11 +5782,11 @@
       </c>
       <c r="J15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$28,0,(IF($A15=VARIABLES!$B$28,0,K14)+H15)*C15*VARIABLES!$B$32)</f>
-        <v>2218.8137354644123</v>
+        <v>1465.7579469072716</v>
       </c>
       <c r="K15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$28,0,(IF($A15=VARIABLES!$B$28,0,K14)+H15)*(1+C15)-J15)</f>
-        <v>552484.62013063871</v>
+        <v>515737.40331894433</v>
       </c>
       <c r="L15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$35,0,IF($A15=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5798,11 +5798,11 @@
       </c>
       <c r="N15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$35,0,(IF($A15=VARIABLES!$B$35,0,O14)+L15)*C15*VARIABLES!$B$39)</f>
-        <v>30105.082138142458</v>
+        <v>18896.810325576418</v>
       </c>
       <c r="O15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$35,0,(IF($A15=VARIABLES!$B$35,0,O14)+L15)*(1+C15)-N15)</f>
-        <v>7496165.4523974722</v>
+        <v>6648977.6902706744</v>
       </c>
       <c r="P15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$42,0,IF($A15=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5814,51 +5814,51 @@
       </c>
       <c r="R15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$42,0,(IF($A15=VARIABLES!$B$42,0,S14)+P15)*C15*VARIABLES!$B$46)</f>
-        <v>281.87762560783329</v>
+        <v>185.28703308150938</v>
       </c>
       <c r="S15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$42,0,(IF($A15=VARIABLES!$B$42,0,S14)+P15)*(1+C15)-R15)</f>
-        <v>281595.7479822255</v>
+        <v>261334.1253733917</v>
       </c>
       <c r="T15" s="44">
         <f>IF($A15&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A15-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15" s="43">
         <f>T15*VARIABLES!$B$53+IF(AND($A15&gt;=VARIABLES!$B$50,MOD($A15-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A15-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>95000</v>
+        <v>100000</v>
       </c>
       <c r="V15" s="43">
         <f>U15*VARIABLES!$B$54</f>
-        <v>712.5</v>
+        <v>750</v>
       </c>
       <c r="W15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$50,0,(IF($A15&lt;VARIABLES!$B$50+1,0,X14)+U15)*C15*VARIABLES!$B$55)</f>
-        <v>3219.9849205327064</v>
+        <v>2511.917966444702</v>
       </c>
       <c r="X15" s="43">
         <f>IF($A15&lt;VARIABLES!$B$50,0,(IF($A15&lt;VARIABLES!$B$50+1,0,X14)+U15)*(1+C15)-W15)</f>
-        <v>801776.24521264387</v>
+        <v>883836.27876475709</v>
       </c>
       <c r="Y15" s="43">
         <f t="shared" si="0"/>
-        <v>355000</v>
+        <v>360000</v>
       </c>
       <c r="Z15" s="43">
         <f t="shared" si="1"/>
-        <v>2662.5</v>
+        <v>2700</v>
       </c>
       <c r="AA15" s="43">
         <f t="shared" si="2"/>
-        <v>39451.64997266703</v>
+        <v>25408.954436239714</v>
       </c>
       <c r="AB15" s="35">
         <f t="shared" si="3"/>
-        <v>42114.14997266703</v>
+        <v>28108.954436239714</v>
       </c>
       <c r="AC15" s="36">
         <f t="shared" si="4"/>
-        <v>12754287.727089684</v>
+        <v>11623237.731219329</v>
       </c>
       <c r="AD15" s="43">
         <f>IF($A15=1,VARIABLES!$B$12,0)</f>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AF15" s="43">
         <f>IF(MOD($A15,12)=0,AC15*VARIABLES!$B$16,0)</f>
-        <v>31885.719317724212</v>
+        <v>29058.094328048322</v>
       </c>
       <c r="AG15" s="43">
         <f>VARIABLES!$B$17</f>
@@ -5882,23 +5882,23 @@
       </c>
       <c r="AI15" s="37">
         <f t="shared" si="5"/>
-        <v>79885.719317724215</v>
+        <v>77058.094328048319</v>
       </c>
       <c r="AJ15" s="38">
         <f>IF($A15&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK15" s="45">
         <f t="shared" si="6"/>
-        <v>-64354.902678390514</v>
+        <v>-56379.139891808605</v>
       </c>
       <c r="AL15" s="45">
         <f t="shared" si="7"/>
-        <v>-456959.74616664316</v>
+        <v>-332190.83435196424</v>
       </c>
       <c r="AM15" s="40">
         <f t="shared" si="8"/>
-        <v>319000</v>
+        <v>89160</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.2">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C16" s="33">
         <f>IF($A16&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$21,0,IF($A16=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5923,11 +5923,11 @@
       </c>
       <c r="F16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$21,0,(IF($A16=VARIABLES!$B$21,0,G15)+D16)*C16*VARIABLES!$B$25)</f>
-        <v>3981.5267305903144</v>
+        <v>2561.8193369209312</v>
       </c>
       <c r="G16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$21,0,(IF($A16=VARIABLES!$B$21,0,G15)+D16)*(1+C16)-F16)</f>
-        <v>3977545.2038597246</v>
+        <v>3613263.1876314785</v>
       </c>
       <c r="H16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$28,0,IF($A16=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5939,11 +5939,11 @@
       </c>
       <c r="J16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$28,0,(IF($A16=VARIABLES!$B$28,0,K15)+H16)*C16*VARIABLES!$B$32)</f>
-        <v>2468.6859172109944</v>
+        <v>1620.9007596802544</v>
       </c>
       <c r="K16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$28,0,(IF($A16=VARIABLES!$B$28,0,K15)+H16)*(1+C16)-J16)</f>
-        <v>614702.79338553769</v>
+        <v>570325.51015606662</v>
       </c>
       <c r="L16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$35,0,IF($A16=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5955,11 +5955,11 @@
       </c>
       <c r="N16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$35,0,(IF($A16=VARIABLES!$B$35,0,O15)+L16)*C16*VARIABLES!$B$39)</f>
-        <v>31234.022718322802</v>
+        <v>19392.851596622797</v>
       </c>
       <c r="O16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$35,0,(IF($A16=VARIABLES!$B$35,0,O15)+L16)*(1+C16)-N16)</f>
-        <v>7777271.6568623781</v>
+        <v>6823513.354640279</v>
       </c>
       <c r="P16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$42,0,IF($A16=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5971,51 +5971,51 @@
       </c>
       <c r="R16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$42,0,(IF($A16=VARIABLES!$B$42,0,S15)+P16)*C16*VARIABLES!$B$46)</f>
-        <v>314.16223748148491</v>
+        <v>205.1394664180981</v>
       </c>
       <c r="S16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$42,0,(IF($A16=VARIABLES!$B$42,0,S15)+P16)*(1+C16)-R16)</f>
-        <v>313848.07524400338</v>
+        <v>289334.5645636975</v>
       </c>
       <c r="T16" s="34">
         <f>IF($A16&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A16-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U16" s="14">
         <f>T16*VARIABLES!$B$53+IF(AND($A16&gt;=VARIABLES!$B$50,MOD($A16-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A16-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>100000</v>
+        <v>105000</v>
       </c>
       <c r="V16" s="14">
         <f>U16*VARIABLES!$B$54</f>
-        <v>750</v>
+        <v>787.5</v>
       </c>
       <c r="W16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$50,0,(IF($A16&lt;VARIABLES!$B$50+1,0,X15)+U16)*C16*VARIABLES!$B$55)</f>
-        <v>3757.4010217193495</v>
+        <v>2884.1058130638748</v>
       </c>
       <c r="X16" s="14">
         <f>IF($A16&lt;VARIABLES!$B$50,0,(IF($A16&lt;VARIABLES!$B$50+1,0,X15)+U16)*(1+C16)-W16)</f>
-        <v>935592.85440811806</v>
+        <v>1014793.2310823319</v>
       </c>
       <c r="Y16" s="14">
         <f t="shared" si="0"/>
-        <v>360000</v>
+        <v>365000</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="1"/>
-        <v>2700</v>
+        <v>2737.5</v>
       </c>
       <c r="AA16" s="14">
         <f t="shared" si="2"/>
-        <v>41755.79862532494</v>
+        <v>26664.816972705954</v>
       </c>
       <c r="AB16" s="35">
         <f t="shared" si="3"/>
-        <v>44455.79862532494</v>
+        <v>29402.316972705954</v>
       </c>
       <c r="AC16" s="36">
         <f t="shared" si="4"/>
-        <v>13618960.583759764</v>
+        <v>12311229.848073853</v>
       </c>
       <c r="AD16" s="14">
         <f>IF($A16=1,VARIABLES!$B$12,0)</f>
@@ -6043,19 +6043,19 @@
       </c>
       <c r="AJ16" s="38">
         <f>IF($A16&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK16" s="39">
         <f t="shared" si="6"/>
-        <v>-27127.534708008392</v>
+        <v>-23027.683027294046</v>
       </c>
       <c r="AL16" s="39">
         <f t="shared" si="7"/>
-        <v>-484087.28087465157</v>
+        <v>-355218.51737925829</v>
       </c>
       <c r="AM16" s="40">
         <f t="shared" si="8"/>
-        <v>345583.33333333331</v>
+        <v>96590</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.2">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C17" s="42">
         <f>IF($A17&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$21,0,IF($A17=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6080,11 +6080,11 @@
       </c>
       <c r="F17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$21,0,(IF($A17=VARIABLES!$B$21,0,G16)+D17)*C17*VARIABLES!$B$25)</f>
-        <v>4351.6095873538798</v>
+        <v>2780.504407647953</v>
       </c>
       <c r="G17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$21,0,(IF($A17=VARIABLES!$B$21,0,G16)+D17)*(1+C17)-F17)</f>
-        <v>4347257.9777665269</v>
+        <v>3921702.8595297481</v>
       </c>
       <c r="H17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$28,0,IF($A17=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6096,11 +6096,11 @@
       </c>
       <c r="J17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$28,0,(IF($A17=VARIABLES!$B$28,0,K16)+H17)*C17*VARIABLES!$B$32)</f>
-        <v>2727.9283057730736</v>
+        <v>1780.1160712885276</v>
       </c>
       <c r="K17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$28,0,(IF($A17=VARIABLES!$B$28,0,K16)+H17)*(1+C17)-J17)</f>
-        <v>679254.14813749539</v>
+        <v>626346.55479766335</v>
       </c>
       <c r="L17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$35,0,IF($A17=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6112,11 +6112,11 @@
       </c>
       <c r="N17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$35,0,(IF($A17=VARIABLES!$B$35,0,O16)+L17)*C17*VARIABLES!$B$39)</f>
-        <v>32405.298570259907</v>
+        <v>19901.913951034148</v>
       </c>
       <c r="O17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$35,0,(IF($A17=VARIABLES!$B$35,0,O16)+L17)*(1+C17)-N17)</f>
-        <v>8068919.343994718</v>
+        <v>7002630.5801995862</v>
       </c>
       <c r="P17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$42,0,IF($A17=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6128,51 +6128,51 @@
       </c>
       <c r="R17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$42,0,(IF($A17=VARIABLES!$B$42,0,S16)+P17)*C17*VARIABLES!$B$46)</f>
-        <v>347.75841171250352</v>
+        <v>225.55645332769606</v>
       </c>
       <c r="S17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$42,0,(IF($A17=VARIABLES!$B$42,0,S16)+P17)*(1+C17)-R17)</f>
-        <v>347410.65330079105</v>
+        <v>318131.26624347758</v>
       </c>
       <c r="T17" s="44">
         <f>IF($A17&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A17-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U17" s="43">
         <f>T17*VARIABLES!$B$53+IF(AND($A17&gt;=VARIABLES!$B$50,MOD($A17-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A17-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>105000</v>
+        <v>110000</v>
       </c>
       <c r="V17" s="43">
         <f>U17*VARIABLES!$B$54</f>
-        <v>787.5</v>
+        <v>825</v>
       </c>
       <c r="W17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$50,0,(IF($A17&lt;VARIABLES!$B$50+1,0,X16)+U17)*C17*VARIABLES!$B$55)</f>
-        <v>4335.8035600338253</v>
+        <v>3280.6469239901344</v>
       </c>
       <c r="X17" s="43">
         <f>IF($A17&lt;VARIABLES!$B$50,0,(IF($A17&lt;VARIABLES!$B$50+1,0,X16)+U17)*(1+C17)-W17)</f>
-        <v>1079615.0864484224</v>
+        <v>1154319.0533982429</v>
       </c>
       <c r="Y17" s="43">
         <f t="shared" si="0"/>
-        <v>365000</v>
+        <v>370000</v>
       </c>
       <c r="Z17" s="43">
         <f t="shared" si="1"/>
-        <v>2737.5</v>
+        <v>2775</v>
       </c>
       <c r="AA17" s="43">
         <f t="shared" si="2"/>
-        <v>44168.398435133189</v>
+        <v>27968.737807288457</v>
       </c>
       <c r="AB17" s="35">
         <f t="shared" si="3"/>
-        <v>46905.898435133189</v>
+        <v>30743.737807288457</v>
       </c>
       <c r="AC17" s="36">
         <f t="shared" si="4"/>
-        <v>14522457.209647952</v>
+        <v>13023130.314168718</v>
       </c>
       <c r="AD17" s="43">
         <f>IF($A17=1,VARIABLES!$B$12,0)</f>
@@ -6200,19 +6200,19 @@
       </c>
       <c r="AJ17" s="38">
         <f>IF($A17&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK17" s="45">
         <f t="shared" si="6"/>
-        <v>-24677.434898200143</v>
+        <v>-21686.262192711543</v>
       </c>
       <c r="AL17" s="45">
         <f t="shared" si="7"/>
-        <v>-508764.71577285172</v>
+        <v>-376904.77957196982</v>
       </c>
       <c r="AM17" s="40">
         <f t="shared" si="8"/>
-        <v>372166.66666666663</v>
+        <v>104020</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.2">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C18" s="33">
         <f>IF($A18&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$21,0,IF($A18=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6237,11 +6237,11 @@
       </c>
       <c r="F18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$21,0,(IF($A18=VARIABLES!$B$21,0,G17)+D18)*C18*VARIABLES!$B$25)</f>
-        <v>4736.7270601734654</v>
+        <v>3005.4083350737747</v>
       </c>
       <c r="G18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$21,0,(IF($A18=VARIABLES!$B$21,0,G17)+D18)*(1+C18)-F18)</f>
-        <v>4731990.3331132922</v>
+        <v>4238913.784597625</v>
       </c>
       <c r="H18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$28,0,IF($A18=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6253,11 +6253,11 @@
       </c>
       <c r="J18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$28,0,(IF($A18=VARIABLES!$B$28,0,K17)+H18)*C18*VARIABLES!$B$32)</f>
-        <v>2996.8922839062307</v>
+        <v>1943.5107848265179</v>
       </c>
       <c r="K18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$28,0,(IF($A18=VARIABLES!$B$28,0,K17)+H18)*(1+C18)-J18)</f>
-        <v>746226.17869265156</v>
+        <v>683838.15186110197</v>
       </c>
       <c r="L18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$35,0,IF($A18=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6269,11 +6269,11 @@
       </c>
       <c r="N18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$35,0,(IF($A18=VARIABLES!$B$35,0,O17)+L18)*C18*VARIABLES!$B$39)</f>
-        <v>33620.497266644663</v>
+        <v>20424.339192248794</v>
       </c>
       <c r="O18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$35,0,(IF($A18=VARIABLES!$B$35,0,O17)+L18)*(1+C18)-N18)</f>
-        <v>8371503.8193945214</v>
+        <v>7186449.6329298243</v>
       </c>
       <c r="P18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$42,0,IF($A18=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6285,51 +6285,51 @@
       </c>
       <c r="R18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$42,0,(IF($A18=VARIABLES!$B$42,0,S17)+P18)*C18*VARIABLES!$B$46)</f>
-        <v>382.71943052165739</v>
+        <v>246.5540483025357</v>
       </c>
       <c r="S18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$42,0,(IF($A18=VARIABLES!$B$42,0,S17)+P18)*(1+C18)-R18)</f>
-        <v>382336.71109113569</v>
+        <v>347746.87412727647</v>
       </c>
       <c r="T18" s="34">
         <f>IF($A18&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A18-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U18" s="14">
         <f>T18*VARIABLES!$B$53+IF(AND($A18&gt;=VARIABLES!$B$50,MOD($A18-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A18-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>110000</v>
+        <v>115000</v>
       </c>
       <c r="V18" s="14">
         <f>U18*VARIABLES!$B$54</f>
-        <v>825</v>
+        <v>862.5</v>
       </c>
       <c r="W18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$50,0,(IF($A18&lt;VARIABLES!$B$50+1,0,X17)+U18)*C18*VARIABLES!$B$55)</f>
-        <v>4956.7295268684265</v>
+        <v>3702.180572411542</v>
       </c>
       <c r="X18" s="14">
         <f>IF($A18&lt;VARIABLES!$B$50,0,(IF($A18&lt;VARIABLES!$B$50+1,0,X17)+U18)*(1+C18)-W18)</f>
-        <v>1234225.6521902385</v>
+        <v>1302638.6785499468</v>
       </c>
       <c r="Y18" s="14">
         <f t="shared" si="0"/>
-        <v>370000</v>
+        <v>375000</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="1"/>
-        <v>2775</v>
+        <v>2812.5</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="2"/>
-        <v>46693.565568114442</v>
+        <v>29321.992932863162</v>
       </c>
       <c r="AB18" s="35">
         <f t="shared" si="3"/>
-        <v>49468.565568114442</v>
+        <v>32134.492932863162</v>
       </c>
       <c r="AC18" s="36">
         <f t="shared" si="4"/>
-        <v>15466282.69448184</v>
+        <v>13759587.122065775</v>
       </c>
       <c r="AD18" s="14">
         <f>IF($A18=1,VARIABLES!$B$12,0)</f>
@@ -6357,19 +6357,19 @@
       </c>
       <c r="AJ18" s="38">
         <f>IF($A18&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK18" s="39">
         <f t="shared" si="6"/>
-        <v>-22114.76776521889</v>
+        <v>-20295.507067136838</v>
       </c>
       <c r="AL18" s="39">
         <f t="shared" si="7"/>
-        <v>-530879.48353807058</v>
+        <v>-397200.28663910663</v>
       </c>
       <c r="AM18" s="40">
         <f t="shared" si="8"/>
-        <v>398749.99999999994</v>
+        <v>111450</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.2">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="C19" s="42">
         <f>IF($A19&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$21,0,IF($A19=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6394,11 +6394,11 @@
       </c>
       <c r="F19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$21,0,(IF($A19=VARIABLES!$B$21,0,G18)+D19)*C19*VARIABLES!$B$25)</f>
-        <v>5137.4899303263464</v>
+        <v>3236.707967935768</v>
       </c>
       <c r="G19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$21,0,(IF($A19=VARIABLES!$B$21,0,G18)+D19)*(1+C19)-F19)</f>
-        <v>5132352.4403960202</v>
+        <v>4565145.3953471193</v>
       </c>
       <c r="H19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$28,0,IF($A19=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6410,11 +6410,11 @@
       </c>
       <c r="J19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$28,0,(IF($A19=VARIABLES!$B$28,0,K18)+H19)*C19*VARIABLES!$B$32)</f>
-        <v>3275.9424112193815</v>
+        <v>2111.1946095948806</v>
       </c>
       <c r="K19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$28,0,(IF($A19=VARIABLES!$B$28,0,K18)+H19)*(1+C19)-J19)</f>
-        <v>815709.66039362608</v>
+        <v>742838.90334745578</v>
       </c>
       <c r="L19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$35,0,IF($A19=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6426,11 +6426,11 @@
       </c>
       <c r="N19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$35,0,(IF($A19=VARIABLES!$B$35,0,O18)+L19)*C19*VARIABLES!$B$39)</f>
-        <v>34881.265914143842</v>
+        <v>20960.478096045321</v>
       </c>
       <c r="O19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$35,0,(IF($A19=VARIABLES!$B$35,0,O18)+L19)*(1+C19)-N19)</f>
-        <v>8685435.2126218155</v>
+        <v>7375093.9357942315</v>
       </c>
       <c r="P19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$42,0,IF($A19=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6442,51 +6442,51 @@
       </c>
       <c r="R19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$42,0,(IF($A19=VARIABLES!$B$42,0,S18)+P19)*C19*VARIABLES!$B$46)</f>
-        <v>419.10074071993296</v>
+        <v>268.14876238447243</v>
       </c>
       <c r="S19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$42,0,(IF($A19=VARIABLES!$B$42,0,S18)+P19)*(1+C19)-R19)</f>
-        <v>418681.63997921313</v>
+        <v>378204.67586027086</v>
       </c>
       <c r="T19" s="44">
         <f>IF($A19&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A19-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U19" s="43">
         <f>T19*VARIABLES!$B$53+IF(AND($A19&gt;=VARIABLES!$B$50,MOD($A19-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A19-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="V19" s="43">
         <f>U19*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="W19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$50,0,(IF($A19&lt;VARIABLES!$B$50+1,0,X18)+U19)*C19*VARIABLES!$B$55)</f>
-        <v>5392.6068841259939</v>
+        <v>4149.3628124373445</v>
       </c>
       <c r="X19" s="43">
         <f>IF($A19&lt;VARIABLES!$B$50,0,(IF($A19&lt;VARIABLES!$B$50+1,0,X18)+U19)*(1+C19)-W19)</f>
-        <v>1342759.1141473723</v>
+        <v>1459982.9438618827</v>
       </c>
       <c r="Y19" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>380000</v>
       </c>
       <c r="Z19" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2850</v>
       </c>
       <c r="AA19" s="43">
         <f t="shared" si="2"/>
-        <v>49106.405880535494</v>
+        <v>30725.892248397788</v>
       </c>
       <c r="AB19" s="35">
         <f t="shared" si="3"/>
-        <v>51506.405880535494</v>
+        <v>33575.892248397788</v>
       </c>
       <c r="AC19" s="36">
         <f t="shared" si="4"/>
-        <v>16394938.067538049</v>
+        <v>14521265.854210962</v>
       </c>
       <c r="AD19" s="43">
         <f>IF($A19=1,VARIABLES!$B$12,0)</f>
@@ -6514,19 +6514,19 @@
       </c>
       <c r="AJ19" s="38">
         <f>IF($A19&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK19" s="45">
         <f t="shared" si="6"/>
-        <v>-20076.927452797838</v>
+        <v>-18854.107751602212</v>
       </c>
       <c r="AL19" s="45">
         <f t="shared" si="7"/>
-        <v>-550956.41099086846</v>
+        <v>-416054.39439070883</v>
       </c>
       <c r="AM19" s="40">
         <f t="shared" si="8"/>
-        <v>425333.33333333326</v>
+        <v>118880</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.2">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="C20" s="33">
         <f>IF($A20&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$21,0,IF($A20=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6551,11 +6551,11 @@
       </c>
       <c r="F20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$21,0,(IF($A20=VARIABLES!$B$21,0,G19)+D20)*C20*VARIABLES!$B$25)</f>
-        <v>5554.5337920791881</v>
+        <v>3474.5851841072745</v>
       </c>
       <c r="G20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$21,0,(IF($A20=VARIABLES!$B$21,0,G19)+D20)*(1+C20)-F20)</f>
-        <v>5548979.2582871085</v>
+        <v>4900654.217527302</v>
       </c>
       <c r="H20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$28,0,IF($A20=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6567,11 +6567,11 @@
       </c>
       <c r="J20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$28,0,(IF($A20=VARIABLES!$B$28,0,K19)+H20)*C20*VARIABLES!$B$32)</f>
-        <v>3565.4569183067756</v>
+        <v>2283.2801347634127</v>
       </c>
       <c r="K20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$28,0,(IF($A20=VARIABLES!$B$28,0,K19)+H20)*(1+C20)-J20)</f>
-        <v>887798.77265838708</v>
+        <v>803388.42456032638</v>
       </c>
       <c r="L20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$35,0,IF($A20=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6583,11 +6583,11 @@
       </c>
       <c r="N20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$35,0,(IF($A20=VARIABLES!$B$35,0,O19)+L20)*C20*VARIABLES!$B$39)</f>
-        <v>36189.31338592423</v>
+        <v>21510.690646066505</v>
       </c>
       <c r="O20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$35,0,(IF($A20=VARIABLES!$B$35,0,O19)+L20)*(1+C20)-N20)</f>
-        <v>9011139.0330951344</v>
+        <v>7568690.1516088294</v>
       </c>
       <c r="P20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$42,0,IF($A20=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6599,51 +6599,51 @@
       </c>
       <c r="R20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$42,0,(IF($A20=VARIABLES!$B$42,0,S19)+P20)*C20*VARIABLES!$B$46)</f>
-        <v>456.96004164501369</v>
+        <v>290.35757614811416</v>
       </c>
       <c r="S20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$42,0,(IF($A20=VARIABLES!$B$42,0,S19)+P20)*(1+C20)-R20)</f>
-        <v>456503.08160336869</v>
+        <v>409528.62133004726</v>
       </c>
       <c r="T20" s="34">
         <f>IF($A20&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A20-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U20" s="14">
         <f>T20*VARIABLES!$B$53+IF(AND($A20&gt;=VARIABLES!$B$50,MOD($A20-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A20-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>125000</v>
       </c>
       <c r="V20" s="14">
         <f>U20*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>937.5</v>
       </c>
       <c r="W20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$50,0,(IF($A20&lt;VARIABLES!$B$50+1,0,X19)+U20)*C20*VARIABLES!$B$55)</f>
-        <v>5844.829642280718</v>
+        <v>4622.8669195971579</v>
       </c>
       <c r="X20" s="14">
         <f>IF($A20&lt;VARIABLES!$B$50,0,(IF($A20&lt;VARIABLES!$B$50+1,0,X19)+U20)*(1+C20)-W20)</f>
-        <v>1455362.5809278989</v>
+        <v>1626588.746138257</v>
       </c>
       <c r="Y20" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>385000</v>
       </c>
       <c r="Z20" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2887.5</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="2"/>
-        <v>51611.093780235926</v>
+        <v>32181.780460682465</v>
       </c>
       <c r="AB20" s="35">
         <f t="shared" si="3"/>
-        <v>54011.093780235926</v>
+        <v>35069.280460682465</v>
       </c>
       <c r="AC20" s="36">
         <f t="shared" si="4"/>
-        <v>17359782.726571899</v>
+        <v>15308850.161164761</v>
       </c>
       <c r="AD20" s="14">
         <f>IF($A20=1,VARIABLES!$B$12,0)</f>
@@ -6671,19 +6671,19 @@
       </c>
       <c r="AJ20" s="38">
         <f>IF($A20&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK20" s="39">
         <f t="shared" si="6"/>
-        <v>-17572.239553097406</v>
+        <v>-17360.719539317535</v>
       </c>
       <c r="AL20" s="39">
         <f t="shared" si="7"/>
-        <v>-568528.65054396586</v>
+        <v>-433415.11393002636</v>
       </c>
       <c r="AM20" s="40">
         <f t="shared" si="8"/>
-        <v>451916.66666666657</v>
+        <v>126310</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C21" s="42">
         <f>IF($A21&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$21,0,IF($A21=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6708,11 +6708,11 @@
       </c>
       <c r="F21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$21,0,(IF($A21=VARIABLES!$B$21,0,G20)+D21)*C21*VARIABLES!$B$25)</f>
-        <v>5988.5200607157385</v>
+        <v>3719.2270336136571</v>
       </c>
       <c r="G21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$21,0,(IF($A21=VARIABLES!$B$21,0,G20)+D21)*(1+C21)-F21)</f>
-        <v>5982531.5406550225</v>
+        <v>5245704.0718382346</v>
       </c>
       <c r="H21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$28,0,IF($A21=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6724,11 +6724,11 @@
       </c>
       <c r="J21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$28,0,(IF($A21=VARIABLES!$B$28,0,K20)+H21)*C21*VARIABLES!$B$32)</f>
-        <v>3865.8282194099465</v>
+        <v>2459.8829049676187</v>
       </c>
       <c r="K21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$28,0,(IF($A21=VARIABLES!$B$28,0,K20)+H21)*(1+C21)-J21)</f>
-        <v>962591.22663307667</v>
+        <v>865527.37070503482</v>
       </c>
       <c r="L21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$35,0,IF($A21=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6740,11 +6740,11 @@
       </c>
       <c r="N21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$35,0,(IF($A21=VARIABLES!$B$35,0,O20)+L21)*C21*VARIABLES!$B$39)</f>
-        <v>37546.412637896392</v>
+        <v>22075.34627552575</v>
       </c>
       <c r="O21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$35,0,(IF($A21=VARIABLES!$B$35,0,O20)+L21)*(1+C21)-N21)</f>
-        <v>9349056.7468362022</v>
+        <v>7767368.2680885596</v>
       </c>
       <c r="P21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$42,0,IF($A21=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6756,51 +6756,51 @@
       </c>
       <c r="R21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$42,0,(IF($A21=VARIABLES!$B$42,0,S20)+P21)*C21*VARIABLES!$B$46)</f>
-        <v>496.35737667017565</v>
+        <v>313.19795305315944</v>
       </c>
       <c r="S21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$42,0,(IF($A21=VARIABLES!$B$42,0,S20)+P21)*(1+C21)-R21)</f>
-        <v>495861.01929350558</v>
+        <v>441743.3414991204</v>
       </c>
       <c r="T21" s="44">
         <f>IF($A21&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A21-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U21" s="43">
         <f>T21*VARIABLES!$B$53+IF(AND($A21&gt;=VARIABLES!$B$50,MOD($A21-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A21-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>130000</v>
       </c>
       <c r="V21" s="43">
         <f>U21*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>975</v>
       </c>
       <c r="W21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$50,0,(IF($A21&lt;VARIABLES!$B$50+1,0,X20)+U21)*C21*VARIABLES!$B$55)</f>
-        <v>6314.0107538662451</v>
+        <v>5123.3838429032494</v>
       </c>
       <c r="X21" s="43">
         <f>IF($A21&lt;VARIABLES!$B$50,0,(IF($A21&lt;VARIABLES!$B$50+1,0,X20)+U21)*(1+C21)-W21)</f>
-        <v>1572188.6777126952</v>
+        <v>1802699.2007243861</v>
       </c>
       <c r="Y21" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>390000</v>
       </c>
       <c r="Z21" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2925</v>
       </c>
       <c r="AA21" s="43">
         <f t="shared" si="2"/>
-        <v>54211.12904855849</v>
+        <v>33691.038010063436</v>
       </c>
       <c r="AB21" s="35">
         <f t="shared" si="3"/>
-        <v>56611.12904855849</v>
+        <v>36616.038010063436</v>
       </c>
       <c r="AC21" s="36">
         <f t="shared" si="4"/>
-        <v>18362229.2111305</v>
+        <v>16123042.252855334</v>
       </c>
       <c r="AD21" s="43">
         <f>IF($A21=1,VARIABLES!$B$12,0)</f>
@@ -6828,19 +6828,19 @@
       </c>
       <c r="AJ21" s="38">
         <f>IF($A21&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK21" s="45">
         <f t="shared" si="6"/>
-        <v>-14972.204284774842</v>
+        <v>-15813.961989936564</v>
       </c>
       <c r="AL21" s="45">
         <f t="shared" si="7"/>
-        <v>-583500.8548287407</v>
+        <v>-449229.07591996295</v>
       </c>
       <c r="AM21" s="40">
         <f t="shared" si="8"/>
-        <v>478499.99999999988</v>
+        <v>133740</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C22" s="33">
         <f>IF($A22&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$21,0,IF($A22=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6865,11 +6865,11 @@
       </c>
       <c r="F22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$21,0,(IF($A22=VARIABLES!$B$21,0,G21)+D22)*C22*VARIABLES!$B$25)</f>
-        <v>6440.1370215156485</v>
+        <v>3970.8258857153796</v>
       </c>
       <c r="G22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$21,0,(IF($A22=VARIABLES!$B$21,0,G21)+D22)*(1+C22)-F22)</f>
-        <v>6433696.8844941333</v>
+        <v>5600566.2813811339</v>
       </c>
       <c r="H22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$28,0,IF($A22=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6881,11 +6881,11 @@
       </c>
       <c r="J22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$28,0,(IF($A22=VARIABLES!$B$28,0,K21)+H22)*C22*VARIABLES!$B$32)</f>
-        <v>4177.4634443044861</v>
+        <v>2641.1214978896846</v>
       </c>
       <c r="K22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$28,0,(IF($A22=VARIABLES!$B$28,0,K21)+H22)*(1+C22)-J22)</f>
-        <v>1040188.397631817</v>
+        <v>929297.46418604197</v>
       </c>
       <c r="L22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$35,0,IF($A22=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6897,11 +6897,11 @@
       </c>
       <c r="N22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$35,0,(IF($A22=VARIABLES!$B$35,0,O21)+L22)*C22*VARIABLES!$B$39)</f>
-        <v>38954.403111817512</v>
+        <v>22654.824115258296</v>
       </c>
       <c r="O22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$35,0,(IF($A22=VARIABLES!$B$35,0,O21)+L22)*(1+C22)-N22)</f>
-        <v>9699646.3748425599</v>
+        <v>7971261.6851258827</v>
       </c>
       <c r="P22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$42,0,IF($A22=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6913,51 +6913,51 @@
       </c>
       <c r="R22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$42,0,(IF($A22=VARIABLES!$B$42,0,S21)+P22)*C22*VARIABLES!$B$46)</f>
-        <v>537.355228430735</v>
+        <v>336.68785317644193</v>
       </c>
       <c r="S22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$42,0,(IF($A22=VARIABLES!$B$42,0,S21)+P22)*(1+C22)-R22)</f>
-        <v>536817.87320230436</v>
+        <v>474874.16777300159</v>
       </c>
       <c r="T22" s="34">
         <f>IF($A22&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A22-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U22" s="14">
         <f>T22*VARIABLES!$B$53+IF(AND($A22&gt;=VARIABLES!$B$50,MOD($A22-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A22-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>135000</v>
       </c>
       <c r="V22" s="14">
         <f>U22*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1012.5</v>
       </c>
       <c r="W22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$50,0,(IF($A22&lt;VARIABLES!$B$50+1,0,X21)+U22)*C22*VARIABLES!$B$55)</f>
-        <v>6800.78615713623</v>
+        <v>5651.6226687794588</v>
       </c>
       <c r="X22" s="14">
         <f>IF($A22&lt;VARIABLES!$B$50,0,(IF($A22&lt;VARIABLES!$B$50+1,0,X21)+U22)*(1+C22)-W22)</f>
-        <v>1693395.7531269214</v>
+        <v>1988563.804743401</v>
       </c>
       <c r="Y22" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>395000</v>
       </c>
       <c r="Z22" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2962.5</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" si="2"/>
-        <v>56910.144963204613</v>
+        <v>35255.08202081926</v>
       </c>
       <c r="AB22" s="35">
         <f t="shared" si="3"/>
-        <v>59310.144963204613</v>
+        <v>38217.58202081926</v>
       </c>
       <c r="AC22" s="36">
         <f t="shared" si="4"/>
-        <v>19403745.28329774</v>
+        <v>16964563.403209459</v>
       </c>
       <c r="AD22" s="14">
         <f>IF($A22=1,VARIABLES!$B$12,0)</f>
@@ -6985,19 +6985,19 @@
       </c>
       <c r="AJ22" s="38">
         <f>IF($A22&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK22" s="39">
         <f t="shared" si="6"/>
-        <v>-12273.188370128719</v>
+        <v>-14212.41797918074</v>
       </c>
       <c r="AL22" s="39">
         <f t="shared" si="7"/>
-        <v>-595774.04319886945</v>
+        <v>-463441.49389914371</v>
       </c>
       <c r="AM22" s="40">
         <f t="shared" si="8"/>
-        <v>505083.3333333332</v>
+        <v>141170</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.2">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C23" s="42">
         <f>IF($A23&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$21,0,IF($A23=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7022,11 +7022,11 @@
       </c>
       <c r="F23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$21,0,(IF($A23=VARIABLES!$B$21,0,G22)+D23)*C23*VARIABLES!$B$25)</f>
-        <v>6910.1009213480547</v>
+        <v>4229.5795801737431</v>
       </c>
       <c r="G23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$21,0,(IF($A23=VARIABLES!$B$21,0,G22)+D23)*(1+C23)-F23)</f>
-        <v>6903190.8204267081</v>
+        <v>5965519.8850079095</v>
       </c>
       <c r="H23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$28,0,IF($A23=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7038,11 +7038,11 @@
       </c>
       <c r="J23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$28,0,(IF($A23=VARIABLES!$B$28,0,K22)+H23)*C23*VARIABLES!$B$32)</f>
-        <v>4500.7849901325708</v>
+        <v>2827.1176038759554</v>
       </c>
       <c r="K23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$28,0,(IF($A23=VARIABLES!$B$28,0,K22)+H23)*(1+C23)-J23)</f>
-        <v>1120695.4625430102</v>
+        <v>994741.52262092545</v>
       </c>
       <c r="L23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$35,0,IF($A23=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="N23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$35,0,(IF($A23=VARIABLES!$B$35,0,O22)+L23)*C23*VARIABLES!$B$39)</f>
-        <v>40415.193228510667</v>
+        <v>23249.513248283823</v>
       </c>
       <c r="O23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$35,0,(IF($A23=VARIABLES!$B$35,0,O22)+L23)*(1+C23)-N23)</f>
-        <v>10063383.113899156</v>
+        <v>8180507.3043604372</v>
       </c>
       <c r="P23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$42,0,IF($A23=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7070,51 +7070,51 @@
       </c>
       <c r="R23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$42,0,(IF($A23=VARIABLES!$B$42,0,S22)+P23)*C23*VARIABLES!$B$46)</f>
-        <v>580.01861791906708</v>
+        <v>360.84574733448034</v>
       </c>
       <c r="S23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$42,0,(IF($A23=VARIABLES!$B$42,0,S22)+P23)*(1+C23)-R23)</f>
-        <v>579438.59930114797</v>
+        <v>508947.1519190463</v>
       </c>
       <c r="T23" s="44">
         <f>IF($A23&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A23-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U23" s="43">
         <f>T23*VARIABLES!$B$53+IF(AND($A23&gt;=VARIABLES!$B$50,MOD($A23-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A23-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="V23" s="43">
         <f>U23*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1050</v>
       </c>
       <c r="W23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$50,0,(IF($A23&lt;VARIABLES!$B$50+1,0,X22)+U23)*C23*VARIABLES!$B$55)</f>
-        <v>7305.8156380288392</v>
+        <v>6208.3110971682518</v>
       </c>
       <c r="X23" s="43">
         <f>IF($A23&lt;VARIABLES!$B$50,0,(IF($A23&lt;VARIABLES!$B$50+1,0,X22)+U23)*(1+C23)-W23)</f>
-        <v>1819148.0938691811</v>
+        <v>2184438.6046179147</v>
       </c>
       <c r="Y23" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>400000</v>
       </c>
       <c r="Z23" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AA23" s="43">
         <f t="shared" si="2"/>
-        <v>59711.913395939198</v>
+        <v>36875.367276836252</v>
       </c>
       <c r="AB23" s="35">
         <f t="shared" si="3"/>
-        <v>62111.913395939198</v>
+        <v>39875.367276836252</v>
       </c>
       <c r="AC23" s="36">
         <f t="shared" si="4"/>
-        <v>20485856.090039205</v>
+        <v>17834154.468526233</v>
       </c>
       <c r="AD23" s="43">
         <f>IF($A23=1,VARIABLES!$B$12,0)</f>
@@ -7142,19 +7142,19 @@
       </c>
       <c r="AJ23" s="38">
         <f>IF($A23&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK23" s="45">
         <f t="shared" si="6"/>
-        <v>-9471.4199373941337</v>
+        <v>-12554.632723163748</v>
       </c>
       <c r="AL23" s="45">
         <f t="shared" si="7"/>
-        <v>-605245.46313626354</v>
+        <v>-475996.12662230746</v>
       </c>
       <c r="AM23" s="40">
         <f t="shared" si="8"/>
-        <v>531666.66666666651</v>
+        <v>148600</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C24" s="33">
         <f>IF($A24&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$21,0,IF($A24=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7179,11 +7179,11 @@
       </c>
       <c r="F24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$21,0,(IF($A24=VARIABLES!$B$21,0,G23)+D24)*C24*VARIABLES!$B$25)</f>
-        <v>7399.157104611154</v>
+        <v>4495.6915828182673</v>
       </c>
       <c r="G24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$21,0,(IF($A24=VARIABLES!$B$21,0,G23)+D24)*(1+C24)-F24)</f>
-        <v>7391757.9475065432</v>
+        <v>6340851.8567378214</v>
       </c>
       <c r="H24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$28,0,IF($A24=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7195,11 +7195,11 @@
       </c>
       <c r="J24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$28,0,(IF($A24=VARIABLES!$B$28,0,K23)+H24)*C24*VARIABLES!$B$32)</f>
-        <v>4836.2310939292092</v>
+        <v>3017.9961076443656</v>
       </c>
       <c r="K24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$28,0,(IF($A24=VARIABLES!$B$28,0,K23)+H24)*(1+C24)-J24)</f>
-        <v>1204221.5423883733</v>
+        <v>1061903.4875897246</v>
       </c>
       <c r="L24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$35,0,IF($A24=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7211,11 +7211,11 @@
       </c>
       <c r="N24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$35,0,(IF($A24=VARIABLES!$B$35,0,O23)+L24)*C24*VARIABLES!$B$39)</f>
-        <v>41930.762974579819</v>
+        <v>23859.812971051273</v>
       </c>
       <c r="O24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$35,0,(IF($A24=VARIABLES!$B$35,0,O23)+L24)*(1+C24)-N24)</f>
-        <v>10440759.980670374</v>
+        <v>8395245.6210998967</v>
       </c>
       <c r="P24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$42,0,IF($A24=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7227,51 +7227,51 @@
       </c>
       <c r="R24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$42,0,(IF($A24=VARIABLES!$B$42,0,S23)+P24)*C24*VARIABLES!$B$46)</f>
-        <v>624.41520760536241</v>
+        <v>385.6906316076379</v>
       </c>
       <c r="S24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$42,0,(IF($A24=VARIABLES!$B$42,0,S23)+P24)*(1+C24)-R24)</f>
-        <v>623790.79239775718</v>
+        <v>543989.08655174414</v>
       </c>
       <c r="T24" s="34">
         <f>IF($A24&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A24-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U24" s="14">
         <f>T24*VARIABLES!$B$53+IF(AND($A24&gt;=VARIABLES!$B$50,MOD($A24-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A24-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>145000</v>
       </c>
       <c r="V24" s="14">
         <f>U24*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1087.5</v>
       </c>
       <c r="W24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$50,0,(IF($A24&lt;VARIABLES!$B$50+1,0,X23)+U24)*C24*VARIABLES!$B$55)</f>
-        <v>7829.7837244549219</v>
+        <v>6794.1959301355837</v>
       </c>
       <c r="X24" s="14">
         <f>IF($A24&lt;VARIABLES!$B$50,0,(IF($A24&lt;VARIABLES!$B$50+1,0,X23)+U24)*(1+C24)-W24)</f>
-        <v>1949616.1473892755</v>
+        <v>2390586.367989135</v>
       </c>
       <c r="Y24" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>405000</v>
       </c>
       <c r="Z24" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3037.5</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" si="2"/>
-        <v>62620.350105180471</v>
+        <v>38553.38722325713</v>
       </c>
       <c r="AB24" s="35">
         <f t="shared" si="3"/>
-        <v>65020.350105180471</v>
+        <v>41590.88722325713</v>
       </c>
       <c r="AC24" s="36">
         <f t="shared" si="4"/>
-        <v>21610146.410352319</v>
+        <v>18732576.419968322</v>
       </c>
       <c r="AD24" s="14">
         <f>IF($A24=1,VARIABLES!$B$12,0)</f>
@@ -7299,19 +7299,19 @@
       </c>
       <c r="AJ24" s="38">
         <f>IF($A24&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK24" s="39">
         <f t="shared" si="6"/>
-        <v>-6562.9832281528616</v>
+        <v>-10839.11277674287</v>
       </c>
       <c r="AL24" s="39">
         <f t="shared" si="7"/>
-        <v>-611808.44636441639</v>
+        <v>-486835.23939905036</v>
       </c>
       <c r="AM24" s="40">
         <f t="shared" si="8"/>
-        <v>558249.99999999988</v>
+        <v>156030</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.2">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="C25" s="42">
         <f>IF($A25&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$21,0,IF($A25=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7336,11 +7336,11 @@
       </c>
       <c r="F25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$21,0,(IF($A25=VARIABLES!$B$21,0,G24)+D25)*C25*VARIABLES!$B$25)</f>
-        <v>7908.0811953193161</v>
+        <v>4769.3711455379944</v>
       </c>
       <c r="G25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$21,0,(IF($A25=VARIABLES!$B$21,0,G24)+D25)*(1+C25)-F25)</f>
-        <v>7900173.1141239973</v>
+        <v>6726857.3314138027</v>
       </c>
       <c r="H25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$28,0,IF($A25=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7352,11 +7352,11 @@
       </c>
       <c r="J25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$28,0,(IF($A25=VARIABLES!$B$28,0,K24)+H25)*C25*VARIABLES!$B$32)</f>
-        <v>5184.2564266182226</v>
+        <v>3213.8851721366968</v>
       </c>
       <c r="K25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$28,0,(IF($A25=VARIABLES!$B$28,0,K24)+H25)*(1+C25)-J25)</f>
-        <v>1290879.8502279373</v>
+        <v>1130828.4541389549</v>
       </c>
       <c r="L25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$35,0,IF($A25=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7368,11 +7368,11 @@
       </c>
       <c r="N25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$35,0,(IF($A25=VARIABLES!$B$35,0,O24)+L25)*C25*VARIABLES!$B$39)</f>
-        <v>43503.166586126557</v>
+        <v>24486.133061541364</v>
       </c>
       <c r="O25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$35,0,(IF($A25=VARIABLES!$B$35,0,O24)+L25)*(1+C25)-N25)</f>
-        <v>10832288.479945512</v>
+        <v>8615620.8186537679</v>
       </c>
       <c r="P25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$42,0,IF($A25=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7384,51 +7384,51 @@
       </c>
       <c r="R25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$42,0,(IF($A25=VARIABLES!$B$42,0,S24)+P25)*C25*VARIABLES!$B$46)</f>
-        <v>670.61540874766376</v>
+        <v>411.24204227731343</v>
       </c>
       <c r="S25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$42,0,(IF($A25=VARIABLES!$B$42,0,S24)+P25)*(1+C25)-R25)</f>
-        <v>669944.79333891603</v>
+        <v>580027.52620055922</v>
       </c>
       <c r="T25" s="44">
         <f>IF($A25&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A25-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U25" s="43">
         <f>T25*VARIABLES!$B$53+IF(AND($A25&gt;=VARIABLES!$B$50,MOD($A25-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A25-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>150000</v>
       </c>
       <c r="V25" s="43">
         <f>U25*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1125</v>
       </c>
       <c r="W25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$50,0,(IF($A25&lt;VARIABLES!$B$50+1,0,X24)+U25)*C25*VARIABLES!$B$55)</f>
-        <v>8373.4006141219816</v>
+        <v>7410.0435733016438</v>
       </c>
       <c r="X25" s="43">
         <f>IF($A25&lt;VARIABLES!$B$50,0,(IF($A25&lt;VARIABLES!$B$50+1,0,X24)+U25)*(1+C25)-W25)</f>
-        <v>2084976.7529163735</v>
+        <v>2607276.7601488493</v>
       </c>
       <c r="Y25" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>410000</v>
       </c>
       <c r="Z25" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3075</v>
       </c>
       <c r="AA25" s="43">
         <f t="shared" si="2"/>
-        <v>65639.520230933747</v>
+        <v>40290.674994795008</v>
       </c>
       <c r="AB25" s="35">
         <f t="shared" si="3"/>
-        <v>68039.520230933747</v>
+        <v>43365.674994795008</v>
       </c>
       <c r="AC25" s="36">
         <f t="shared" si="4"/>
-        <v>22778262.990552738</v>
+        <v>19660610.890555933</v>
       </c>
       <c r="AD25" s="43">
         <f>IF($A25=1,VARIABLES!$B$12,0)</f>
@@ -7456,19 +7456,19 @@
       </c>
       <c r="AJ25" s="38">
         <f>IF($A25&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK25" s="45">
         <f t="shared" si="6"/>
-        <v>-3543.8131023995847</v>
+        <v>-9064.3250052049916</v>
       </c>
       <c r="AL25" s="45">
         <f t="shared" si="7"/>
-        <v>-615352.25946681597</v>
+        <v>-495899.56440425536</v>
       </c>
       <c r="AM25" s="40">
         <f t="shared" si="8"/>
-        <v>584833.33333333326</v>
+        <v>163460</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.2">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="C26" s="33">
         <f>IF($A26&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$21,0,IF($A26=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7493,11 +7493,11 @@
       </c>
       <c r="F26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$21,0,(IF($A26=VARIABLES!$B$21,0,G25)+D26)*C26*VARIABLES!$B$25)</f>
-        <v>8437.6803272124962</v>
+        <v>5050.8334708225639</v>
       </c>
       <c r="G26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$21,0,(IF($A26=VARIABLES!$B$21,0,G25)+D26)*(1+C26)-F26)</f>
-        <v>8429242.6468852852</v>
+        <v>7123839.8367758822</v>
       </c>
       <c r="H26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$28,0,IF($A26=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7509,11 +7509,11 @@
       </c>
       <c r="J26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$28,0,(IF($A26=VARIABLES!$B$28,0,K25)+H26)*C26*VARIABLES!$B$32)</f>
-        <v>5545.3327092830723</v>
+        <v>3414.9163245719519</v>
       </c>
       <c r="K26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$28,0,(IF($A26=VARIABLES!$B$28,0,K25)+H26)*(1+C26)-J26)</f>
-        <v>1380787.844611485</v>
+        <v>1201562.7010601023</v>
       </c>
       <c r="L26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$35,0,IF($A26=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7525,11 +7525,11 @@
       </c>
       <c r="N26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$35,0,(IF($A26=VARIABLES!$B$35,0,O25)+L26)*C26*VARIABLES!$B$39)</f>
-        <v>45134.535333106302</v>
+        <v>25128.894054406821</v>
       </c>
       <c r="O26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$35,0,(IF($A26=VARIABLES!$B$35,0,O25)+L26)*(1+C26)-N26)</f>
-        <v>11238499.297943469</v>
+        <v>8841780.8651434276</v>
       </c>
       <c r="P26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$42,0,IF($A26=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7541,51 +7541,51 @@
       </c>
       <c r="R26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$42,0,(IF($A26=VARIABLES!$B$42,0,S25)+P26)*C26*VARIABLES!$B$46)</f>
-        <v>718.6924930613709</v>
+        <v>437.52007118790772</v>
       </c>
       <c r="S26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$42,0,(IF($A26=VARIABLES!$B$42,0,S25)+P26)*(1+C26)-R26)</f>
-        <v>717973.8005683095</v>
+        <v>617090.80897688761</v>
       </c>
       <c r="T26" s="34">
         <f>IF($A26&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A26-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="U26" s="14">
         <f>T26*VARIABLES!$B$53+IF(AND($A26&gt;=VARIABLES!$B$50,MOD($A26-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A26-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>155000</v>
       </c>
       <c r="V26" s="14">
         <f>U26*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1162.5</v>
       </c>
       <c r="W26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$50,0,(IF($A26&lt;VARIABLES!$B$50+1,0,X25)+U26)*C26*VARIABLES!$B$55)</f>
-        <v>8937.4031371515557</v>
+        <v>8056.6405504341428</v>
       </c>
       <c r="X26" s="14">
         <f>IF($A26&lt;VARIABLES!$B$50,0,(IF($A26&lt;VARIABLES!$B$50+1,0,X25)+U26)*(1+C26)-W26)</f>
-        <v>2225413.3811507374</v>
+        <v>2834786.5251027565</v>
       </c>
       <c r="Y26" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>415000</v>
       </c>
       <c r="Z26" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3112.5</v>
       </c>
       <c r="AA26" s="14">
         <f t="shared" si="2"/>
-        <v>68773.643999814798</v>
+        <v>42088.804471423391</v>
       </c>
       <c r="AB26" s="35">
         <f t="shared" si="3"/>
-        <v>71173.643999814798</v>
+        <v>45201.304471423391</v>
       </c>
       <c r="AC26" s="36">
         <f t="shared" si="4"/>
-        <v>23991916.971159283</v>
+        <v>20619060.737059057</v>
       </c>
       <c r="AD26" s="14">
         <f>IF($A26=1,VARIABLES!$B$12,0)</f>
@@ -7613,19 +7613,19 @@
       </c>
       <c r="AJ26" s="38">
         <f>IF($A26&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK26" s="39">
         <f t="shared" si="6"/>
-        <v>-409.68933351853411</v>
+        <v>-7228.6955285766089</v>
       </c>
       <c r="AL26" s="39">
         <f t="shared" si="7"/>
-        <v>-615761.94880033447</v>
+        <v>-503128.25993283198</v>
       </c>
       <c r="AM26" s="40">
         <f t="shared" si="8"/>
-        <v>611416.66666666663</v>
+        <v>170890</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.2">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C27" s="42">
         <f>IF($A27&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$21,0,IF($A27=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7650,11 +7650,11 @@
       </c>
       <c r="F27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$21,0,(IF($A27=VARIABLES!$B$21,0,G26)+D27)*C27*VARIABLES!$B$25)</f>
-        <v>8988.7944238388391</v>
+        <v>5340.2998809824139</v>
       </c>
       <c r="G27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$21,0,(IF($A27=VARIABLES!$B$21,0,G26)+D27)*(1+C27)-F27)</f>
-        <v>8979805.6294149999</v>
+        <v>7532111.5321341958</v>
       </c>
       <c r="H27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$28,0,IF($A27=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7666,11 +7666,11 @@
       </c>
       <c r="J27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$28,0,(IF($A27=VARIABLES!$B$28,0,K26)+H27)*C27*VARIABLES!$B$32)</f>
-        <v>5919.9493525478538</v>
+        <v>3621.2245447586315</v>
       </c>
       <c r="K27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$28,0,(IF($A27=VARIABLES!$B$28,0,K26)+H27)*(1+C27)-J27)</f>
-        <v>1474067.388784416</v>
+        <v>1274153.7219629299</v>
       </c>
       <c r="L27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$35,0,IF($A27=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7682,11 +7682,11 @@
       </c>
       <c r="N27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$35,0,(IF($A27=VARIABLES!$B$35,0,O26)+L27)*C27*VARIABLES!$B$39)</f>
-        <v>46827.08040809779</v>
+        <v>25788.527523334997</v>
       </c>
       <c r="O27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$35,0,(IF($A27=VARIABLES!$B$35,0,O26)+L27)*(1+C27)-N27)</f>
-        <v>11659943.021616349</v>
+        <v>9073877.6128534414</v>
       </c>
       <c r="P27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$42,0,IF($A27=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7698,51 +7698,51 @@
       </c>
       <c r="R27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$42,0,(IF($A27=VARIABLES!$B$42,0,S26)+P27)*C27*VARIABLES!$B$46)</f>
-        <v>768.72270892532242</v>
+        <v>464.54538154564716</v>
       </c>
       <c r="S27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$42,0,(IF($A27=VARIABLES!$B$42,0,S26)+P27)*(1+C27)-R27)</f>
-        <v>767953.98621639702</v>
+        <v>655208.07885716774</v>
       </c>
       <c r="T27" s="44">
         <f>IF($A27&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A27-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="U27" s="43">
         <f>T27*VARIABLES!$B$53+IF(AND($A27&gt;=VARIABLES!$B$50,MOD($A27-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A27-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>160000</v>
       </c>
       <c r="V27" s="43">
         <f>U27*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="W27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$50,0,(IF($A27&lt;VARIABLES!$B$50+1,0,X26)+U27)*C27*VARIABLES!$B$55)</f>
-        <v>9522.5557547947392</v>
+        <v>8734.7940315497053</v>
       </c>
       <c r="X27" s="43">
         <f>IF($A27&lt;VARIABLES!$B$50,0,(IF($A27&lt;VARIABLES!$B$50+1,0,X26)+U27)*(1+C27)-W27)</f>
-        <v>2371116.3829438901</v>
+        <v>3073399.6713867034</v>
       </c>
       <c r="Y27" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>420000</v>
       </c>
       <c r="Z27" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3150</v>
       </c>
       <c r="AA27" s="43">
         <f t="shared" si="2"/>
-        <v>72027.102648204542</v>
+        <v>43949.391362171395</v>
       </c>
       <c r="AB27" s="35">
         <f t="shared" si="3"/>
-        <v>74427.102648204542</v>
+        <v>47099.391362171395</v>
       </c>
       <c r="AC27" s="36">
         <f t="shared" si="4"/>
-        <v>25252886.408976052</v>
+        <v>21608750.61719444</v>
       </c>
       <c r="AD27" s="43">
         <f>IF($A27=1,VARIABLES!$B$12,0)</f>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AF27" s="43">
         <f>IF(MOD($A27,12)=0,AC27*VARIABLES!$B$16,0)</f>
-        <v>63132.21602244013</v>
+        <v>54021.876542986101</v>
       </c>
       <c r="AG27" s="43">
         <f>VARIABLES!$B$17</f>
@@ -7766,23 +7766,23 @@
       </c>
       <c r="AI27" s="37">
         <f t="shared" si="5"/>
-        <v>111132.21602244013</v>
+        <v>102021.87654298611</v>
       </c>
       <c r="AJ27" s="38">
         <f>IF($A27&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK27" s="45">
         <f t="shared" si="6"/>
-        <v>-63288.446707568917</v>
+        <v>-62352.485180814714</v>
       </c>
       <c r="AL27" s="45">
         <f t="shared" si="7"/>
-        <v>-679050.39550790342</v>
+        <v>-565480.74511364673</v>
       </c>
       <c r="AM27" s="40">
         <f t="shared" si="8"/>
-        <v>638000</v>
+        <v>178320</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.2">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C28" s="33">
         <f>IF($A28&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$21,0,IF($A28=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7807,11 +7807,11 @@
       </c>
       <c r="F28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$21,0,(IF($A28=VARIABLES!$B$21,0,G27)+D28)*C28*VARIABLES!$B$25)</f>
-        <v>9562.2975306406242</v>
+        <v>5637.9979921811837</v>
       </c>
       <c r="G28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$21,0,(IF($A28=VARIABLES!$B$21,0,G27)+D28)*(1+C28)-F28)</f>
-        <v>9552735.2331099864</v>
+        <v>7951993.4538292615</v>
       </c>
       <c r="H28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$28,0,IF($A28=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7823,11 +7823,11 @@
       </c>
       <c r="J28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$28,0,(IF($A28=VARIABLES!$B$28,0,K27)+H28)*C28*VARIABLES!$B$32)</f>
-        <v>6308.6141199350668</v>
+        <v>3832.948355725212</v>
       </c>
       <c r="K28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$28,0,(IF($A28=VARIABLES!$B$28,0,K27)+H28)*(1+C28)-J28)</f>
-        <v>1570844.9158638318</v>
+        <v>1348650.2571644566</v>
       </c>
       <c r="L28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$35,0,IF($A28=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7839,11 +7839,11 @@
       </c>
       <c r="N28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$35,0,(IF($A28=VARIABLES!$B$35,0,O27)+L28)*C28*VARIABLES!$B$39)</f>
-        <v>48583.095923401452</v>
+        <v>26465.476370822536</v>
       </c>
       <c r="O28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$35,0,(IF($A28=VARIABLES!$B$35,0,O27)+L28)*(1+C28)-N28)</f>
-        <v>12097190.884926964</v>
+        <v>9312066.9001908433</v>
       </c>
       <c r="P28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$42,0,IF($A28=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7855,51 +7855,51 @@
       </c>
       <c r="R28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$42,0,(IF($A28=VARIABLES!$B$42,0,S27)+P28)*C28*VARIABLES!$B$46)</f>
-        <v>820.78540230874682</v>
+        <v>492.33922416668474</v>
       </c>
       <c r="S28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$42,0,(IF($A28=VARIABLES!$B$42,0,S27)+P28)*(1+C28)-R28)</f>
-        <v>819964.61690643814</v>
+        <v>694409.30859966832</v>
       </c>
       <c r="T28" s="34">
         <f>IF($A28&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A28-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="U28" s="14">
         <f>T28*VARIABLES!$B$53+IF(AND($A28&gt;=VARIABLES!$B$50,MOD($A28-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A28-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>165000</v>
       </c>
       <c r="V28" s="14">
         <f>U28*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1237.5</v>
       </c>
       <c r="W28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$50,0,(IF($A28&lt;VARIABLES!$B$50+1,0,X27)+U28)*C28*VARIABLES!$B$55)</f>
-        <v>10129.651595599542</v>
+        <v>9445.3323748778839</v>
       </c>
       <c r="X28" s="14">
         <f>IF($A28&lt;VARIABLES!$B$50,0,(IF($A28&lt;VARIABLES!$B$50+1,0,X27)+U28)*(1+C28)-W28)</f>
-        <v>2522283.2473042863</v>
+        <v>3323407.6627606042</v>
       </c>
       <c r="Y28" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>425000</v>
       </c>
       <c r="Z28" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3187.5</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" si="2"/>
-        <v>75404.444571885426</v>
+        <v>45874.09431777351</v>
       </c>
       <c r="AB28" s="35">
         <f t="shared" si="3"/>
-        <v>77804.444571885426</v>
+        <v>49061.59431777351</v>
       </c>
       <c r="AC28" s="36">
         <f t="shared" si="4"/>
-        <v>26563018.898111507</v>
+        <v>22630527.582544833</v>
       </c>
       <c r="AD28" s="14">
         <f>IF($A28=1,VARIABLES!$B$12,0)</f>
@@ -7927,19 +7927,19 @@
       </c>
       <c r="AJ28" s="38">
         <f>IF($A28&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK28" s="39">
         <f t="shared" si="6"/>
-        <v>6221.1112385520937</v>
+        <v>-3368.4056822264902</v>
       </c>
       <c r="AL28" s="39">
         <f t="shared" si="7"/>
-        <v>-672829.28426935128</v>
+        <v>-568849.15079587325</v>
       </c>
       <c r="AM28" s="40">
         <f t="shared" si="8"/>
-        <v>664583.33333333337</v>
+        <v>185750</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.2">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C29" s="42">
         <f>IF($A29&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$21,0,IF($A29=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7964,11 +7964,11 @@
       </c>
       <c r="F29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$21,0,(IF($A29=VARIABLES!$B$21,0,G28)+D29)*C29*VARIABLES!$B$25)</f>
-        <v>10159.099201156236</v>
+        <v>5944.1618934171693</v>
       </c>
       <c r="G29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$21,0,(IF($A29=VARIABLES!$B$21,0,G28)+D29)*(1+C29)-F29)</f>
-        <v>10148940.10195508</v>
+        <v>8383815.7676725304</v>
       </c>
       <c r="H29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$28,0,IF($A29=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7980,11 +7980,11 @@
       </c>
       <c r="J29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$28,0,(IF($A29=VARIABLES!$B$28,0,K28)+H29)*C29*VARIABLES!$B$32)</f>
-        <v>6711.8538160992994</v>
+        <v>4050.2299167296646</v>
       </c>
       <c r="K29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$28,0,(IF($A29=VARIABLES!$B$28,0,K28)+H29)*(1+C29)-J29)</f>
-        <v>1671251.6002087255</v>
+        <v>1425102.3264150235</v>
       </c>
       <c r="L29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$35,0,IF($A29=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7996,11 +7996,11 @@
       </c>
       <c r="N29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$35,0,(IF($A29=VARIABLES!$B$35,0,O28)+L29)*C29*VARIABLES!$B$39)</f>
-        <v>50404.962020529019</v>
+        <v>27160.195125556624</v>
       </c>
       <c r="O29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$35,0,(IF($A29=VARIABLES!$B$35,0,O28)+L29)*(1+C29)-N29)</f>
-        <v>12550835.543111725</v>
+        <v>9556508.6563208513</v>
       </c>
       <c r="P29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$42,0,IF($A29=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8012,51 +8012,51 @@
       </c>
       <c r="R29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$42,0,(IF($A29=VARIABLES!$B$42,0,S28)+P29)*C29*VARIABLES!$B$46)</f>
-        <v>874.96314261087309</v>
+        <v>520.92345418725813</v>
       </c>
       <c r="S29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$42,0,(IF($A29=VARIABLES!$B$42,0,S28)+P29)*(1+C29)-R29)</f>
-        <v>874088.17946826224</v>
+        <v>734725.32331297139</v>
       </c>
       <c r="T29" s="44">
         <f>IF($A29&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A29-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U29" s="43">
         <f>T29*VARIABLES!$B$53+IF(AND($A29&gt;=VARIABLES!$B$50,MOD($A29-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A29-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>170000</v>
       </c>
       <c r="V29" s="43">
         <f>U29*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1275</v>
       </c>
       <c r="W29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$50,0,(IF($A29&lt;VARIABLES!$B$50+1,0,X28)+U29)*C29*VARIABLES!$B$55)</f>
-        <v>10759.513530434526</v>
+        <v>10189.105683051763</v>
       </c>
       <c r="X29" s="43">
         <f>IF($A29&lt;VARIABLES!$B$50,0,(IF($A29&lt;VARIABLES!$B$50+1,0,X28)+U29)*(1+C29)-W29)</f>
-        <v>2679118.8690781971</v>
+        <v>3585109.6139080697</v>
       </c>
       <c r="Y29" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>430000</v>
       </c>
       <c r="Z29" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3225</v>
       </c>
       <c r="AA29" s="43">
         <f t="shared" si="2"/>
-        <v>78910.39171082995</v>
+        <v>47864.616072942474</v>
       </c>
       <c r="AB29" s="35">
         <f t="shared" si="3"/>
-        <v>81310.39171082995</v>
+        <v>51089.616072942474</v>
       </c>
       <c r="AC29" s="36">
         <f t="shared" si="4"/>
-        <v>27924234.29382199</v>
+        <v>23685261.687629446</v>
       </c>
       <c r="AD29" s="43">
         <f>IF($A29=1,VARIABLES!$B$12,0)</f>
@@ -8084,19 +8084,19 @@
       </c>
       <c r="AJ29" s="38">
         <f>IF($A29&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK29" s="45">
         <f t="shared" si="6"/>
-        <v>9727.058377496618</v>
+        <v>-1340.3839270575263</v>
       </c>
       <c r="AL29" s="45">
         <f t="shared" si="7"/>
-        <v>-663102.22589185461</v>
+        <v>-570189.53472293075</v>
       </c>
       <c r="AM29" s="40">
         <f t="shared" si="8"/>
-        <v>691166.66666666674</v>
+        <v>193180</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.2">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C30" s="33">
         <f>IF($A30&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$21,0,IF($A30=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="F30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$21,0,(IF($A30=VARIABLES!$B$21,0,G29)+D30)*C30*VARIABLES!$B$25)</f>
-        <v>10780.145939536542</v>
+        <v>6259.032330594554</v>
       </c>
       <c r="G30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$21,0,(IF($A30=VARIABLES!$B$21,0,G29)+D30)*(1+C30)-F30)</f>
-        <v>10769365.793597007</v>
+        <v>8827918.0285657179</v>
       </c>
       <c r="H30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$28,0,IF($A30=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8137,11 +8137,11 @@
       </c>
       <c r="J30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$28,0,(IF($A30=VARIABLES!$B$28,0,K29)+H30)*C30*VARIABLES!$B$32)</f>
-        <v>7130.215000869689</v>
+        <v>4273.2151187104855</v>
       </c>
       <c r="K30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$28,0,(IF($A30=VARIABLES!$B$28,0,K29)+H30)*(1+C30)-J30)</f>
-        <v>1775423.5352165529</v>
+        <v>1503561.2624834178</v>
       </c>
       <c r="L30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$35,0,IF($A30=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="N30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$35,0,(IF($A30=VARIABLES!$B$35,0,O29)+L30)*C30*VARIABLES!$B$39)</f>
-        <v>52295.148096298857</v>
+        <v>27873.15024760248</v>
       </c>
       <c r="O30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$35,0,(IF($A30=VARIABLES!$B$35,0,O29)+L30)*(1+C30)-N30)</f>
-        <v>13021491.875978416</v>
+        <v>9807367.008549273</v>
       </c>
       <c r="P30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$42,0,IF($A30=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8169,51 +8169,51 @@
       </c>
       <c r="R30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$42,0,(IF($A30=VARIABLES!$B$42,0,S29)+P30)*C30*VARIABLES!$B$46)</f>
-        <v>931.34185361277309</v>
+        <v>550.32054824904162</v>
       </c>
       <c r="S30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$42,0,(IF($A30=VARIABLES!$B$42,0,S29)+P30)*(1+C30)-R30)</f>
-        <v>930410.51175916044</v>
+        <v>776187.82469468389</v>
       </c>
       <c r="T30" s="34">
         <f>IF($A30&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A30-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="U30" s="14">
         <f>T30*VARIABLES!$B$53+IF(AND($A30&gt;=VARIABLES!$B$50,MOD($A30-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A30-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>175000</v>
       </c>
       <c r="V30" s="14">
         <f>U30*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1312.5</v>
       </c>
       <c r="W30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$50,0,(IF($A30&lt;VARIABLES!$B$50+1,0,X29)+U30)*C30*VARIABLES!$B$55)</f>
-        <v>11412.995287825821</v>
+        <v>10966.986373898537</v>
       </c>
       <c r="X30" s="14">
         <f>IF($A30&lt;VARIABLES!$B$50,0,(IF($A30&lt;VARIABLES!$B$50+1,0,X29)+U30)*(1+C30)-W30)</f>
-        <v>2841835.8266686294</v>
+        <v>3858812.4912731559</v>
       </c>
       <c r="Y30" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>435000</v>
       </c>
       <c r="Z30" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3262.5</v>
       </c>
       <c r="AA30" s="14">
         <f t="shared" si="2"/>
-        <v>82549.846178143678</v>
+        <v>49922.704619055097</v>
       </c>
       <c r="AB30" s="35">
         <f t="shared" si="3"/>
-        <v>84949.846178143678</v>
+        <v>53185.204619055097</v>
       </c>
       <c r="AC30" s="36">
         <f t="shared" si="4"/>
-        <v>29338527.543219768</v>
+        <v>24773846.615566254</v>
       </c>
       <c r="AD30" s="14">
         <f>IF($A30=1,VARIABLES!$B$12,0)</f>
@@ -8241,19 +8241,19 @@
       </c>
       <c r="AJ30" s="38">
         <f>IF($A30&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK30" s="39">
         <f t="shared" si="6"/>
-        <v>13366.512844810346</v>
+        <v>755.20461905509728</v>
       </c>
       <c r="AL30" s="39">
         <f t="shared" si="7"/>
-        <v>-649735.71304704424</v>
+        <v>-569434.3301038756</v>
       </c>
       <c r="AM30" s="40">
         <f t="shared" si="8"/>
-        <v>717750.00000000012</v>
+        <v>200610</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.2">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="C31" s="42">
         <f>IF($A31&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$21,0,IF($A31=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8278,11 +8278,11 @@
       </c>
       <c r="F31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$21,0,(IF($A31=VARIABLES!$B$21,0,G30)+D31)*C31*VARIABLES!$B$25)</f>
-        <v>11426.422701663549</v>
+        <v>6582.8568958291689</v>
       </c>
       <c r="G31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$21,0,(IF($A31=VARIABLES!$B$21,0,G30)+D31)*(1+C31)-F31)</f>
-        <v>11414996.278961886</v>
+        <v>9284649.4475030545</v>
       </c>
       <c r="H31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$28,0,IF($A31=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8294,11 +8294,11 @@
       </c>
       <c r="J31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$28,0,(IF($A31=VARIABLES!$B$28,0,K30)+H31)*C31*VARIABLES!$B$32)</f>
-        <v>7564.2647300689705</v>
+        <v>4502.0536822433014</v>
       </c>
       <c r="K31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$28,0,(IF($A31=VARIABLES!$B$28,0,K30)+H31)*(1+C31)-J31)</f>
-        <v>1883501.917787174</v>
+        <v>1584079.7456236074</v>
       </c>
       <c r="L31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$35,0,IF($A31=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8310,11 +8310,11 @@
       </c>
       <c r="N31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$35,0,(IF($A31=VARIABLES!$B$35,0,O30)+L31)*C31*VARIABLES!$B$39)</f>
-        <v>54256.216149910062</v>
+        <v>28604.820441602045</v>
       </c>
       <c r="O31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$35,0,(IF($A31=VARIABLES!$B$35,0,O30)+L31)*(1+C31)-N31)</f>
-        <v>13509797.821327608</v>
+        <v>10064810.392523691</v>
       </c>
       <c r="P31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$42,0,IF($A31=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8326,51 +8326,51 @@
       </c>
       <c r="R31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$42,0,(IF($A31=VARIABLES!$B$42,0,S30)+P31)*C31*VARIABLES!$B$46)</f>
-        <v>990.01094974912542</v>
+        <v>580.55362217320703</v>
       </c>
       <c r="S31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$42,0,(IF($A31=VARIABLES!$B$42,0,S30)+P31)*(1+C31)-R31)</f>
-        <v>989020.93879937637</v>
+        <v>818829.41595943877</v>
       </c>
       <c r="T31" s="44">
         <f>IF($A31&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A31-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="U31" s="43">
         <f>T31*VARIABLES!$B$53+IF(AND($A31&gt;=VARIABLES!$B$50,MOD($A31-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A31-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="V31" s="43">
         <f>U31*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1350</v>
       </c>
       <c r="W31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$50,0,(IF($A31&lt;VARIABLES!$B$50+1,0,X30)+U31)*C31*VARIABLES!$B$55)</f>
-        <v>12090.982611119289</v>
+        <v>11779.869766213371</v>
       </c>
       <c r="X31" s="43">
         <f>IF($A31&lt;VARIABLES!$B$50,0,(IF($A31&lt;VARIABLES!$B$50+1,0,X30)+U31)*(1+C31)-W31)</f>
-        <v>3010654.6701687034</v>
+        <v>4144831.3191690757</v>
       </c>
       <c r="Y31" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>440000</v>
       </c>
       <c r="Z31" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3300</v>
       </c>
       <c r="AA31" s="43">
         <f t="shared" si="2"/>
-        <v>86327.897142510978</v>
+        <v>52050.154408061091</v>
       </c>
       <c r="AB31" s="35">
         <f t="shared" si="3"/>
-        <v>88727.897142510978</v>
+        <v>55350.154408061091</v>
       </c>
       <c r="AC31" s="36">
         <f t="shared" si="4"/>
-        <v>30807971.627044745</v>
+        <v>25897200.320778869</v>
       </c>
       <c r="AD31" s="43">
         <f>IF($A31=1,VARIABLES!$B$12,0)</f>
@@ -8398,19 +8398,19 @@
       </c>
       <c r="AJ31" s="38">
         <f>IF($A31&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK31" s="45">
         <f t="shared" si="6"/>
-        <v>17144.563809177645</v>
+        <v>2920.1544080610911</v>
       </c>
       <c r="AL31" s="45">
         <f t="shared" si="7"/>
-        <v>-632591.14923786663</v>
+        <v>-566514.17569581454</v>
       </c>
       <c r="AM31" s="40">
         <f t="shared" si="8"/>
-        <v>744333.33333333349</v>
+        <v>208040</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.2">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C32" s="33">
         <f>IF($A32&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$21,0,IF($A32=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8435,11 +8435,11 @@
       </c>
       <c r="F32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$21,0,(IF($A32=VARIABLES!$B$21,0,G31)+D32)*C32*VARIABLES!$B$25)</f>
-        <v>12098.954457251964</v>
+        <v>6915.8902221376429</v>
       </c>
       <c r="G32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$21,0,(IF($A32=VARIABLES!$B$21,0,G31)+D32)*(1+C32)-F32)</f>
-        <v>12086855.502794715</v>
+        <v>9754369.166166421</v>
       </c>
       <c r="H32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$28,0,IF($A32=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8451,11 +8451,11 @@
       </c>
       <c r="J32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$28,0,(IF($A32=VARIABLES!$B$28,0,K31)+H32)*C32*VARIABLES!$B$32)</f>
-        <v>8014.5913241132257</v>
+        <v>4736.8992580688546</v>
       </c>
       <c r="K32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$28,0,(IF($A32=VARIABLES!$B$28,0,K31)+H32)*(1+C32)-J32)</f>
-        <v>1995633.2397041931</v>
+        <v>1666711.838946227</v>
       </c>
       <c r="L32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$35,0,IF($A32=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8467,11 +8467,11 @@
       </c>
       <c r="N32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$35,0,(IF($A32=VARIABLES!$B$35,0,O31)+L32)*C32*VARIABLES!$B$39)</f>
-        <v>56290.824255531705</v>
+        <v>29355.696978194101</v>
       </c>
       <c r="O32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$35,0,(IF($A32=VARIABLES!$B$35,0,O31)+L32)*(1+C32)-N32)</f>
-        <v>14016415.239627395</v>
+        <v>10329011.665327437</v>
       </c>
       <c r="P32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$42,0,IF($A32=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8483,51 +8483,51 @@
       </c>
       <c r="R32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$42,0,(IF($A32=VARIABLES!$B$42,0,S31)+P32)*C32*VARIABLES!$B$46)</f>
-        <v>1051.0634779160171</v>
+        <v>611.64644913709071</v>
       </c>
       <c r="S32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$42,0,(IF($A32=VARIABLES!$B$42,0,S31)+P32)*(1+C32)-R32)</f>
-        <v>1050012.4144381012</v>
+        <v>862683.62747578521</v>
       </c>
       <c r="T32" s="34">
         <f>IF($A32&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A32-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="U32" s="14">
         <f>T32*VARIABLES!$B$53+IF(AND($A32&gt;=VARIABLES!$B$50,MOD($A32-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A32-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>185000</v>
       </c>
       <c r="V32" s="14">
         <f>U32*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1387.5</v>
       </c>
       <c r="W32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$50,0,(IF($A32&lt;VARIABLES!$B$50+1,0,X31)+U32)*C32*VARIABLES!$B$55)</f>
-        <v>12794.394459036264</v>
+        <v>12628.674680909804</v>
       </c>
       <c r="X32" s="14">
         <f>IF($A32&lt;VARIABLES!$B$50,0,(IF($A32&lt;VARIABLES!$B$50+1,0,X31)+U32)*(1+C32)-W32)</f>
-        <v>3185804.22030003</v>
+        <v>4443489.391297264</v>
       </c>
       <c r="Y32" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>445000</v>
       </c>
       <c r="Z32" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3337.5</v>
       </c>
       <c r="AA32" s="14">
         <f t="shared" si="2"/>
-        <v>90249.827973849184</v>
+        <v>54248.807588447497</v>
       </c>
       <c r="AB32" s="35">
         <f t="shared" si="3"/>
-        <v>92649.827973849184</v>
+        <v>57586.307588447497</v>
       </c>
       <c r="AC32" s="36">
         <f t="shared" si="4"/>
-        <v>32334720.616864435</v>
+        <v>27056265.689213134</v>
       </c>
       <c r="AD32" s="14">
         <f>IF($A32=1,VARIABLES!$B$12,0)</f>
@@ -8555,19 +8555,19 @@
       </c>
       <c r="AJ32" s="38">
         <f>IF($A32&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK32" s="39">
         <f t="shared" si="6"/>
-        <v>21066.494640515852</v>
+        <v>5156.3075884474965</v>
       </c>
       <c r="AL32" s="39">
         <f t="shared" si="7"/>
-        <v>-611524.65459735075</v>
+        <v>-561357.86810736707</v>
       </c>
       <c r="AM32" s="40">
         <f t="shared" si="8"/>
-        <v>770916.66666666686</v>
+        <v>215470</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C33" s="42">
         <f>IF($A33&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$21,0,IF($A33=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8592,11 +8592,11 @@
       </c>
       <c r="F33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$21,0,(IF($A33=VARIABLES!$B$21,0,G32)+D33)*C33*VARIABLES!$B$25)</f>
-        <v>12798.807815411161</v>
+        <v>7258.3941836630147</v>
       </c>
       <c r="G33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$21,0,(IF($A33=VARIABLES!$B$21,0,G32)+D33)*(1+C33)-F33)</f>
-        <v>12786009.00759575</v>
+        <v>10237446.539329277</v>
       </c>
       <c r="H33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$28,0,IF($A33=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8608,11 +8608,11 @@
       </c>
       <c r="J33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$28,0,(IF($A33=VARIABLES!$B$28,0,K32)+H33)*C33*VARIABLES!$B$32)</f>
-        <v>8481.805165434138</v>
+        <v>4977.9095302598289</v>
       </c>
       <c r="K33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$28,0,(IF($A33=VARIABLES!$B$28,0,K32)+H33)*(1+C33)-J33)</f>
-        <v>2111969.4861931005</v>
+        <v>1751513.0247185652</v>
       </c>
       <c r="L33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$35,0,IF($A33=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8624,11 +8624,11 @@
       </c>
       <c r="N33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$35,0,(IF($A33=VARIABLES!$B$35,0,O32)+L33)*C33*VARIABLES!$B$39)</f>
-        <v>58401.730165114139</v>
+        <v>30126.284023871689</v>
       </c>
       <c r="O33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$35,0,(IF($A33=VARIABLES!$B$35,0,O32)+L33)*(1+C33)-N33)</f>
-        <v>14542030.811113423</v>
+        <v>10600148.221542282</v>
       </c>
       <c r="P33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$42,0,IF($A33=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8640,51 +8640,51 @@
       </c>
       <c r="R33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$42,0,(IF($A33=VARIABLES!$B$42,0,S32)+P33)*C33*VARIABLES!$B$46)</f>
-        <v>1114.5962650396887</v>
+        <v>643.62347836776007</v>
       </c>
       <c r="S33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$42,0,(IF($A33=VARIABLES!$B$42,0,S32)+P33)*(1+C33)-R33)</f>
-        <v>1113481.6687746493</v>
+        <v>907784.94313212775</v>
       </c>
       <c r="T33" s="44">
         <f>IF($A33&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A33-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="U33" s="43">
         <f>T33*VARIABLES!$B$53+IF(AND($A33&gt;=VARIABLES!$B$50,MOD($A33-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A33-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>190000</v>
       </c>
       <c r="V33" s="43">
         <f>U33*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1425</v>
       </c>
       <c r="W33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$50,0,(IF($A33&lt;VARIABLES!$B$50+1,0,X32)+U33)*C33*VARIABLES!$B$55)</f>
-        <v>13524.184251250124</v>
+        <v>13514.344057950351</v>
       </c>
       <c r="X33" s="43">
         <f>IF($A33&lt;VARIABLES!$B$50,0,(IF($A33&lt;VARIABLES!$B$50+1,0,X32)+U33)*(1+C33)-W33)</f>
-        <v>3367521.8785612811</v>
+        <v>4755118.4878188167</v>
       </c>
       <c r="Y33" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>450000</v>
       </c>
       <c r="Z33" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3375</v>
       </c>
       <c r="AA33" s="43">
         <f t="shared" si="2"/>
-        <v>94321.123662249243</v>
+        <v>56520.555274112638</v>
       </c>
       <c r="AB33" s="35">
         <f t="shared" si="3"/>
-        <v>96721.123662249243</v>
+        <v>59895.555274112638</v>
       </c>
       <c r="AC33" s="36">
         <f t="shared" si="4"/>
-        <v>33921012.852238201</v>
+        <v>28252011.216541074</v>
       </c>
       <c r="AD33" s="43">
         <f>IF($A33=1,VARIABLES!$B$12,0)</f>
@@ -8712,19 +8712,19 @@
       </c>
       <c r="AJ33" s="38">
         <f>IF($A33&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK33" s="45">
         <f t="shared" si="6"/>
-        <v>25137.790328915911</v>
+        <v>7465.5552741126376</v>
       </c>
       <c r="AL33" s="45">
         <f t="shared" si="7"/>
-        <v>-586386.86426843482</v>
+        <v>-553892.31283325446</v>
       </c>
       <c r="AM33" s="40">
         <f t="shared" si="8"/>
-        <v>797500.00000000023</v>
+        <v>222900</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="C34" s="33">
         <f>IF($A34&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$21,0,IF($A34=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8749,11 +8749,11 @@
       </c>
       <c r="F34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$21,0,(IF($A34=VARIABLES!$B$21,0,G33)+D34)*C34*VARIABLES!$B$25)</f>
-        <v>13527.092716245572</v>
+        <v>7610.6381015942643</v>
       </c>
       <c r="G34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$21,0,(IF($A34=VARIABLES!$B$21,0,G33)+D34)*(1+C34)-F34)</f>
-        <v>13513565.623529328</v>
+        <v>10734261.425291453</v>
       </c>
       <c r="H34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$28,0,IF($A34=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8765,11 +8765,11 @@
       </c>
       <c r="J34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$28,0,(IF($A34=VARIABLES!$B$28,0,K33)+H34)*C34*VARIABLES!$B$32)</f>
-        <v>8966.5395258045846</v>
+        <v>5225.2463220958152</v>
       </c>
       <c r="K34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$28,0,(IF($A34=VARIABLES!$B$28,0,K33)+H34)*(1+C34)-J34)</f>
-        <v>2232668.3419253421</v>
+        <v>1838540.2416174272</v>
       </c>
       <c r="L34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$35,0,IF($A34=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8781,11 +8781,11 @@
       </c>
       <c r="N34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$35,0,(IF($A34=VARIABLES!$B$35,0,O33)+L34)*C34*VARIABLES!$B$39)</f>
-        <v>60591.795046305924</v>
+        <v>30917.098979498318</v>
       </c>
       <c r="O34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$35,0,(IF($A34=VARIABLES!$B$35,0,O33)+L34)*(1+C34)-N34)</f>
-        <v>15087356.966530178</v>
+        <v>10878402.112357765</v>
       </c>
       <c r="P34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$42,0,IF($A34=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8797,51 +8797,51 @@
       </c>
       <c r="R34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$42,0,(IF($A34=VARIABLES!$B$42,0,S33)+P34)*C34*VARIABLES!$B$46)</f>
-        <v>1180.7100716402597</v>
+        <v>676.50985436717644</v>
       </c>
       <c r="S34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$42,0,(IF($A34=VARIABLES!$B$42,0,S33)+P34)*(1+C34)-R34)</f>
-        <v>1179529.3615686195</v>
+        <v>954168.82745244761</v>
       </c>
       <c r="T34" s="34">
         <f>IF($A34&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A34-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="U34" s="14">
         <f>T34*VARIABLES!$B$53+IF(AND($A34&gt;=VARIABLES!$B$50,MOD($A34-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A34-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>195000</v>
       </c>
       <c r="V34" s="14">
         <f>U34*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1462.5</v>
       </c>
       <c r="W34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$50,0,(IF($A34&lt;VARIABLES!$B$50+1,0,X33)+U34)*C34*VARIABLES!$B$55)</f>
-        <v>14281.341160672004</v>
+        <v>14437.845589471548</v>
       </c>
       <c r="X34" s="14">
         <f>IF($A34&lt;VARIABLES!$B$50,0,(IF($A34&lt;VARIABLES!$B$50+1,0,X33)+U34)*(1+C34)-W34)</f>
-        <v>3556053.9490073295</v>
+        <v>5080059.0981240598</v>
       </c>
       <c r="Y34" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>455000</v>
       </c>
       <c r="Z34" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3412.5</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" si="2"/>
-        <v>98547.478520668345</v>
+        <v>58867.338847027117</v>
       </c>
       <c r="AB34" s="35">
         <f t="shared" si="3"/>
-        <v>100947.47852066834</v>
+        <v>62279.838847027117</v>
       </c>
       <c r="AC34" s="36">
         <f t="shared" si="4"/>
-        <v>35569174.242560796</v>
+        <v>29485431.704843152</v>
       </c>
       <c r="AD34" s="14">
         <f>IF($A34=1,VARIABLES!$B$12,0)</f>
@@ -8869,19 +8869,19 @@
       </c>
       <c r="AJ34" s="38">
         <f>IF($A34&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK34" s="39">
         <f t="shared" si="6"/>
-        <v>29364.145187335012</v>
+        <v>9849.8388470271166</v>
       </c>
       <c r="AL34" s="39">
         <f t="shared" si="7"/>
-        <v>-557022.71908109984</v>
+        <v>-544042.4739862273</v>
       </c>
       <c r="AM34" s="40">
         <f t="shared" si="8"/>
-        <v>824083.3333333336</v>
+        <v>230330</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.2">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="C35" s="42">
         <f>IF($A35&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$21,0,IF($A35=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8906,11 +8906,11 @@
       </c>
       <c r="F35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$21,0,(IF($A35=VARIABLES!$B$21,0,G34)+D35)*C35*VARIABLES!$B$25)</f>
-        <v>14284.964191176383</v>
+        <v>7972.8989559416841</v>
       </c>
       <c r="G35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$21,0,(IF($A35=VARIABLES!$B$21,0,G34)+D35)*(1+C35)-F35)</f>
-        <v>14270679.226985209</v>
+        <v>11245204.484573178</v>
       </c>
       <c r="H35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$28,0,IF($A35=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8922,11 +8922,11 @@
       </c>
       <c r="J35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$28,0,(IF($A35=VARIABLES!$B$28,0,K34)+H35)*C35*VARIABLES!$B$32)</f>
-        <v>9469.4514246889248</v>
+        <v>5479.0757047174957</v>
       </c>
       <c r="K35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$28,0,(IF($A35=VARIABLES!$B$28,0,K34)+H35)*(1+C35)-J35)</f>
-        <v>2357893.4047475425</v>
+        <v>1927851.9229598844</v>
       </c>
       <c r="L35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$35,0,IF($A35=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8938,11 +8938,11 @@
       </c>
       <c r="N35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$35,0,(IF($A35=VARIABLES!$B$35,0,O34)+L35)*C35*VARIABLES!$B$39)</f>
-        <v>62863.987360542407</v>
+        <v>31728.67282771015</v>
       </c>
       <c r="O35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$35,0,(IF($A35=VARIABLES!$B$35,0,O34)+L35)*(1+C35)-N35)</f>
-        <v>15653132.85277506</v>
+        <v>11163960.167807156</v>
       </c>
       <c r="P35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$42,0,IF($A35=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8954,51 +8954,51 @@
       </c>
       <c r="R35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$42,0,(IF($A35=VARIABLES!$B$42,0,S34)+P35)*C35*VARIABLES!$B$46)</f>
-        <v>1249.5097516339786</v>
+        <v>710.33143668407638</v>
       </c>
       <c r="S35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$42,0,(IF($A35=VARIABLES!$B$42,0,S34)+P35)*(1+C35)-R35)</f>
-        <v>1248260.2418823447</v>
+        <v>1001871.7534831264</v>
       </c>
       <c r="T35" s="44">
         <f>IF($A35&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A35-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="U35" s="43">
         <f>T35*VARIABLES!$B$53+IF(AND($A35&gt;=VARIABLES!$B$50,MOD($A35-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A35-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>200000</v>
       </c>
       <c r="V35" s="43">
         <f>U35*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1500</v>
       </c>
       <c r="W35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$50,0,(IF($A35&lt;VARIABLES!$B$50+1,0,X34)+U35)*C35*VARIABLES!$B$55)</f>
-        <v>15066.891454197204</v>
+        <v>15400.172369528507</v>
       </c>
       <c r="X35" s="43">
         <f>IF($A35&lt;VARIABLES!$B$50,0,(IF($A35&lt;VARIABLES!$B$50+1,0,X34)+U35)*(1+C35)-W35)</f>
-        <v>3751655.9720951049</v>
+        <v>5418660.649449816</v>
       </c>
       <c r="Y35" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>460000</v>
       </c>
       <c r="Z35" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3450</v>
       </c>
       <c r="AA35" s="43">
         <f t="shared" si="2"/>
-        <v>102934.80418223889</v>
+        <v>61291.151294581912</v>
       </c>
       <c r="AB35" s="35">
         <f t="shared" si="3"/>
-        <v>105334.80418223889</v>
+        <v>64741.151294581912</v>
       </c>
       <c r="AC35" s="36">
         <f t="shared" si="4"/>
-        <v>37281621.698485255</v>
+        <v>30757548.978273161</v>
       </c>
       <c r="AD35" s="43">
         <f>IF($A35=1,VARIABLES!$B$12,0)</f>
@@ -9026,19 +9026,19 @@
       </c>
       <c r="AJ35" s="38">
         <f>IF($A35&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK35" s="45">
         <f t="shared" si="6"/>
-        <v>33751.470848905563</v>
+        <v>12311.151294581912</v>
       </c>
       <c r="AL35" s="45">
         <f t="shared" si="7"/>
-        <v>-523271.24823219428</v>
+        <v>-531731.32269164536</v>
       </c>
       <c r="AM35" s="40">
         <f t="shared" si="8"/>
-        <v>850666.66666666698</v>
+        <v>237760</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.2">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C36" s="33">
         <f>IF($A36&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$21,0,IF($A36=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9063,11 +9063,11 @@
       </c>
       <c r="F36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$21,0,(IF($A36=VARIABLES!$B$21,0,G35)+D36)*C36*VARIABLES!$B$25)</f>
-        <v>15073.624194776259</v>
+        <v>8345.4616033346083</v>
       </c>
       <c r="G36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$21,0,(IF($A36=VARIABLES!$B$21,0,G35)+D36)*(1+C36)-F36)</f>
-        <v>15058550.570581483</v>
+        <v>11770677.487103228</v>
       </c>
       <c r="H36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$28,0,IF($A36=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9079,11 +9079,11 @@
       </c>
       <c r="J36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$28,0,(IF($A36=VARIABLES!$B$28,0,K35)+H36)*C36*VARIABLES!$B$32)</f>
-        <v>9991.2225197814259</v>
+        <v>5739.568108632996</v>
       </c>
       <c r="K36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$28,0,(IF($A36=VARIABLES!$B$28,0,K35)+H36)*(1+C36)-J36)</f>
-        <v>2487814.4074255754</v>
+        <v>2019508.0359375812</v>
       </c>
       <c r="L36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$35,0,IF($A36=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9095,11 +9095,11 @@
       </c>
       <c r="N36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$35,0,(IF($A36=VARIABLES!$B$35,0,O35)+L36)*C36*VARIABLES!$B$39)</f>
-        <v>65221.386886562745</v>
+        <v>32561.550489437534</v>
       </c>
       <c r="O36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$35,0,(IF($A36=VARIABLES!$B$35,0,O35)+L36)*(1+C36)-N36)</f>
-        <v>16240125.334754124</v>
+        <v>11457014.122212093</v>
       </c>
       <c r="P36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$42,0,IF($A36=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9111,51 +9111,51 @@
       </c>
       <c r="R36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$42,0,(IF($A36=VARIABLES!$B$42,0,S35)+P36)*C36*VARIABLES!$B$46)</f>
-        <v>1321.1044186274423</v>
+        <v>745.11482024811301</v>
       </c>
       <c r="S36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$42,0,(IF($A36=VARIABLES!$B$42,0,S35)+P36)*(1+C36)-R36)</f>
-        <v>1319783.3142088151</v>
+        <v>1050931.2314728026</v>
       </c>
       <c r="T36" s="34">
         <f>IF($A36&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A36-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="U36" s="14">
         <f>T36*VARIABLES!$B$53+IF(AND($A36&gt;=VARIABLES!$B$50,MOD($A36-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A36-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>205000</v>
       </c>
       <c r="V36" s="14">
         <f>U36*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1537.5</v>
       </c>
       <c r="W36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$50,0,(IF($A36&lt;VARIABLES!$B$50+1,0,X35)+U36)*C36*VARIABLES!$B$55)</f>
-        <v>15881.899883729604</v>
+        <v>16402.343560895297</v>
       </c>
       <c r="X36" s="14">
         <f>IF($A36&lt;VARIABLES!$B$50,0,(IF($A36&lt;VARIABLES!$B$50+1,0,X35)+U36)*(1+C36)-W36)</f>
-        <v>3954593.0710486718</v>
+        <v>5771281.7414978733</v>
       </c>
       <c r="Y36" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>465000</v>
       </c>
       <c r="Z36" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3487.5</v>
       </c>
       <c r="AA36" s="14">
         <f t="shared" si="2"/>
-        <v>107489.23790347748</v>
+        <v>63794.038582548543</v>
       </c>
       <c r="AB36" s="35">
         <f t="shared" si="3"/>
-        <v>109889.23790347748</v>
+        <v>67281.538582548543</v>
       </c>
       <c r="AC36" s="36">
         <f t="shared" si="4"/>
-        <v>39060866.69801867</v>
+        <v>32069412.618223578</v>
       </c>
       <c r="AD36" s="14">
         <f>IF($A36=1,VARIABLES!$B$12,0)</f>
@@ -9183,19 +9183,19 @@
       </c>
       <c r="AJ36" s="38">
         <f>IF($A36&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK36" s="39">
         <f t="shared" si="6"/>
-        <v>38305.90457014415</v>
+        <v>14851.538582548543</v>
       </c>
       <c r="AL36" s="39">
         <f t="shared" si="7"/>
-        <v>-484965.34366205015</v>
+        <v>-516879.7841090968</v>
       </c>
       <c r="AM36" s="40">
         <f t="shared" si="8"/>
-        <v>877250.00000000035</v>
+        <v>245190</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.2">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="C37" s="42">
         <f>IF($A37&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$21,0,IF($A37=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="F37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$21,0,(IF($A37=VARIABLES!$B$21,0,G36)+D37)*C37*VARIABLES!$B$25)</f>
-        <v>15894.323511022376</v>
+        <v>8728.6190010127702</v>
       </c>
       <c r="G37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$21,0,(IF($A37=VARIABLES!$B$21,0,G36)+D37)*(1+C37)-F37)</f>
-        <v>15878429.187511357</v>
+        <v>12311093.628142726</v>
       </c>
       <c r="H37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$28,0,IF($A37=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9236,11 +9236,11 @@
       </c>
       <c r="J37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$28,0,(IF($A37=VARIABLES!$B$28,0,K36)+H37)*C37*VARIABLES!$B$32)</f>
-        <v>10532.560030939898</v>
+        <v>6006.8984381512782</v>
       </c>
       <c r="K37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$28,0,(IF($A37=VARIABLES!$B$28,0,K36)+H37)*(1+C37)-J37)</f>
-        <v>2622607.4477040344</v>
+        <v>2113570.1218809425</v>
       </c>
       <c r="L37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$35,0,IF($A37=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9252,11 +9252,11 @@
       </c>
       <c r="N37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$35,0,(IF($A37=VARIABLES!$B$35,0,O36)+L37)*C37*VARIABLES!$B$39)</f>
-        <v>67667.18889480886</v>
+        <v>33416.291189785268</v>
       </c>
       <c r="O37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$35,0,(IF($A37=VARIABLES!$B$35,0,O36)+L37)*(1+C37)-N37)</f>
-        <v>16849130.034807406</v>
+        <v>11757760.742920158</v>
       </c>
       <c r="P37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$42,0,IF($A37=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9268,51 +9268,51 @@
       </c>
       <c r="R37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$42,0,(IF($A37=VARIABLES!$B$42,0,S36)+P37)*C37*VARIABLES!$B$46)</f>
-        <v>1395.6076189675159</v>
+        <v>780.88735628225186</v>
       </c>
       <c r="S37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$42,0,(IF($A37=VARIABLES!$B$42,0,S36)+P37)*(1+C37)-R37)</f>
-        <v>1394212.0113485483</v>
+        <v>1101385.8383678102</v>
       </c>
       <c r="T37" s="44">
         <f>IF($A37&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A37-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="U37" s="43">
         <f>T37*VARIABLES!$B$53+IF(AND($A37&gt;=VARIABLES!$B$50,MOD($A37-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A37-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>210000</v>
       </c>
       <c r="V37" s="43">
         <f>U37*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1575</v>
       </c>
       <c r="W37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$50,0,(IF($A37&lt;VARIABLES!$B$50+1,0,X36)+U37)*C37*VARIABLES!$B$55)</f>
-        <v>16727.471129369467</v>
+        <v>17445.405079368797</v>
       </c>
       <c r="X37" s="43">
         <f>IF($A37&lt;VARIABLES!$B$50,0,(IF($A37&lt;VARIABLES!$B$50+1,0,X36)+U37)*(1+C37)-W37)</f>
-        <v>4165140.3112129974</v>
+        <v>6138290.3872121926</v>
       </c>
       <c r="Y37" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>470000</v>
       </c>
       <c r="Z37" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3525</v>
       </c>
       <c r="AA37" s="43">
         <f t="shared" si="2"/>
-        <v>112217.15118510813</v>
+        <v>66378.101064600356</v>
       </c>
       <c r="AB37" s="35">
         <f t="shared" si="3"/>
-        <v>114617.15118510813</v>
+        <v>69903.101064600356</v>
       </c>
       <c r="AC37" s="36">
         <f t="shared" si="4"/>
-        <v>40909518.99258434</v>
+        <v>33422100.71852383</v>
       </c>
       <c r="AD37" s="43">
         <f>IF($A37=1,VARIABLES!$B$12,0)</f>
@@ -9340,19 +9340,19 @@
       </c>
       <c r="AJ37" s="38">
         <f>IF($A37&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK37" s="45">
         <f t="shared" si="6"/>
-        <v>43033.817851774802</v>
+        <v>17473.101064600356</v>
       </c>
       <c r="AL37" s="45">
         <f t="shared" si="7"/>
-        <v>-441931.52581027534</v>
+        <v>-499406.68304449646</v>
       </c>
       <c r="AM37" s="40">
         <f t="shared" si="8"/>
-        <v>903833.33333333372</v>
+        <v>252620</v>
       </c>
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.2">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="C38" s="33">
         <f>IF($A38&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$21,0,IF($A38=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9377,11 +9377,11 @@
       </c>
       <c r="F38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$21,0,(IF($A38=VARIABLES!$B$21,0,G37)+D38)*C38*VARIABLES!$B$25)</f>
-        <v>16748.363736990996</v>
+        <v>9122.6724371874043</v>
       </c>
       <c r="G38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$21,0,(IF($A38=VARIABLES!$B$21,0,G37)+D38)*(1+C38)-F38)</f>
-        <v>16731615.373254007</v>
+        <v>12866877.853193033</v>
       </c>
       <c r="H38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$28,0,IF($A38=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9393,11 +9393,11 @@
       </c>
       <c r="J38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$28,0,(IF($A38=VARIABLES!$B$28,0,K37)+H38)*C38*VARIABLES!$B$32)</f>
-        <v>11094.197698766809</v>
+        <v>6281.2461888194157</v>
       </c>
       <c r="K38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$28,0,(IF($A38=VARIABLES!$B$28,0,K37)+H38)*(1+C38)-J38)</f>
-        <v>2762455.2269929359</v>
+        <v>2210101.3375803172</v>
       </c>
       <c r="L38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$35,0,IF($A38=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9409,11 +9409,11 @@
       </c>
       <c r="N38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$35,0,(IF($A38=VARIABLES!$B$35,0,O37)+L38)*C38*VARIABLES!$B$39)</f>
-        <v>70204.708478364191</v>
+        <v>34293.46883351713</v>
       </c>
       <c r="O38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$35,0,(IF($A38=VARIABLES!$B$35,0,O37)+L38)*(1+C38)-N38)</f>
-        <v>17480972.411112685</v>
+        <v>12066401.962421812</v>
       </c>
       <c r="P38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$42,0,IF($A38=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9425,51 +9425,51 @@
       </c>
       <c r="R38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$42,0,(IF($A38=VARIABLES!$B$42,0,S37)+P38)*C38*VARIABLES!$B$46)</f>
-        <v>1473.1375118214046</v>
+        <v>817.67717380986153</v>
       </c>
       <c r="S38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$42,0,(IF($A38=VARIABLES!$B$42,0,S37)+P38)*(1+C38)-R38)</f>
-        <v>1471664.3743095831</v>
+        <v>1153275.2481463947</v>
       </c>
       <c r="T38" s="34">
         <f>IF($A38&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A38-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="U38" s="14">
         <f>T38*VARIABLES!$B$53+IF(AND($A38&gt;=VARIABLES!$B$50,MOD($A38-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A38-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>215000</v>
       </c>
       <c r="V38" s="14">
         <f>U38*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1612.5</v>
       </c>
       <c r="W38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$50,0,(IF($A38&lt;VARIABLES!$B$50+1,0,X37)+U38)*C38*VARIABLES!$B$55)</f>
-        <v>17604.751296720824</v>
+        <v>18530.43029603556</v>
       </c>
       <c r="X38" s="14">
         <f>IF($A38&lt;VARIABLES!$B$50,0,(IF($A38&lt;VARIABLES!$B$50+1,0,X37)+U38)*(1+C38)-W38)</f>
-        <v>4383583.0728834858</v>
+        <v>6520064.259876512</v>
       </c>
       <c r="Y38" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>475000</v>
       </c>
       <c r="Z38" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3562.5</v>
       </c>
       <c r="AA38" s="14">
         <f t="shared" si="2"/>
-        <v>117125.15872266423</v>
+        <v>69045.494929369364</v>
       </c>
       <c r="AB38" s="35">
         <f t="shared" si="3"/>
-        <v>119525.15872266423</v>
+        <v>72607.994929369364</v>
       </c>
       <c r="AC38" s="36">
         <f t="shared" si="4"/>
-        <v>42830290.458552703</v>
+        <v>34816720.661218077</v>
       </c>
       <c r="AD38" s="14">
         <f>IF($A38=1,VARIABLES!$B$12,0)</f>
@@ -9497,19 +9497,19 @@
       </c>
       <c r="AJ38" s="38">
         <f>IF($A38&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK38" s="39">
         <f t="shared" si="6"/>
-        <v>47941.825389330901</v>
+        <v>20177.994929369364</v>
       </c>
       <c r="AL38" s="39">
         <f t="shared" si="7"/>
-        <v>-393989.70042094443</v>
+        <v>-479228.68811512709</v>
       </c>
       <c r="AM38" s="40">
         <f t="shared" si="8"/>
-        <v>930416.66666666709</v>
+        <v>260050</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.2">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C39" s="42">
         <f>IF($A39&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="D39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$21,0,IF($A39=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9534,11 +9534,11 @@
       </c>
       <c r="F39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$21,0,(IF($A39=VARIABLES!$B$21,0,G38)+D39)*C39*VARIABLES!$B$25)</f>
-        <v>17637.099347139592</v>
+        <v>9527.9317679532523</v>
       </c>
       <c r="G39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$21,0,(IF($A39=VARIABLES!$B$21,0,G38)+D39)*(1+C39)-F39)</f>
-        <v>17619462.247792453</v>
+        <v>13438467.192143209</v>
       </c>
       <c r="H39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$28,0,IF($A39=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9550,11 +9550,11 @@
       </c>
       <c r="J39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$28,0,(IF($A39=VARIABLES!$B$28,0,K38)+H39)*C39*VARIABLES!$B$32)</f>
-        <v>11676.896779137234</v>
+        <v>6562.7955679425913</v>
       </c>
       <c r="K39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$28,0,(IF($A39=VARIABLES!$B$28,0,K38)+H39)*(1+C39)-J39)</f>
-        <v>2907547.2980051711</v>
+        <v>2309166.4976917999</v>
       </c>
       <c r="L39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$35,0,IF($A39=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9566,11 +9566,11 @@
       </c>
       <c r="N39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$35,0,(IF($A39=VARIABLES!$B$35,0,O38)+L39)*C39*VARIABLES!$B$39)</f>
-        <v>72837.38504630285</v>
+        <v>35193.672390396954</v>
       </c>
       <c r="O39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$35,0,(IF($A39=VARIABLES!$B$35,0,O38)+L39)*(1+C39)-N39)</f>
-        <v>18136508.87652941</v>
+        <v>12383145.013935383</v>
       </c>
       <c r="P39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$42,0,IF($A39=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9582,51 +9582,51 @@
       </c>
       <c r="R39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$42,0,(IF($A39=VARIABLES!$B$42,0,S38)+P39)*C39*VARIABLES!$B$46)</f>
-        <v>1553.8170565724824</v>
+        <v>855.51320177341279</v>
       </c>
       <c r="S39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$42,0,(IF($A39=VARIABLES!$B$42,0,S38)+P39)*(1+C39)-R39)</f>
-        <v>1552263.2395159099</v>
+        <v>1206640.2630155578</v>
       </c>
       <c r="T39" s="44">
         <f>IF($A39&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A39-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="U39" s="43">
         <f>T39*VARIABLES!$B$53+IF(AND($A39&gt;=VARIABLES!$B$50,MOD($A39-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A39-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>220000</v>
       </c>
       <c r="V39" s="43">
         <f>U39*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1650</v>
       </c>
       <c r="W39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$50,0,(IF($A39&lt;VARIABLES!$B$50+1,0,X38)+U39)*C39*VARIABLES!$B$55)</f>
-        <v>18514.929470347859</v>
+        <v>19658.520757973161</v>
       </c>
       <c r="X39" s="43">
         <f>IF($A39&lt;VARIABLES!$B$50,0,(IF($A39&lt;VARIABLES!$B$50+1,0,X38)+U39)*(1+C39)-W39)</f>
-        <v>4610217.4381166166</v>
+        <v>6916990.9466982698</v>
       </c>
       <c r="Y39" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>480000</v>
       </c>
       <c r="Z39" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="AA39" s="43">
         <f t="shared" si="2"/>
-        <v>122220.12769950004</v>
+        <v>71798.433686039381</v>
       </c>
       <c r="AB39" s="35">
         <f t="shared" si="3"/>
-        <v>124620.12769950004</v>
+        <v>75398.433686039381</v>
       </c>
       <c r="AC39" s="36">
         <f t="shared" si="4"/>
-        <v>44825999.09995956</v>
+        <v>36254409.913484216</v>
       </c>
       <c r="AD39" s="43">
         <f>IF($A39=1,VARIABLES!$B$12,0)</f>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="AF39" s="43">
         <f>IF(MOD($A39,12)=0,AC39*VARIABLES!$B$16,0)</f>
-        <v>112064.9977498989</v>
+        <v>90636.024783710542</v>
       </c>
       <c r="AG39" s="43">
         <f>VARIABLES!$B$17</f>
@@ -9650,23 +9650,23 @@
       </c>
       <c r="AI39" s="37">
         <f t="shared" si="5"/>
-        <v>160064.9977498989</v>
+        <v>138636.02478371054</v>
       </c>
       <c r="AJ39" s="38">
         <f>IF($A39&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>26583.333333333332</v>
+        <v>7430</v>
       </c>
       <c r="AK39" s="45">
         <f t="shared" si="6"/>
-        <v>-62028.203383732194</v>
+        <v>-70667.59109767116</v>
       </c>
       <c r="AL39" s="45">
         <f t="shared" si="7"/>
-        <v>-456017.90380467661</v>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM39" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>267480</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.2">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C40" s="33">
         <f>IF($A40&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$21,0,IF($A40=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9691,11 +9691,11 @@
       </c>
       <c r="F40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$21,0,(IF($A40=VARIABLES!$B$21,0,G39)+D40)*C40*VARIABLES!$B$25)</f>
-        <v>3712.3879682900947</v>
+        <v>2557.2125985268522</v>
       </c>
       <c r="G40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$21,0,(IF($A40=VARIABLES!$B$21,0,G39)+D40)*(1+C40)-F40)</f>
-        <v>17964245.378555764</v>
+        <v>13738198.483485756</v>
       </c>
       <c r="H40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$28,0,IF($A40=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9707,11 +9707,11 @@
       </c>
       <c r="J40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$28,0,(IF($A40=VARIABLES!$B$28,0,K39)+H40)*C40*VARIABLES!$B$32)</f>
-        <v>2456.2894150043094</v>
+        <v>1761.87487326885</v>
       </c>
       <c r="K40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$28,0,(IF($A40=VARIABLES!$B$28,0,K39)+H40)*(1+C40)-J40)</f>
-        <v>2969653.9027402098</v>
+        <v>2365023.3715512198</v>
       </c>
       <c r="L40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$35,0,IF($A40=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9723,11 +9723,11 @@
       </c>
       <c r="N40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$35,0,(IF($A40=VARIABLES!$B$35,0,O39)+L40)*C40*VARIABLES!$B$39)</f>
-        <v>15113.757397107842</v>
+        <v>9287.3587604515378</v>
       </c>
       <c r="O40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$35,0,(IF($A40=VARIABLES!$B$35,0,O39)+L40)*(1+C40)-N40)</f>
-        <v>18272532.693103381</v>
+        <v>12466731.242779447</v>
       </c>
       <c r="P40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$42,0,IF($A40=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9739,51 +9739,51 @@
       </c>
       <c r="R40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$42,0,(IF($A40=VARIABLES!$B$42,0,S39)+P40)*C40*VARIABLES!$B$46)</f>
-        <v>327.55484156581457</v>
+        <v>229.99504931541708</v>
       </c>
       <c r="S40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$42,0,(IF($A40=VARIABLES!$B$42,0,S39)+P40)*(1+C40)-R40)</f>
-        <v>1585037.8783369765</v>
+        <v>1235610.069938859</v>
       </c>
       <c r="T40" s="34">
         <f>IF($A40&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A40-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="U40" s="14">
         <f>T40*VARIABLES!$B$53+IF(AND($A40&gt;=VARIABLES!$B$50,MOD($A40-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A40-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>225000</v>
       </c>
       <c r="V40" s="14">
         <f>U40*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1687.5</v>
       </c>
       <c r="W40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$50,0,(IF($A40&lt;VARIABLES!$B$50+1,0,X39)+U40)*C40*VARIABLES!$B$55)</f>
-        <v>3891.8478650971806</v>
+        <v>5356.493210023702</v>
       </c>
       <c r="X40" s="14">
         <f>IF($A40&lt;VARIABLES!$B$50,0,(IF($A40&lt;VARIABLES!$B$50+1,0,X39)+U40)*(1+C40)-W40)</f>
-        <v>4705244.0689024907</v>
+        <v>7190199.3855884839</v>
       </c>
       <c r="Y40" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>485000</v>
       </c>
       <c r="Z40" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3637.5</v>
       </c>
       <c r="AA40" s="14">
         <f t="shared" si="2"/>
-        <v>25501.837487065244</v>
+        <v>19192.934491586358</v>
       </c>
       <c r="AB40" s="35">
         <f t="shared" si="3"/>
-        <v>27901.837487065244</v>
+        <v>22830.434491586358</v>
       </c>
       <c r="AC40" s="36">
         <f t="shared" si="4"/>
-        <v>45496713.921638824</v>
+        <v>36995762.553343765</v>
       </c>
       <c r="AD40" s="14">
         <f>IF($A40=1,VARIABLES!$B$12,0)</f>
@@ -9815,15 +9815,15 @@
       </c>
       <c r="AK40" s="39">
         <f t="shared" si="6"/>
-        <v>-17098.162512934756</v>
+        <v>-22169.565508413642</v>
       </c>
       <c r="AL40" s="39">
-        <f t="shared" si="7"/>
-        <v>-473116.06631761137</v>
+        <f>IF(AJ40&gt;0,AL39+AK40,AL39)</f>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM40" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>245310.43449158635</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.2">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="C41" s="42">
         <f>IF($A41&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$21,0,IF($A41=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9848,11 +9848,11 @@
       </c>
       <c r="F41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$21,0,(IF($A41=VARIABLES!$B$21,0,G40)+D41)*C41*VARIABLES!$B$25)</f>
-        <v>3784.2177871991175</v>
+        <v>2613.4122156535796</v>
       </c>
       <c r="G41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$21,0,(IF($A41=VARIABLES!$B$21,0,G40)+D41)*(1+C41)-F41)</f>
-        <v>18311829.872256529</v>
+        <v>14040121.559896247</v>
       </c>
       <c r="H41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$28,0,IF($A41=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9864,11 +9864,11 @@
       </c>
       <c r="J41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$28,0,(IF($A41=VARIABLES!$B$28,0,K40)+H41)*C41*VARIABLES!$B$32)</f>
-        <v>2508.0449189501751</v>
+        <v>1803.7675286634149</v>
       </c>
       <c r="K41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$28,0,(IF($A41=VARIABLES!$B$28,0,K40)+H41)*(1+C41)-J41)</f>
-        <v>3032226.3070107615</v>
+        <v>2421257.2793091908</v>
       </c>
       <c r="L41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$35,0,IF($A41=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9880,11 +9880,11 @@
       </c>
       <c r="N41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$35,0,(IF($A41=VARIABLES!$B$35,0,O40)+L41)*C41*VARIABLES!$B$39)</f>
-        <v>15227.110577586151</v>
+        <v>9350.0484320845844</v>
       </c>
       <c r="O41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$35,0,(IF($A41=VARIABLES!$B$35,0,O40)+L41)*(1+C41)-N41)</f>
-        <v>18409576.688301653</v>
+        <v>12550881.67866821</v>
       </c>
       <c r="P41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$42,0,IF($A41=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9896,51 +9896,51 @@
       </c>
       <c r="R41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$42,0,(IF($A41=VARIABLES!$B$42,0,S40)+P41)*C41*VARIABLES!$B$46)</f>
-        <v>334.3828913202035</v>
+        <v>235.42688811353605</v>
       </c>
       <c r="S41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$42,0,(IF($A41=VARIABLES!$B$42,0,S40)+P41)*(1+C41)-R41)</f>
-        <v>1618078.8110984645</v>
+        <v>1264791.7185752869</v>
       </c>
       <c r="T41" s="44">
         <f>IF($A41&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A41-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="U41" s="43">
         <f>T41*VARIABLES!$B$53+IF(AND($A41&gt;=VARIABLES!$B$50,MOD($A41-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A41-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>230000</v>
       </c>
       <c r="V41" s="43">
         <f>U41*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1725</v>
       </c>
       <c r="W41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$50,0,(IF($A41&lt;VARIABLES!$B$50+1,0,X40)+U41)*C41*VARIABLES!$B$55)</f>
-        <v>3971.0367240854089</v>
+        <v>5565.1495391913631</v>
       </c>
       <c r="X41" s="43">
         <f>IF($A41&lt;VARIABLES!$B$50,0,(IF($A41&lt;VARIABLES!$B$50+1,0,X40)+U41)*(1+C41)-W41)</f>
-        <v>4800983.3994192593</v>
+        <v>7470285.7314412063</v>
       </c>
       <c r="Y41" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>490000</v>
       </c>
       <c r="Z41" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3675</v>
       </c>
       <c r="AA41" s="43">
         <f t="shared" si="2"/>
-        <v>25824.792899141059</v>
+        <v>19567.804603706478</v>
       </c>
       <c r="AB41" s="35">
         <f t="shared" si="3"/>
-        <v>28224.792899141059</v>
+        <v>23242.804603706478</v>
       </c>
       <c r="AC41" s="36">
         <f t="shared" si="4"/>
-        <v>46172695.078086659</v>
+        <v>37747337.967890143</v>
       </c>
       <c r="AD41" s="43">
         <f>IF($A41=1,VARIABLES!$B$12,0)</f>
@@ -9972,15 +9972,15 @@
       </c>
       <c r="AK41" s="45">
         <f t="shared" si="6"/>
-        <v>-16775.207100858941</v>
+        <v>-21757.195396293522</v>
       </c>
       <c r="AL41" s="45">
-        <f t="shared" si="7"/>
-        <v>-489891.27341847029</v>
+        <f t="shared" ref="AL41:AL51" si="9">IF(AJ41&gt;0,AL40+AK41,AL40)</f>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM41" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>223553.23909529281</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.2">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="C42" s="33">
         <f>IF($A42&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$21,0,IF($A42=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10005,11 +10005,11 @@
       </c>
       <c r="F42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$21,0,(IF($A42=VARIABLES!$B$21,0,G41)+D42)*C42*VARIABLES!$B$25)</f>
-        <v>3856.6312233867766</v>
+        <v>2670.0227924805463</v>
       </c>
       <c r="G42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$21,0,(IF($A42=VARIABLES!$B$21,0,G41)+D42)*(1+C42)-F42)</f>
-        <v>18662238.489968613</v>
+        <v>14344252.448802989</v>
       </c>
       <c r="H42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$28,0,IF($A42=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10021,11 +10021,11 @@
       </c>
       <c r="J42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$28,0,(IF($A42=VARIABLES!$B$28,0,K41)+H42)*C42*VARIABLES!$B$32)</f>
-        <v>2560.1885891756347</v>
+        <v>1845.9429594818932</v>
       </c>
       <c r="K42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$28,0,(IF($A42=VARIABLES!$B$28,0,K41)+H42)*(1+C42)-J42)</f>
-        <v>3095268.0043133418</v>
+        <v>2477870.7659445279</v>
       </c>
       <c r="L42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$35,0,IF($A42=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10037,11 +10037,11 @@
       </c>
       <c r="N42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$35,0,(IF($A42=VARIABLES!$B$35,0,O41)+L42)*C42*VARIABLES!$B$39)</f>
-        <v>15341.313906918045</v>
+        <v>9413.1612590011573</v>
       </c>
       <c r="O42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$35,0,(IF($A42=VARIABLES!$B$35,0,O41)+L42)*(1+C42)-N42)</f>
-        <v>18547648.513463914</v>
+        <v>12635600.129999222</v>
       </c>
       <c r="P42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$42,0,IF($A42=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10053,51 +10053,51 @@
       </c>
       <c r="R42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$42,0,(IF($A42=VARIABLES!$B$42,0,S41)+P42)*C42*VARIABLES!$B$46)</f>
-        <v>341.26641897884679</v>
+        <v>240.89844723286629</v>
       </c>
       <c r="S42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$42,0,(IF($A42=VARIABLES!$B$42,0,S41)+P42)*(1+C42)-R42)</f>
-        <v>1651388.2014386395</v>
+        <v>1294186.7580173688</v>
       </c>
       <c r="T42" s="34">
         <f>IF($A42&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A42-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="U42" s="14">
         <f>T42*VARIABLES!$B$53+IF(AND($A42&gt;=VARIABLES!$B$50,MOD($A42-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A42-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>235000</v>
       </c>
       <c r="V42" s="14">
         <f>U42*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1762.5</v>
       </c>
       <c r="W42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$50,0,(IF($A42&lt;VARIABLES!$B$50+1,0,X41)+U42)*C42*VARIABLES!$B$55)</f>
-        <v>4050.8194995160493</v>
+        <v>5778.9642985809051</v>
       </c>
       <c r="X42" s="14">
         <f>IF($A42&lt;VARIABLES!$B$50,0,(IF($A42&lt;VARIABLES!$B$50+1,0,X41)+U42)*(1+C42)-W42)</f>
-        <v>4897440.7749149036</v>
+        <v>7757296.4101284351</v>
       </c>
       <c r="Y42" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>495000</v>
       </c>
       <c r="Z42" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3712.5</v>
       </c>
       <c r="AA42" s="14">
         <f t="shared" si="2"/>
-        <v>26150.219637975355</v>
+        <v>19948.98975677737</v>
       </c>
       <c r="AB42" s="35">
         <f t="shared" si="3"/>
-        <v>28550.219637975355</v>
+        <v>23661.48975677737</v>
       </c>
       <c r="AC42" s="36">
         <f t="shared" si="4"/>
-        <v>46853983.984099418</v>
+        <v>38509206.512892544</v>
       </c>
       <c r="AD42" s="14">
         <f>IF($A42=1,VARIABLES!$B$12,0)</f>
@@ -10129,15 +10129,15 @@
       </c>
       <c r="AK42" s="39">
         <f t="shared" si="6"/>
-        <v>-16449.780362024645</v>
+        <v>-21338.51024322263</v>
       </c>
       <c r="AL42" s="39">
-        <f t="shared" si="7"/>
-        <v>-506341.05378049496</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM42" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>202214.72885207017</v>
       </c>
     </row>
     <row r="43" spans="1:39" x14ac:dyDescent="0.2">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C43" s="42">
         <f>IF($A43&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$21,0,IF($A43=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10162,11 +10162,11 @@
       </c>
       <c r="F43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$21,0,(IF($A43=VARIABLES!$B$21,0,G42)+D43)*C43*VARIABLES!$B$25)</f>
-        <v>3929.633018743461</v>
+        <v>2727.0473341505603</v>
       </c>
       <c r="G43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$21,0,(IF($A43=VARIABLES!$B$21,0,G42)+D43)*(1+C43)-F43)</f>
-        <v>19015494.177699607</v>
+        <v>14650607.294834862</v>
       </c>
       <c r="H43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$28,0,IF($A43=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10178,11 +10178,11 @@
       </c>
       <c r="J43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$28,0,(IF($A43=VARIABLES!$B$28,0,K42)+H43)*C43*VARIABLES!$B$32)</f>
-        <v>2612.7233369277851</v>
+        <v>1888.4030744583958</v>
       </c>
       <c r="K43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$28,0,(IF($A43=VARIABLES!$B$28,0,K42)+H43)*(1+C43)-J43)</f>
-        <v>3158782.514345692</v>
+        <v>2534866.393614654</v>
       </c>
       <c r="L43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$35,0,IF($A43=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10194,11 +10194,11 @@
       </c>
       <c r="N43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$35,0,(IF($A43=VARIABLES!$B$35,0,O42)+L43)*C43*VARIABLES!$B$39)</f>
-        <v>15456.373761219927</v>
+        <v>9476.7000974994171</v>
       </c>
       <c r="O43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$35,0,(IF($A43=VARIABLES!$B$35,0,O42)+L43)*(1+C43)-N43)</f>
-        <v>18686755.877314892</v>
+        <v>12720890.430876717</v>
       </c>
       <c r="P43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$42,0,IF($A43=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10210,51 +10210,51 @@
       </c>
       <c r="R43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$42,0,(IF($A43=VARIABLES!$B$42,0,S42)+P43)*C43*VARIABLES!$B$46)</f>
-        <v>348.20587529971658</v>
+        <v>246.41001712825664</v>
       </c>
       <c r="S43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$42,0,(IF($A43=VARIABLES!$B$42,0,S42)+P43)*(1+C43)-R43)</f>
-        <v>1684968.2305753285</v>
+        <v>1323796.7486853709</v>
       </c>
       <c r="T43" s="44">
         <f>IF($A43&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A43-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="U43" s="43">
         <f>T43*VARIABLES!$B$53+IF(AND($A43&gt;=VARIABLES!$B$50,MOD($A43-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A43-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>240000</v>
       </c>
       <c r="V43" s="43">
         <f>U43*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="W43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$50,0,(IF($A43&lt;VARIABLES!$B$50+1,0,X42)+U43)*C43*VARIABLES!$B$55)</f>
-        <v>4131.2006457624193</v>
+        <v>5997.9723075963266</v>
       </c>
       <c r="X43" s="43">
         <f>IF($A43&lt;VARIABLES!$B$50,0,(IF($A43&lt;VARIABLES!$B$50+1,0,X42)+U43)*(1+C43)-W43)</f>
-        <v>4994621.5807267651</v>
+        <v>8051278.1608968023</v>
       </c>
       <c r="Y43" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>500000</v>
       </c>
       <c r="Z43" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3750</v>
       </c>
       <c r="AA43" s="43">
         <f t="shared" si="2"/>
-        <v>26478.13663795331</v>
+        <v>20336.532830832955</v>
       </c>
       <c r="AB43" s="35">
         <f t="shared" si="3"/>
-        <v>28878.13663795331</v>
+        <v>24086.532830832955</v>
       </c>
       <c r="AC43" s="36">
         <f t="shared" si="4"/>
-        <v>47540622.380662285</v>
+        <v>39281439.028908409</v>
       </c>
       <c r="AD43" s="43">
         <f>IF($A43=1,VARIABLES!$B$12,0)</f>
@@ -10286,15 +10286,15 @@
       </c>
       <c r="AK43" s="45">
         <f t="shared" si="6"/>
-        <v>-16121.86336204669</v>
+        <v>-20913.467169167045</v>
       </c>
       <c r="AL43" s="45">
-        <f t="shared" si="7"/>
-        <v>-522462.91714254167</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM43" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>181301.26168290313</v>
       </c>
     </row>
     <row r="44" spans="1:39" x14ac:dyDescent="0.2">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="C44" s="33">
         <f>IF($A44&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$21,0,IF($A44=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10319,11 +10319,11 @@
       </c>
       <c r="F44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$21,0,(IF($A44=VARIABLES!$B$21,0,G43)+D44)*C44*VARIABLES!$B$25)</f>
-        <v>4003.227953687418</v>
+        <v>2784.4888677815366</v>
       </c>
       <c r="G44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$21,0,(IF($A44=VARIABLES!$B$21,0,G43)+D44)*(1+C44)-F44)</f>
-        <v>19371620.067893416</v>
+        <v>14959202.360678341</v>
       </c>
       <c r="H44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$28,0,IF($A44=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10335,11 +10335,11 @@
       </c>
       <c r="J44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$28,0,(IF($A44=VARIABLES!$B$28,0,K43)+H44)*C44*VARIABLES!$B$32)</f>
-        <v>2665.6520952880765</v>
+        <v>1931.1497952109905</v>
       </c>
       <c r="K44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$28,0,(IF($A44=VARIABLES!$B$28,0,K43)+H44)*(1+C44)-J44)</f>
-        <v>3222773.3832032848</v>
+        <v>2592246.7417715532</v>
       </c>
       <c r="L44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$35,0,IF($A44=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10351,11 +10351,11 @@
       </c>
       <c r="N44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$35,0,(IF($A44=VARIABLES!$B$35,0,O43)+L44)*C44*VARIABLES!$B$39)</f>
-        <v>15572.296564429076</v>
+        <v>9540.6678231575388</v>
       </c>
       <c r="O44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$35,0,(IF($A44=VARIABLES!$B$35,0,O43)+L44)*(1+C44)-N44)</f>
-        <v>18826906.54639475</v>
+        <v>12806756.441285135</v>
       </c>
       <c r="P44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$42,0,IF($A44=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10367,51 +10367,51 @@
       </c>
       <c r="R44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$42,0,(IF($A44=VARIABLES!$B$42,0,S43)+P44)*C44*VARIABLES!$B$46)</f>
-        <v>355.20171470319343</v>
+        <v>251.96189037850706</v>
       </c>
       <c r="S44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$42,0,(IF($A44=VARIABLES!$B$42,0,S43)+P44)*(1+C44)-R44)</f>
-        <v>1718821.097448753</v>
+        <v>1353623.2624101327</v>
       </c>
       <c r="T44" s="34">
         <f>IF($A44&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A44-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="U44" s="14">
         <f>T44*VARIABLES!$B$53+IF(AND($A44&gt;=VARIABLES!$B$50,MOD($A44-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A44-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>245000</v>
       </c>
       <c r="V44" s="14">
         <f>U44*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1837.5</v>
       </c>
       <c r="W44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$50,0,(IF($A44&lt;VARIABLES!$B$50+1,0,X43)+U44)*C44*VARIABLES!$B$55)</f>
-        <v>4212.1846506056381</v>
+        <v>6222.2086206726017</v>
       </c>
       <c r="X44" s="14">
         <f>IF($A44&lt;VARIABLES!$B$50,0,(IF($A44&lt;VARIABLES!$B$50+1,0,X43)+U44)*(1+C44)-W44)</f>
-        <v>5092531.2425822159</v>
+        <v>8352278.038482856</v>
       </c>
       <c r="Y44" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>505000</v>
       </c>
       <c r="Z44" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3787.5</v>
       </c>
       <c r="AA44" s="14">
         <f t="shared" si="2"/>
-        <v>26808.562978713402</v>
+        <v>20730.476997201175</v>
       </c>
       <c r="AB44" s="35">
         <f t="shared" si="3"/>
-        <v>29208.562978713402</v>
+        <v>24517.976997201175</v>
       </c>
       <c r="AC44" s="36">
         <f t="shared" si="4"/>
-        <v>48232652.337522417</v>
+        <v>40064106.844628021</v>
       </c>
       <c r="AD44" s="14">
         <f>IF($A44=1,VARIABLES!$B$12,0)</f>
@@ -10443,15 +10443,15 @@
       </c>
       <c r="AK44" s="39">
         <f t="shared" si="6"/>
-        <v>-15791.437021286598</v>
+        <v>-20482.023002798825</v>
       </c>
       <c r="AL44" s="39">
-        <f t="shared" si="7"/>
-        <v>-538254.35416382831</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM44" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>160819.23868010432</v>
       </c>
     </row>
     <row r="45" spans="1:39" x14ac:dyDescent="0.2">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C45" s="42">
         <f>IF($A45&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$21,0,IF($A45=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="F45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$21,0,(IF($A45=VARIABLES!$B$21,0,G44)+D45)*C45*VARIABLES!$B$25)</f>
-        <v>4077.4208474777952</v>
+        <v>2842.3504426271888</v>
       </c>
       <c r="G45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$21,0,(IF($A45=VARIABLES!$B$21,0,G44)+D45)*(1+C45)-F45)</f>
-        <v>19730639.480945047</v>
+        <v>15270054.027940802</v>
       </c>
       <c r="H45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$28,0,IF($A45=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10492,11 +10492,11 @@
       </c>
       <c r="J45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$28,0,(IF($A45=VARIABLES!$B$28,0,K44)+H45)*C45*VARIABLES!$B$32)</f>
-        <v>2718.9778193360708</v>
+        <v>1974.1850563286648</v>
       </c>
       <c r="K45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$28,0,(IF($A45=VARIABLES!$B$28,0,K44)+H45)*(1+C45)-J45)</f>
-        <v>3287244.1835773094</v>
+        <v>2650014.4072785112</v>
       </c>
       <c r="L45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$35,0,IF($A45=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10508,11 +10508,11 @@
       </c>
       <c r="N45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$35,0,(IF($A45=VARIABLES!$B$35,0,O44)+L45)*C45*VARIABLES!$B$39)</f>
-        <v>15689.088788662293</v>
+        <v>9605.0673309638514</v>
       </c>
       <c r="O45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$35,0,(IF($A45=VARIABLES!$B$35,0,O44)+L45)*(1+C45)-N45)</f>
-        <v>18968108.345492709</v>
+        <v>12893202.04726381</v>
       </c>
       <c r="P45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$42,0,IF($A45=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10524,51 +10524,51 @@
       </c>
       <c r="R45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$42,0,(IF($A45=VARIABLES!$B$42,0,S44)+P45)*C45*VARIABLES!$B$46)</f>
-        <v>362.25439530182354</v>
+        <v>257.55436170189989</v>
       </c>
       <c r="S45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$42,0,(IF($A45=VARIABLES!$B$42,0,S44)+P45)*(1+C45)-R45)</f>
-        <v>1752949.0188655239</v>
+        <v>1383667.8825165068</v>
       </c>
       <c r="T45" s="44">
         <f>IF($A45&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A45-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="U45" s="43">
         <f>T45*VARIABLES!$B$53+IF(AND($A45&gt;=VARIABLES!$B$50,MOD($A45-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A45-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>250000</v>
       </c>
       <c r="V45" s="43">
         <f>U45*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1875</v>
       </c>
       <c r="W45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$50,0,(IF($A45&lt;VARIABLES!$B$50+1,0,X44)+U45)*C45*VARIABLES!$B$55)</f>
-        <v>4293.7760354851807</v>
+        <v>6451.708528862142</v>
       </c>
       <c r="X45" s="43">
         <f>IF($A45&lt;VARIABLES!$B$50,0,(IF($A45&lt;VARIABLES!$B$50+1,0,X44)+U45)*(1+C45)-W45)</f>
-        <v>5191175.2269015824</v>
+        <v>8660343.4152426161</v>
       </c>
       <c r="Y45" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>510000</v>
       </c>
       <c r="Z45" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3825</v>
       </c>
       <c r="AA45" s="43">
         <f t="shared" si="2"/>
-        <v>27141.517886263166</v>
+        <v>21130.865720483747</v>
       </c>
       <c r="AB45" s="35">
         <f t="shared" si="3"/>
-        <v>29541.517886263166</v>
+        <v>24955.865720483747</v>
       </c>
       <c r="AC45" s="36">
         <f t="shared" si="4"/>
-        <v>48930116.25578218</v>
+        <v>40857281.780242249</v>
       </c>
       <c r="AD45" s="43">
         <f>IF($A45=1,VARIABLES!$B$12,0)</f>
@@ -10600,15 +10600,15 @@
       </c>
       <c r="AK45" s="45">
         <f t="shared" si="6"/>
-        <v>-15458.482113736834</v>
+        <v>-20044.134279516253</v>
       </c>
       <c r="AL45" s="45">
-        <f t="shared" si="7"/>
-        <v>-553712.8362775651</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM45" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>140775.10440058805</v>
       </c>
     </row>
     <row r="46" spans="1:39" x14ac:dyDescent="0.2">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="C46" s="33">
         <f>IF($A46&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$21,0,IF($A46=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10633,11 +10633,11 @@
       </c>
       <c r="F46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$21,0,(IF($A46=VARIABLES!$B$21,0,G45)+D46)*C46*VARIABLES!$B$25)</f>
-        <v>4152.2165585302182</v>
+        <v>2900.6351302389007</v>
       </c>
       <c r="G46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$21,0,(IF($A46=VARIABLES!$B$21,0,G45)+D46)*(1+C46)-F46)</f>
-        <v>20092575.926727723</v>
+        <v>15583178.798020119</v>
       </c>
       <c r="H46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$28,0,IF($A46=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10649,11 +10649,11 @@
       </c>
       <c r="J46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$28,0,(IF($A46=VARIABLES!$B$28,0,K45)+H46)*C46*VARIABLES!$B$32)</f>
-        <v>2772.7034863144245</v>
+        <v>2017.5108054588834</v>
       </c>
       <c r="K46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$28,0,(IF($A46=VARIABLES!$B$28,0,K45)+H46)*(1+C46)-J46)</f>
-        <v>3352198.514954139</v>
+        <v>2708172.0045276415</v>
       </c>
       <c r="L46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$35,0,IF($A46=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10665,11 +10665,11 @@
       </c>
       <c r="N46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$35,0,(IF($A46=VARIABLES!$B$35,0,O45)+L46)*C46*VARIABLES!$B$39)</f>
-        <v>15806.756954577257</v>
+        <v>9669.9015354478579</v>
       </c>
       <c r="O46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$35,0,(IF($A46=VARIABLES!$B$35,0,O45)+L46)*(1+C46)-N46)</f>
-        <v>19110369.158083905</v>
+        <v>12980231.161082841</v>
       </c>
       <c r="P46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$42,0,IF($A46=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10681,51 +10681,51 @@
       </c>
       <c r="R46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$42,0,(IF($A46=VARIABLES!$B$42,0,S45)+P46)*C46*VARIABLES!$B$46)</f>
-        <v>369.36437893031751</v>
+        <v>263.18772797184505</v>
       </c>
       <c r="S46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$42,0,(IF($A46=VARIABLES!$B$42,0,S45)+P46)*(1+C46)-R46)</f>
-        <v>1787354.2296438061</v>
+        <v>1413932.2039074088</v>
       </c>
       <c r="T46" s="34">
         <f>IF($A46&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A46-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="U46" s="14">
         <f>T46*VARIABLES!$B$53+IF(AND($A46&gt;=VARIABLES!$B$50,MOD($A46-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A46-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>255000</v>
       </c>
       <c r="V46" s="14">
         <f>U46*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1912.5</v>
       </c>
       <c r="W46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$50,0,(IF($A46&lt;VARIABLES!$B$50+1,0,X45)+U46)*C46*VARIABLES!$B$55)</f>
-        <v>4375.9793557513185</v>
+        <v>6686.5075614319621</v>
       </c>
       <c r="X46" s="14">
         <f>IF($A46&lt;VARIABLES!$B$50,0,(IF($A46&lt;VARIABLES!$B$50+1,0,X45)+U46)*(1+C46)-W46)</f>
-        <v>5290559.0411033435</v>
+        <v>8975521.983295504</v>
       </c>
       <c r="Y46" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>515000</v>
       </c>
       <c r="Z46" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3862.5</v>
       </c>
       <c r="AA46" s="14">
         <f t="shared" si="2"/>
-        <v>27477.020734103535</v>
+        <v>21537.742760549449</v>
       </c>
       <c r="AB46" s="35">
         <f t="shared" si="3"/>
-        <v>29877.020734103535</v>
+        <v>25400.242760549449</v>
       </c>
       <c r="AC46" s="36">
         <f t="shared" si="4"/>
-        <v>49633056.87051291</v>
+        <v>41661036.150833517</v>
       </c>
       <c r="AD46" s="14">
         <f>IF($A46=1,VARIABLES!$B$12,0)</f>
@@ -10757,15 +10757,15 @@
       </c>
       <c r="AK46" s="39">
         <f t="shared" si="6"/>
-        <v>-15122.979265896465</v>
+        <v>-19599.757239450551</v>
       </c>
       <c r="AL46" s="39">
-        <f t="shared" si="7"/>
-        <v>-568835.81554346159</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM46" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>121175.3471611375</v>
       </c>
     </row>
     <row r="47" spans="1:39" x14ac:dyDescent="0.2">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C47" s="42">
         <f>IF($A47&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$21,0,IF($A47=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10790,11 +10790,11 @@
       </c>
       <c r="F47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$21,0,(IF($A47=VARIABLES!$B$21,0,G46)+D47)*C47*VARIABLES!$B$25)</f>
-        <v>4227.6199847349426</v>
+        <v>2959.3460246287723</v>
       </c>
       <c r="G47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$21,0,(IF($A47=VARIABLES!$B$21,0,G46)+D47)*(1+C47)-F47)</f>
-        <v>20457453.106132384</v>
+        <v>15898593.292980641</v>
       </c>
       <c r="H47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$28,0,IF($A47=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10806,11 +10806,11 @@
       </c>
       <c r="J47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$28,0,(IF($A47=VARIABLES!$B$28,0,K46)+H47)*C47*VARIABLES!$B$32)</f>
-        <v>2826.8320957951159</v>
+        <v>2061.1290033957312</v>
       </c>
       <c r="K47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$28,0,(IF($A47=VARIABLES!$B$28,0,K46)+H47)*(1+C47)-J47)</f>
-        <v>3417640.0038162949</v>
+        <v>2766722.1655582031</v>
       </c>
       <c r="L47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$35,0,IF($A47=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10822,11 +10822,11 @@
       </c>
       <c r="N47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$35,0,(IF($A47=VARIABLES!$B$35,0,O46)+L47)*C47*VARIABLES!$B$39)</f>
-        <v>15925.307631736587</v>
+        <v>9735.1733708121301</v>
       </c>
       <c r="O47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$35,0,(IF($A47=VARIABLES!$B$35,0,O46)+L47)*(1+C47)-N47)</f>
-        <v>19253696.926769536</v>
+        <v>13067847.721420152</v>
       </c>
       <c r="P47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$42,0,IF($A47=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10838,51 +10838,51 @@
       </c>
       <c r="R47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$42,0,(IF($A47=VARIABLES!$B$42,0,S46)+P47)*C47*VARIABLES!$B$46)</f>
-        <v>376.53213117579298</v>
+        <v>268.86228823263917</v>
       </c>
       <c r="S47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$42,0,(IF($A47=VARIABLES!$B$42,0,S46)+P47)*(1+C47)-R47)</f>
-        <v>1822038.982759662</v>
+        <v>1444417.8331484818</v>
       </c>
       <c r="T47" s="44">
         <f>IF($A47&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A47-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="U47" s="43">
         <f>T47*VARIABLES!$B$53+IF(AND($A47&gt;=VARIABLES!$B$50,MOD($A47-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A47-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>260000</v>
       </c>
       <c r="V47" s="43">
         <f>U47*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1950</v>
       </c>
       <c r="W47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$50,0,(IF($A47&lt;VARIABLES!$B$50+1,0,X46)+U47)*C47*VARIABLES!$B$55)</f>
-        <v>4458.7992009194531</v>
+        <v>6926.6414874716284</v>
       </c>
       <c r="X47" s="43">
         <f>IF($A47&lt;VARIABLES!$B$50,0,(IF($A47&lt;VARIABLES!$B$50+1,0,X46)+U47)*(1+C47)-W47)</f>
-        <v>5390688.2339116186</v>
+        <v>9297861.7566827498</v>
       </c>
       <c r="Y47" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>520000</v>
       </c>
       <c r="Z47" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="AA47" s="43">
         <f t="shared" si="2"/>
-        <v>27815.091044361892</v>
+        <v>21951.152174540905</v>
       </c>
       <c r="AB47" s="35">
         <f t="shared" si="3"/>
-        <v>30215.091044361892</v>
+        <v>25851.152174540905</v>
       </c>
       <c r="AC47" s="36">
         <f t="shared" si="4"/>
-        <v>50341517.2533895</v>
+        <v>42475442.769790232</v>
       </c>
       <c r="AD47" s="43">
         <f>IF($A47=1,VARIABLES!$B$12,0)</f>
@@ -10914,15 +10914,15 @@
       </c>
       <c r="AK47" s="45">
         <f t="shared" si="6"/>
-        <v>-14784.908955638108</v>
+        <v>-19148.847825459095</v>
       </c>
       <c r="AL47" s="45">
-        <f t="shared" si="7"/>
-        <v>-583620.72449909966</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM47" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>102026.49933567841</v>
       </c>
     </row>
     <row r="48" spans="1:39" x14ac:dyDescent="0.2">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="C48" s="33">
         <f>IF($A48&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$21,0,IF($A48=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -10947,11 +10947,11 @@
       </c>
       <c r="F48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$21,0,(IF($A48=VARIABLES!$B$21,0,G47)+D48)*C48*VARIABLES!$B$25)</f>
-        <v>4303.6360637775797</v>
+        <v>3018.4862424338703</v>
       </c>
       <c r="G48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$21,0,(IF($A48=VARIABLES!$B$21,0,G47)+D48)*(1+C48)-F48)</f>
-        <v>20825294.91261971</v>
+        <v>16216314.256435564</v>
       </c>
       <c r="H48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$28,0,IF($A48=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10963,11 +10963,11 @@
       </c>
       <c r="J48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$28,0,(IF($A48=VARIABLES!$B$28,0,K47)+H48)*C48*VARIABLES!$B$32)</f>
-        <v>2881.3666698469128</v>
+        <v>2105.0416241686521</v>
       </c>
       <c r="K48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$28,0,(IF($A48=VARIABLES!$B$28,0,K47)+H48)*(1+C48)-J48)</f>
-        <v>3483572.3038449171</v>
+        <v>2825667.540175721</v>
       </c>
       <c r="L48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$35,0,IF($A48=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10979,11 +10979,11 @@
       </c>
       <c r="N48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$35,0,(IF($A48=VARIABLES!$B$35,0,O47)+L48)*C48*VARIABLES!$B$39)</f>
-        <v>16044.747438974615</v>
+        <v>9800.8857910651132</v>
       </c>
       <c r="O48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$35,0,(IF($A48=VARIABLES!$B$35,0,O47)+L48)*(1+C48)-N48)</f>
-        <v>19398099.653720308</v>
+        <v>13156055.693539739</v>
       </c>
       <c r="P48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$42,0,IF($A48=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10995,51 +10995,51 @@
       </c>
       <c r="R48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$42,0,(IF($A48=VARIABLES!$B$42,0,S47)+P48)*C48*VARIABLES!$B$46)</f>
-        <v>383.75812140826292</v>
+        <v>274.57834371534034</v>
       </c>
       <c r="S48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$42,0,(IF($A48=VARIABLES!$B$42,0,S47)+P48)*(1+C48)-R48)</f>
-        <v>1857005.5494945841</v>
+        <v>1475126.3885533803</v>
       </c>
       <c r="T48" s="34">
         <f>IF($A48&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A48-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="U48" s="14">
         <f>T48*VARIABLES!$B$53+IF(AND($A48&gt;=VARIABLES!$B$50,MOD($A48-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A48-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>265000</v>
       </c>
       <c r="V48" s="14">
         <f>U48*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>1987.5</v>
       </c>
       <c r="W48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$50,0,(IF($A48&lt;VARIABLES!$B$50+1,0,X47)+U48)*C48*VARIABLES!$B$55)</f>
-        <v>4542.2401949263494</v>
+        <v>7172.1463175120625</v>
       </c>
       <c r="X48" s="14">
         <f>IF($A48&lt;VARIABLES!$B$50,0,(IF($A48&lt;VARIABLES!$B$50+1,0,X47)+U48)*(1+C48)-W48)</f>
-        <v>5491568.3956659557</v>
+        <v>9627411.0735403597</v>
       </c>
       <c r="Y48" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>525000</v>
       </c>
       <c r="Z48" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3937.5</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="2"/>
-        <v>28155.748488933721</v>
+        <v>22371.138318895039</v>
       </c>
       <c r="AB48" s="35">
         <f t="shared" si="3"/>
-        <v>30555.748488933721</v>
+        <v>26308.638318895039</v>
       </c>
       <c r="AC48" s="36">
         <f t="shared" si="4"/>
-        <v>51055540.815345481</v>
+        <v>43300574.952244766</v>
       </c>
       <c r="AD48" s="14">
         <f>IF($A48=1,VARIABLES!$B$12,0)</f>
@@ -11071,15 +11071,15 @@
       </c>
       <c r="AK48" s="39">
         <f t="shared" si="6"/>
-        <v>-14444.251511066279</v>
+        <v>-18691.361681104961</v>
       </c>
       <c r="AL48" s="39">
-        <f t="shared" si="7"/>
-        <v>-598064.97601016588</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM48" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>83335.137654573453</v>
       </c>
     </row>
     <row r="49" spans="1:39" x14ac:dyDescent="0.2">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="C49" s="42">
         <f>IF($A49&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$21,0,IF($A49=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -11104,11 +11104,11 @@
       </c>
       <c r="F49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$21,0,(IF($A49=VARIABLES!$B$21,0,G48)+D49)*C49*VARIABLES!$B$25)</f>
-        <v>4380.2697734624398</v>
+        <v>3078.0589230816681</v>
       </c>
       <c r="G49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$21,0,(IF($A49=VARIABLES!$B$21,0,G48)+D49)*(1+C49)-F49)</f>
-        <v>21196125.433784746</v>
+        <v>16536358.554435749</v>
       </c>
       <c r="H49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$28,0,IF($A49=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11120,11 +11120,11 @@
       </c>
       <c r="J49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$28,0,(IF($A49=VARIABLES!$B$28,0,K48)+H49)*C49*VARIABLES!$B$32)</f>
-        <v>2936.3102532040975</v>
+        <v>2149.2506551317906</v>
       </c>
       <c r="K49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$28,0,(IF($A49=VARIABLES!$B$28,0,K48)+H49)*(1+C49)-J49)</f>
-        <v>3549999.0961237536</v>
+        <v>2885010.796071907</v>
       </c>
       <c r="L49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$35,0,IF($A49=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11136,11 +11136,11 @@
       </c>
       <c r="N49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$35,0,(IF($A49=VARIABLES!$B$35,0,O48)+L49)*C49*VARIABLES!$B$39)</f>
-        <v>16165.083044766923</v>
+        <v>9867.0417701548049</v>
       </c>
       <c r="O49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$35,0,(IF($A49=VARIABLES!$B$35,0,O48)+L49)*(1+C49)-N49)</f>
-        <v>19543585.401123211</v>
+        <v>13244859.069471132</v>
       </c>
       <c r="P49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$42,0,IF($A49=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11152,51 +11152,51 @@
       </c>
       <c r="R49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$42,0,(IF($A49=VARIABLES!$B$42,0,S48)+P49)*C49*VARIABLES!$B$46)</f>
-        <v>391.04282281137171</v>
+        <v>280.33619785375879</v>
       </c>
       <c r="S49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$42,0,(IF($A49=VARIABLES!$B$42,0,S48)+P49)*(1+C49)-R49)</f>
-        <v>1892256.2195842275</v>
+        <v>1506059.500269677</v>
       </c>
       <c r="T49" s="44">
         <f>IF($A49&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A49-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="U49" s="43">
         <f>T49*VARIABLES!$B$53+IF(AND($A49&gt;=VARIABLES!$B$50,MOD($A49-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A49-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>270000</v>
       </c>
       <c r="V49" s="43">
         <f>U49*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>2025</v>
       </c>
       <c r="W49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$50,0,(IF($A49&lt;VARIABLES!$B$50+1,0,X48)+U49)*C49*VARIABLES!$B$55)</f>
-        <v>4626.3069963882963</v>
+        <v>7423.0583051552694</v>
       </c>
       <c r="X49" s="43">
         <f>IF($A49&lt;VARIABLES!$B$50,0,(IF($A49&lt;VARIABLES!$B$50+1,0,X48)+U49)*(1+C49)-W49)</f>
-        <v>5593205.15863345</v>
+        <v>9964218.5982867572</v>
       </c>
       <c r="Y49" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>530000</v>
       </c>
       <c r="Z49" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>3975</v>
       </c>
       <c r="AA49" s="43">
         <f t="shared" si="2"/>
-        <v>28499.012890633127</v>
+        <v>22797.745851377294</v>
       </c>
       <c r="AB49" s="35">
         <f t="shared" si="3"/>
-        <v>30899.012890633127</v>
+        <v>26772.745851377294</v>
       </c>
       <c r="AC49" s="36">
         <f t="shared" si="4"/>
-        <v>51775171.309249386</v>
+        <v>44136506.518535219</v>
       </c>
       <c r="AD49" s="43">
         <f>IF($A49=1,VARIABLES!$B$12,0)</f>
@@ -11228,15 +11228,15 @@
       </c>
       <c r="AK49" s="45">
         <f t="shared" si="6"/>
-        <v>-14100.987109366873</v>
+        <v>-18227.254148622706</v>
       </c>
       <c r="AL49" s="45">
-        <f t="shared" si="7"/>
-        <v>-612165.9631195328</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM49" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>65107.883505950747</v>
       </c>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.2">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="C50" s="33">
         <f>IF($A50&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$21,0,IF($A50=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -11261,11 +11261,11 @@
       </c>
       <c r="F50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$21,0,(IF($A50=VARIABLES!$B$21,0,G49)+D50)*C50*VARIABLES!$B$25)</f>
-        <v>4457.5261320384889</v>
+        <v>3138.0672289567028</v>
       </c>
       <c r="G50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$21,0,(IF($A50=VARIABLES!$B$21,0,G49)+D50)*(1+C50)-F50)</f>
-        <v>21569968.952934247</v>
+        <v>16858743.176365059</v>
       </c>
       <c r="H50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$28,0,IF($A50=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11277,11 +11277,11 @@
       </c>
       <c r="J50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$28,0,(IF($A50=VARIABLES!$B$28,0,K49)+H50)*C50*VARIABLES!$B$32)</f>
-        <v>2991.6659134364618</v>
+        <v>2193.7580970539302</v>
       </c>
       <c r="K50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$28,0,(IF($A50=VARIABLES!$B$28,0,K49)+H50)*(1+C50)-J50)</f>
-        <v>3616924.0893446817</v>
+        <v>2944754.6189453928</v>
       </c>
       <c r="L50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$35,0,IF($A50=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11293,11 +11293,11 @@
       </c>
       <c r="N50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$35,0,(IF($A50=VARIABLES!$B$35,0,O49)+L50)*C50*VARIABLES!$B$39)</f>
-        <v>16286.321167602677</v>
+        <v>9933.6443021033483</v>
       </c>
       <c r="O50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$35,0,(IF($A50=VARIABLES!$B$35,0,O49)+L50)*(1+C50)-N50)</f>
-        <v>19690162.291631635</v>
+        <v>13334261.868190063</v>
       </c>
       <c r="P50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$42,0,IF($A50=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11309,51 +11309,51 @@
       </c>
       <c r="R50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$42,0,(IF($A50=VARIABLES!$B$42,0,S49)+P50)*C50*VARIABLES!$B$46)</f>
-        <v>398.38671241338079</v>
+        <v>286.13615630056444</v>
       </c>
       <c r="S50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$42,0,(IF($A50=VARIABLES!$B$42,0,S49)+P50)*(1+C50)-R50)</f>
-        <v>1927793.3013683495</v>
+        <v>1537218.8103653991</v>
       </c>
       <c r="T50" s="34">
         <f>IF($A50&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A50-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="U50" s="14">
         <f>T50*VARIABLES!$B$53+IF(AND($A50&gt;=VARIABLES!$B$50,MOD($A50-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A50-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>275000</v>
       </c>
       <c r="V50" s="14">
         <f>U50*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>2062.5</v>
       </c>
       <c r="W50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$50,0,(IF($A50&lt;VARIABLES!$B$50+1,0,X49)+U50)*C50*VARIABLES!$B$55)</f>
-        <v>4711.0042988612086</v>
+        <v>7679.4139487150678</v>
       </c>
       <c r="X50" s="14">
         <f>IF($A50&lt;VARIABLES!$B$50,0,(IF($A50&lt;VARIABLES!$B$50+1,0,X49)+U50)*(1+C50)-W50)</f>
-        <v>5695604.1973232012</v>
+        <v>10308333.323825194</v>
       </c>
       <c r="Y50" s="14">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>535000</v>
       </c>
       <c r="Z50" s="14">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>4012.5</v>
       </c>
       <c r="AA50" s="14">
         <f t="shared" si="2"/>
-        <v>28844.904224352213</v>
+        <v>23231.019733129615</v>
       </c>
       <c r="AB50" s="35">
         <f t="shared" si="3"/>
-        <v>31244.904224352213</v>
+        <v>27243.519733129615</v>
       </c>
       <c r="AC50" s="36">
         <f t="shared" si="4"/>
-        <v>52500452.832602113</v>
+        <v>44983311.797691114</v>
       </c>
       <c r="AD50" s="14">
         <f>IF($A50=1,VARIABLES!$B$12,0)</f>
@@ -11385,15 +11385,15 @@
       </c>
       <c r="AK50" s="39">
         <f t="shared" si="6"/>
-        <v>-13755.095775647787</v>
+        <v>-17756.480266870385</v>
       </c>
       <c r="AL50" s="39">
-        <f t="shared" si="7"/>
-        <v>-625921.05889518058</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM50" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>47351.403239080362</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.2">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="C51" s="42">
         <f>IF($A51&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>8.3333333333333332E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$21,0,IF($A51=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -11418,11 +11418,11 @@
       </c>
       <c r="F51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$21,0,(IF($A51=VARIABLES!$B$21,0,G50)+D51)*C51*VARIABLES!$B$25)</f>
-        <v>4535.4101985279685</v>
+        <v>3198.5143455684483</v>
       </c>
       <c r="G51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$21,0,(IF($A51=VARIABLES!$B$21,0,G50)+D51)*(1+C51)-F51)</f>
-        <v>21946849.950676836</v>
+        <v>17183485.235842232</v>
       </c>
       <c r="H51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$28,0,IF($A51=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11434,11 +11434,11 @@
       </c>
       <c r="J51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$28,0,(IF($A51=VARIABLES!$B$28,0,K50)+H51)*C51*VARIABLES!$B$32)</f>
-        <v>3047.4367411205681</v>
+        <v>2238.5659642090445</v>
       </c>
       <c r="K51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$28,0,(IF($A51=VARIABLES!$B$28,0,K50)+H51)*(1+C51)-J51)</f>
-        <v>3684351.0200147666</v>
+        <v>3004901.7126232744</v>
       </c>
       <c r="L51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$35,0,IF($A51=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11450,11 +11450,11 @@
       </c>
       <c r="N51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$35,0,(IF($A51=VARIABLES!$B$35,0,O50)+L51)*C51*VARIABLES!$B$39)</f>
-        <v>16408.468576359697</v>
+        <v>10000.696401142548</v>
       </c>
       <c r="O51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$35,0,(IF($A51=VARIABLES!$B$35,0,O50)+L51)*(1+C51)-N51)</f>
-        <v>19837838.508818872</v>
+        <v>13424268.135800347</v>
       </c>
       <c r="P51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$42,0,IF($A51=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11466,51 +11466,51 @@
       </c>
       <c r="R51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$42,0,(IF($A51=VARIABLES!$B$42,0,S50)+P51)*C51*VARIABLES!$B$46)</f>
-        <v>405.79027111840617</v>
+        <v>291.97852694351235</v>
       </c>
       <c r="S51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$42,0,(IF($A51=VARIABLES!$B$42,0,S50)+P51)*(1+C51)-R51)</f>
-        <v>1963619.1219419672</v>
+        <v>1568605.9729161961</v>
       </c>
       <c r="T51" s="44">
         <f>IF($A51&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A51-VARIABLES!$B$50)/VARIABLES!$B$51)+1))</f>
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="U51" s="43">
         <f>T51*VARIABLES!$B$53+IF(AND($A51&gt;=VARIABLES!$B$50,MOD($A51-VARIABLES!$B$50,VARIABLES!$B$51)=0,($A51-VARIABLES!$B$50)/VARIABLES!$B$51&lt;VARIABLES!$B$49),VARIABLES!$B$52,0)</f>
-        <v>60000</v>
+        <v>280000</v>
       </c>
       <c r="V51" s="43">
         <f>U51*VARIABLES!$B$54</f>
-        <v>450</v>
+        <v>2100</v>
       </c>
       <c r="W51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$50,0,(IF($A51&lt;VARIABLES!$B$50+1,0,X50)+U51)*C51*VARIABLES!$B$55)</f>
-        <v>4796.3368311026679</v>
+        <v>7941.2499928688958</v>
       </c>
       <c r="X51" s="43">
         <f>IF($A51&lt;VARIABLES!$B$50,0,(IF($A51&lt;VARIABLES!$B$50+1,0,X50)+U51)*(1+C51)-W51)</f>
-        <v>5798771.2288031243</v>
+        <v>10659804.573761014</v>
       </c>
       <c r="Y51" s="43">
         <f t="shared" si="0"/>
-        <v>320000</v>
+        <v>540000</v>
       </c>
       <c r="Z51" s="43">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>4050</v>
       </c>
       <c r="AA51" s="43">
         <f t="shared" si="2"/>
-        <v>29193.442618229306</v>
+        <v>23671.005230732451</v>
       </c>
       <c r="AB51" s="35">
         <f t="shared" si="3"/>
-        <v>31593.442618229306</v>
+        <v>27721.005230732451</v>
       </c>
       <c r="AC51" s="36">
         <f t="shared" si="4"/>
-        <v>53231429.830255568</v>
+        <v>45841065.630943067</v>
       </c>
       <c r="AD51" s="43">
         <f>IF($A51=1,VARIABLES!$B$12,0)</f>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AF51" s="43">
         <f>IF(MOD($A51,12)=0,AC51*VARIABLES!$B$16,0)</f>
-        <v>133078.57457563892</v>
+        <v>114602.66407735767</v>
       </c>
       <c r="AG51" s="43">
         <f>VARIABLES!$B$17</f>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AI51" s="37">
         <f t="shared" si="5"/>
-        <v>181078.57457563892</v>
+        <v>162602.66407735768</v>
       </c>
       <c r="AJ51" s="38">
         <f>IF($A51&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11542,86 +11542,86 @@
       </c>
       <c r="AK51" s="45">
         <f t="shared" si="6"/>
-        <v>-149485.13195740961</v>
+        <v>-134881.65884662524</v>
       </c>
       <c r="AL51" s="45">
-        <f t="shared" si="7"/>
-        <v>-775406.19085259014</v>
+        <f t="shared" si="9"/>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM51" s="40">
         <f t="shared" si="8"/>
-        <v>957000.00000000047</v>
+        <v>-87530.255607544881</v>
       </c>
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A52" s="46" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B52" s="6"/>
       <c r="Y52" s="47">
         <f>SUM(Y4:Y51)</f>
-        <v>20690000</v>
+        <v>25425000</v>
       </c>
       <c r="Z52" s="47">
         <f>SUM(Z4:Z51)</f>
-        <v>155175</v>
+        <v>190687.5</v>
       </c>
       <c r="AA52" s="47">
         <f>SUM(AA4:AA51)</f>
-        <v>2498580.3168131122</v>
+        <v>1592204.6249117595</v>
       </c>
       <c r="AB52" s="47">
         <f>SUM(AB4:AB51)</f>
-        <v>2653755.3168131113</v>
+        <v>1782892.1249117597</v>
       </c>
       <c r="AC52" s="47">
         <f>AC51</f>
-        <v>53231429.830255568</v>
+        <v>45841065.630943067</v>
       </c>
       <c r="AD52" s="47">
-        <f t="shared" ref="AD52:AK52" si="9">SUM(AD4:AD51)</f>
+        <f t="shared" ref="AD52:AK52" si="10">SUM(AD4:AD51)</f>
         <v>50000</v>
       </c>
       <c r="AE52" s="47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1830000</v>
       </c>
       <c r="AF52" s="47">
-        <f t="shared" si="9"/>
-        <v>340161.50766570214</v>
+        <f t="shared" si="10"/>
+        <v>288318.65973210265</v>
       </c>
       <c r="AG52" s="47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>240000</v>
       </c>
       <c r="AH52" s="47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12000</v>
       </c>
       <c r="AI52" s="47">
-        <f t="shared" si="9"/>
-        <v>2472161.5076657021</v>
+        <f t="shared" si="10"/>
+        <v>2420318.6597321029</v>
       </c>
       <c r="AJ52" s="47">
-        <f t="shared" si="9"/>
-        <v>957000.00000000047</v>
+        <f t="shared" si="10"/>
+        <v>267480</v>
       </c>
       <c r="AK52" s="47">
-        <f t="shared" si="9"/>
-        <v>-775406.19085259014</v>
+        <f t="shared" si="10"/>
+        <v>-904906.53482034302</v>
       </c>
       <c r="AL52" s="47">
         <f>AL51</f>
-        <v>-775406.19085259014</v>
+        <v>-549896.27921279822</v>
       </c>
       <c r="AM52" s="47">
         <f>AM51</f>
-        <v>957000.00000000047</v>
+        <v>-87530.255607544881</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:39" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -11690,7 +11690,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
